--- a/Undigitised_Records.xlsx
+++ b/Undigitised_Records.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sotonac-my.sharepoint.com/personal/ck1g20_soton_ac_uk/Documents/Documents/PhD/20_Historical_record_catalogue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="177" documentId="8_{2EBFFBB5-AA1D-4DD9-A43A-243907206CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9F96041-261D-4B3D-8D8D-35559416F685}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="8_{2EBFFBB5-AA1D-4DD9-A43A-243907206CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A68813BD-25DA-42FC-8298-11136F99AE1F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B145EA35-1BD5-495C-A7E0-BAB6ECA9BC95}"/>
   </bookViews>
@@ -2676,6 +2676,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3066,7 +3070,7 @@
         <v>1953</v>
       </c>
       <c r="G2" s="9">
-        <f>(1+(F2-E2))-I2</f>
+        <f t="shared" ref="G2:G7" si="0">(1+(F2-E2))-I2</f>
         <v>2</v>
       </c>
       <c r="H2" s="8" t="s">
@@ -3102,7 +3106,7 @@
         <v>1958</v>
       </c>
       <c r="G3" s="9">
-        <f>(1+(F3-E3))-I3</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H3" s="8" t="s">
@@ -3138,7 +3142,7 @@
         <v>1931</v>
       </c>
       <c r="G4" s="9">
-        <f>(1+(F4-E4))-I4</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H4" s="8" t="s">
@@ -3174,7 +3178,7 @@
         <v>1850</v>
       </c>
       <c r="G5" s="9">
-        <f>(1+(F5-E5))-I5</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="H5" s="8" t="s">
@@ -3210,7 +3214,7 @@
         <v>1921</v>
       </c>
       <c r="G6" s="9">
-        <f>(1+(F6-E6))-I6</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -3246,7 +3250,7 @@
         <v>1958</v>
       </c>
       <c r="G7" s="9">
-        <f>(1+(F7-E7))-I7</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H7" s="8" t="s">
@@ -3317,7 +3321,7 @@
         <v>1958</v>
       </c>
       <c r="G9" s="9">
-        <f>(1+(F9-E9))-I9</f>
+        <f t="shared" ref="G9:G14" si="1">(1+(F9-E9))-I9</f>
         <v>3</v>
       </c>
       <c r="H9" s="8" t="s">
@@ -3353,7 +3357,7 @@
         <v>1984</v>
       </c>
       <c r="G10" s="9">
-        <f>(1+(F10-E10))-I10</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="H10" s="8" t="s">
@@ -3389,7 +3393,7 @@
         <v>1986</v>
       </c>
       <c r="G11" s="9">
-        <f>(1+(F11-E11))-I11</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="H11" s="8" t="s">
@@ -3425,7 +3429,7 @@
         <v>1803</v>
       </c>
       <c r="G12" s="9">
-        <f>(1+(F12-E12))-I12</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="H12" s="8" t="s">
@@ -3461,7 +3465,7 @@
         <v>1808</v>
       </c>
       <c r="G13" s="9">
-        <f>(1+(F13-E13))-I13</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="H13" s="8" t="s">
@@ -3497,7 +3501,7 @@
         <v>1973</v>
       </c>
       <c r="G14" s="9">
-        <f>(1+(F14-E14))-I14</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="H14" s="8" t="s">
@@ -3568,7 +3572,7 @@
         <v>1952</v>
       </c>
       <c r="G16" s="9">
-        <f>(1+(F16-E16))-I16</f>
+        <f t="shared" ref="G16:G47" si="2">(1+(F16-E16))-I16</f>
         <v>2</v>
       </c>
       <c r="H16" s="8" t="s">
@@ -3604,7 +3608,7 @@
         <v>1938</v>
       </c>
       <c r="G17" s="9">
-        <f>(1+(F17-E17))-I17</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H17" s="8" t="s">
@@ -3640,7 +3644,7 @@
         <v>1868</v>
       </c>
       <c r="G18" s="9">
-        <f>(1+(F18-E18))-I18</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="H18" s="8" t="s">
@@ -3676,7 +3680,7 @@
         <v>1930</v>
       </c>
       <c r="G19" s="9">
-        <f>(1+(F19-E19))-I19</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H19" s="8" t="s">
@@ -3712,7 +3716,7 @@
         <v>1928</v>
       </c>
       <c r="G20" s="9">
-        <f>(1+(F20-E20))-I20</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H20" s="8" t="s">
@@ -3748,7 +3752,7 @@
         <v>1955</v>
       </c>
       <c r="G21" s="9">
-        <f>(1+(F21-E21))-I21</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H21" s="8" t="s">
@@ -3784,7 +3788,7 @@
         <v>1955</v>
       </c>
       <c r="G22" s="9">
-        <f>(1+(F22-E22))-I22</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="H22" s="8" t="s">
@@ -3821,7 +3825,7 @@
         <v>1915</v>
       </c>
       <c r="G23" s="9">
-        <f>(1+(F23-E23))-I23</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H23" s="8" t="s">
@@ -3858,7 +3862,7 @@
         <v>1862</v>
       </c>
       <c r="G24" s="9">
-        <f>(1+(F24-E24))-I24</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="H24" s="8" t="s">
@@ -3895,7 +3899,7 @@
         <v>1909</v>
       </c>
       <c r="G25" s="9">
-        <f>(1+(F25-E25))-I25</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="H25" s="8" t="s">
@@ -3932,7 +3936,7 @@
         <v>1948</v>
       </c>
       <c r="G26" s="9">
-        <f>(1+(F26-E26))-I26</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="H26" s="8" t="s">
@@ -3969,7 +3973,7 @@
         <v>1926</v>
       </c>
       <c r="G27" s="9">
-        <f>(1+(F27-E27))-I27</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="H27" s="8" t="s">
@@ -4006,7 +4010,7 @@
         <v>1950</v>
       </c>
       <c r="G28" s="9">
-        <f>(1+(F28-E28))-I28</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="H28" s="8" t="s">
@@ -4043,7 +4047,7 @@
         <v>1900</v>
       </c>
       <c r="G29" s="9">
-        <f>(1+(F29-E29))-I29</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H29" s="8" t="s">
@@ -4080,7 +4084,7 @@
         <v>1911</v>
       </c>
       <c r="G30" s="9">
-        <f>(1+(F30-E30))-I30</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="H30" s="8" t="s">
@@ -4117,7 +4121,7 @@
         <v>1914</v>
       </c>
       <c r="G31" s="9">
-        <f>(1+(F31-E31))-I31</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="H31" s="8" t="s">
@@ -4154,7 +4158,7 @@
         <v>1926</v>
       </c>
       <c r="G32" s="9">
-        <f>(1+(F32-E32))-I32</f>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="H32" s="8" t="s">
@@ -4191,7 +4195,7 @@
         <v>1926</v>
       </c>
       <c r="G33" s="9">
-        <f>(1+(F33-E33))-I33</f>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="H33" s="8" t="s">
@@ -4228,7 +4232,7 @@
         <v>1960</v>
       </c>
       <c r="G34" s="9">
-        <f>(1+(F34-E34))-I34</f>
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
       <c r="H34" s="8" t="s">
@@ -4265,7 +4269,7 @@
         <v>1930</v>
       </c>
       <c r="G35" s="9">
-        <f>(1+(F35-E35))-I35</f>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="H35" s="8" t="s">
@@ -4302,7 +4306,7 @@
         <v>1914</v>
       </c>
       <c r="G36" s="9">
-        <f>(1+(F36-E36))-I36</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="H36" s="8" t="s">
@@ -4339,7 +4343,7 @@
         <v>1942</v>
       </c>
       <c r="G37" s="9">
-        <f>(1+(F37-E37))-I37</f>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="H37" s="8" t="s">
@@ -4376,7 +4380,7 @@
         <v>1940</v>
       </c>
       <c r="G38" s="9">
-        <f>(1+(F38-E38))-I38</f>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="H38" s="8" t="s">
@@ -4413,7 +4417,7 @@
         <v>1908</v>
       </c>
       <c r="G39" s="9">
-        <f>(1+(F39-E39))-I39</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="H39" s="8" t="s">
@@ -4450,7 +4454,7 @@
         <v>1950</v>
       </c>
       <c r="G40" s="9">
-        <f>(1+(F40-E40))-I40</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="H40" s="8" t="s">
@@ -4487,7 +4491,7 @@
         <v>1950</v>
       </c>
       <c r="G41" s="9">
-        <f>(1+(F41-E41))-I41</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="H41" s="8" t="s">
@@ -4524,7 +4528,7 @@
         <v>1888</v>
       </c>
       <c r="G42" s="9">
-        <f>(1+(F42-E42))-I42</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H42" s="8" t="s">
@@ -4561,7 +4565,7 @@
         <v>1995</v>
       </c>
       <c r="G43" s="9">
-        <f>(1+(F43-E43))-I43</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="H43" s="8" t="s">
@@ -4598,7 +4602,7 @@
         <v>1883</v>
       </c>
       <c r="G44" s="9">
-        <f>(1+(F44-E44))-I44</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="H44" s="8" t="s">
@@ -4635,7 +4639,7 @@
         <v>1901</v>
       </c>
       <c r="G45" s="9">
-        <f>(1+(F45-E45))-I45</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H45" s="8" t="s">
@@ -4672,7 +4676,7 @@
         <v>1860</v>
       </c>
       <c r="G46" s="9">
-        <f>(1+(F46-E46))-I46</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H46" s="8" t="s">
@@ -4709,7 +4713,7 @@
         <v>1980</v>
       </c>
       <c r="G47" s="9">
-        <f>(1+(F47-E47))-I47</f>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="H47" s="8" t="s">
@@ -4746,7 +4750,7 @@
         <v>1974</v>
       </c>
       <c r="G48" s="9">
-        <f>(1+(F48-E48))-I48</f>
+        <f t="shared" ref="G48:G79" si="3">(1+(F48-E48))-I48</f>
         <v>85</v>
       </c>
       <c r="H48" s="8" t="s">
@@ -4783,7 +4787,7 @@
         <v>1972</v>
       </c>
       <c r="G49" s="9">
-        <f>(1+(F49-E49))-I49</f>
+        <f t="shared" si="3"/>
         <v>83</v>
       </c>
       <c r="H49" s="8" t="s">
@@ -4820,7 +4824,7 @@
         <v>1971</v>
       </c>
       <c r="G50" s="9">
-        <f>(1+(F50-E50))-I50</f>
+        <f t="shared" si="3"/>
         <v>82</v>
       </c>
       <c r="H50" s="8" t="s">
@@ -4857,7 +4861,7 @@
         <v>1969</v>
       </c>
       <c r="G51" s="9">
-        <f>(1+(F51-E51))-I51</f>
+        <f t="shared" si="3"/>
         <v>47</v>
       </c>
       <c r="H51" s="8" t="s">
@@ -4894,7 +4898,7 @@
         <v>1972</v>
       </c>
       <c r="G52" s="9">
-        <f>(1+(F52-E52))-I52</f>
+        <f t="shared" si="3"/>
         <v>83</v>
       </c>
       <c r="H52" s="8" t="s">
@@ -4931,7 +4935,7 @@
         <v>1970</v>
       </c>
       <c r="G53" s="9">
-        <f>(1+(F53-E53))-I53</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="H53" s="8" t="s">
@@ -4968,7 +4972,7 @@
         <v>1970</v>
       </c>
       <c r="G54" s="9">
-        <f>(1+(F54-E54))-I54</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="H54" s="8" t="s">
@@ -5005,7 +5009,7 @@
         <v>1891</v>
       </c>
       <c r="G55" s="9">
-        <f>(1+(F55-E55))-I55</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="H55" s="8" t="s">
@@ -5042,7 +5046,7 @@
         <v>1952</v>
       </c>
       <c r="G56" s="9">
-        <f>(1+(F56-E56))-I56</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="H56" s="8" t="s">
@@ -5079,7 +5083,7 @@
         <v>1928</v>
       </c>
       <c r="G57" s="9">
-        <f>(1+(F57-E57))-I57</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="H57" s="8" t="s">
@@ -5116,7 +5120,7 @@
         <v>1899</v>
       </c>
       <c r="G58" s="9">
-        <f>(1+(F58-E58))-I58</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H58" s="8" t="s">
@@ -5154,7 +5158,7 @@
         <v>1956</v>
       </c>
       <c r="G59" s="9">
-        <f>(1+(F59-E59))-I59</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="H59" s="8" t="s">
@@ -5191,7 +5195,7 @@
         <v>1951</v>
       </c>
       <c r="G60" s="9">
-        <f>(1+(F60-E60))-I60</f>
+        <f t="shared" si="3"/>
         <v>61</v>
       </c>
       <c r="H60" s="8" t="s">
@@ -5228,7 +5232,7 @@
         <v>1949</v>
       </c>
       <c r="G61" s="9">
-        <f>(1+(F61-E61))-I61</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="H61" s="8" t="s">
@@ -5265,7 +5269,7 @@
         <v>1978</v>
       </c>
       <c r="G62" s="9">
-        <f>(1+(F62-E62))-I62</f>
+        <f t="shared" si="3"/>
         <v>74</v>
       </c>
       <c r="H62" s="8" t="s">
@@ -5302,7 +5306,7 @@
         <v>1954</v>
       </c>
       <c r="G63" s="9">
-        <f>(1+(F63-E63))-I63</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="H63" s="8" t="s">
@@ -5339,7 +5343,7 @@
         <v>1985</v>
       </c>
       <c r="G64" s="9">
-        <f>(1+(F64-E64))-I64</f>
+        <f t="shared" si="3"/>
         <v>49</v>
       </c>
       <c r="H64" s="8" t="s">
@@ -5377,7 +5381,7 @@
         <v>1834</v>
       </c>
       <c r="G65" s="9">
-        <f>(1+(F65-E65))-I65</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H65" s="8" t="s">
@@ -5414,7 +5418,7 @@
         <v>1936</v>
       </c>
       <c r="G66" s="9">
-        <f>(1+(F66-E66))-I66</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="H66" s="8" t="s">
@@ -5452,7 +5456,7 @@
         <v>1954</v>
       </c>
       <c r="G67" s="9">
-        <f>(1+(F67-E67))-I67</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="H67" s="8" t="s">
@@ -5489,7 +5493,7 @@
         <v>1878</v>
       </c>
       <c r="G68" s="9">
-        <f>(1+(F68-E68))-I68</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H68" s="8" t="s">
@@ -5526,7 +5530,7 @@
         <v>1937</v>
       </c>
       <c r="G69" s="9">
-        <f>(1+(F69-E69))-I69</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H69" s="8" t="s">
@@ -5563,7 +5567,7 @@
         <v>1978</v>
       </c>
       <c r="G70" s="9">
-        <f>(1+(F70-E70))-I70</f>
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
       <c r="H70" s="8" t="s">
@@ -5601,7 +5605,7 @@
         <v>1896</v>
       </c>
       <c r="G71" s="9">
-        <f>(1+(F71-E71))-I71</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="H71" s="8" t="s">
@@ -5639,7 +5643,7 @@
         <v>1869</v>
       </c>
       <c r="G72" s="9">
-        <f>(1+(F72-E72))-I72</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H72" s="8" t="s">
@@ -5676,7 +5680,7 @@
         <v>1878</v>
       </c>
       <c r="G73" s="9">
-        <f>(1+(F73-E73))-I73</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="H73" s="8" t="s">
@@ -5713,7 +5717,7 @@
         <v>1850</v>
       </c>
       <c r="G74" s="9">
-        <f>(1+(F74-E74))-I74</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="H74" s="8" t="s">
@@ -5750,7 +5754,7 @@
         <v>1950</v>
       </c>
       <c r="G75" s="9">
-        <f>(1+(F75-E75))-I75</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="H75" s="8" t="s">
@@ -5787,7 +5791,7 @@
         <v>1869</v>
       </c>
       <c r="G76" s="9">
-        <f>(1+(F76-E76))-I76</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="H76" s="8" t="s">
@@ -5824,7 +5828,7 @@
         <v>1962</v>
       </c>
       <c r="G77" s="9">
-        <f>(1+(F77-E77))-I77</f>
+        <f t="shared" si="3"/>
         <v>73</v>
       </c>
       <c r="H77" s="8" t="s">
@@ -5861,7 +5865,7 @@
         <v>1920</v>
       </c>
       <c r="G78" s="9">
-        <f>(1+(F78-E78))-I78</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="H78" s="8" t="s">
@@ -5898,7 +5902,7 @@
         <v>1976</v>
       </c>
       <c r="G79" s="9">
-        <f>(1+(F79-E79))-I79</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="H79" s="8" t="s">
@@ -5935,7 +5939,7 @@
         <v>1982</v>
       </c>
       <c r="G80" s="9">
-        <f>(1+(F80-E80))-I80</f>
+        <f t="shared" ref="G80:G111" si="4">(1+(F80-E80))-I80</f>
         <v>9</v>
       </c>
       <c r="H80" s="8" t="s">
@@ -5972,7 +5976,7 @@
         <v>1913</v>
       </c>
       <c r="G81" s="9">
-        <f>(1+(F81-E81))-I81</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H81" s="8" t="s">
@@ -6009,7 +6013,7 @@
         <v>1860</v>
       </c>
       <c r="G82" s="9">
-        <f>(1+(F82-E82))-I82</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="H82" s="8">
@@ -6046,7 +6050,7 @@
         <v>1869</v>
       </c>
       <c r="G83" s="9">
-        <f>(1+(F83-E83))-I83</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H83" s="8" t="s">
@@ -6083,7 +6087,7 @@
         <v>1960</v>
       </c>
       <c r="G84" s="9">
-        <f>(1+(F84-E84))-I84</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="H84" s="8" t="s">
@@ -6120,7 +6124,7 @@
         <v>1951</v>
       </c>
       <c r="G85" s="9">
-        <f>(1+(F85-E85))-I85</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="H85" s="8" t="s">
@@ -6157,7 +6161,7 @@
         <v>1876</v>
       </c>
       <c r="G86" s="9">
-        <f>(1+(F86-E86))-I86</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H86" s="8" t="s">
@@ -6194,7 +6198,7 @@
         <v>1933</v>
       </c>
       <c r="G87" s="9">
-        <f>(1+(F87-E87))-I87</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H87" s="8" t="s">
@@ -6231,7 +6235,7 @@
         <v>1951</v>
       </c>
       <c r="G88" s="9">
-        <f>(1+(F88-E88))-I88</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="H88" s="8" t="s">
@@ -6268,7 +6272,7 @@
         <v>1950</v>
       </c>
       <c r="G89" s="9">
-        <f>(1+(F89-E89))-I89</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="H89" s="8" t="s">
@@ -6305,7 +6309,7 @@
         <v>1979</v>
       </c>
       <c r="G90" s="9">
-        <f>(1+(F90-E90))-I90</f>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="H90" s="8" t="s">
@@ -6342,7 +6346,7 @@
         <v>1914</v>
       </c>
       <c r="G91" s="9">
-        <f>(1+(F91-E91))-I91</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="H91" s="8" t="s">
@@ -6379,7 +6383,7 @@
         <v>1922</v>
       </c>
       <c r="G92" s="9">
-        <f>(1+(F92-E92))-I92</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H92" s="8" t="s">
@@ -6416,7 +6420,7 @@
         <v>1952</v>
       </c>
       <c r="G93" s="9">
-        <f>(1+(F93-E93))-I93</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H93" s="8" t="s">
@@ -6453,7 +6457,7 @@
         <v>1922</v>
       </c>
       <c r="G94" s="9">
-        <f>(1+(F94-E94))-I94</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H94" s="8" t="s">
@@ -6490,7 +6494,7 @@
         <v>1902</v>
       </c>
       <c r="G95" s="9">
-        <f>(1+(F95-E95))-I95</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H95" s="8" t="s">
@@ -6527,7 +6531,7 @@
         <v>1902</v>
       </c>
       <c r="G96" s="9">
-        <f>(1+(F96-E96))-I96</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H96" s="8" t="s">
@@ -6564,7 +6568,7 @@
         <v>1832</v>
       </c>
       <c r="G97" s="9">
-        <f>(1+(F97-E97))-I97</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H97" s="8" t="s">
@@ -6601,7 +6605,7 @@
         <v>1924</v>
       </c>
       <c r="G98" s="9">
-        <f>(1+(F98-E98))-I98</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H98" s="8" t="s">
@@ -6638,7 +6642,7 @@
         <v>1922</v>
       </c>
       <c r="G99" s="9">
-        <f>(1+(F99-E99))-I99</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="H99" s="8" t="s">
@@ -6675,7 +6679,7 @@
         <v>1840</v>
       </c>
       <c r="G100" s="9">
-        <f>(1+(F100-E100))-I100</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="H100" s="8" t="s">
@@ -6712,7 +6716,7 @@
         <v>1840</v>
       </c>
       <c r="G101" s="9">
-        <f>(1+(F101-E101))-I101</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="H101" s="8" t="s">
@@ -6749,7 +6753,7 @@
         <v>1924</v>
       </c>
       <c r="G102" s="9">
-        <f>(1+(F102-E102))-I102</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="H102" s="8" t="s">
@@ -6786,7 +6790,7 @@
         <v>1960</v>
       </c>
       <c r="G103" s="9">
-        <f>(1+(F103-E103))-I103</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H103" s="8" t="s">
@@ -6823,7 +6827,7 @@
         <v>1841</v>
       </c>
       <c r="G104" s="9">
-        <f>(1+(F104-E104))-I104</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="H104" s="8" t="s">
@@ -6860,7 +6864,7 @@
         <v>1950</v>
       </c>
       <c r="G105" s="9">
-        <f>(1+(F105-E105))-I105</f>
+        <f t="shared" si="4"/>
         <v>65</v>
       </c>
       <c r="H105" s="8" t="s">
@@ -6897,7 +6901,7 @@
         <v>1917</v>
       </c>
       <c r="G106" s="9">
-        <f>(1+(F106-E106))-I106</f>
+        <f t="shared" si="4"/>
         <v>68</v>
       </c>
       <c r="H106" s="8" t="s">
@@ -6934,7 +6938,7 @@
         <v>1925</v>
       </c>
       <c r="G107" s="9">
-        <f>(1+(F107-E107))-I107</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H107" s="8" t="s">
@@ -6971,7 +6975,7 @@
         <v>1902</v>
       </c>
       <c r="G108" s="9">
-        <f>(1+(F108-E108))-I108</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H108" s="8" t="s">
@@ -7008,7 +7012,7 @@
         <v>1929</v>
       </c>
       <c r="G109" s="9">
-        <f>(1+(F109-E109))-I109</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="H109" s="8" t="s">
@@ -7045,7 +7049,7 @@
         <v>1902</v>
       </c>
       <c r="G110" s="9">
-        <f>(1+(F110-E110))-I110</f>
+        <f t="shared" si="4"/>
         <v>65</v>
       </c>
       <c r="H110" s="8" t="s">
@@ -7082,7 +7086,7 @@
         <v>1902</v>
       </c>
       <c r="G111" s="9">
-        <f>(1+(F111-E111))-I111</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H111" s="8" t="s">
@@ -7119,7 +7123,7 @@
         <v>1932</v>
       </c>
       <c r="G112" s="9">
-        <f>(1+(F112-E112))-I112</f>
+        <f t="shared" ref="G112:G143" si="5">(1+(F112-E112))-I112</f>
         <v>9</v>
       </c>
       <c r="H112" s="8" t="s">
@@ -7156,7 +7160,7 @@
         <v>1935</v>
       </c>
       <c r="G113" s="9">
-        <f>(1+(F113-E113))-I113</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="H113" s="8" t="s">
@@ -7193,7 +7197,7 @@
         <v>1956</v>
       </c>
       <c r="G114" s="9">
-        <f>(1+(F114-E114))-I114</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H114" s="8" t="s">
@@ -7230,7 +7234,7 @@
         <v>1956</v>
       </c>
       <c r="G115" s="9">
-        <f>(1+(F115-E115))-I115</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="H115" s="8" t="s">
@@ -7267,7 +7271,7 @@
         <v>1931</v>
       </c>
       <c r="G116" s="9">
-        <f>(1+(F116-E116))-I116</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="H116" s="8" t="s">
@@ -7304,7 +7308,7 @@
         <v>1954</v>
       </c>
       <c r="G117" s="9">
-        <f>(1+(F117-E117))-I117</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H117" s="8" t="s">
@@ -7341,7 +7345,7 @@
         <v>1932</v>
       </c>
       <c r="G118" s="9">
-        <f>(1+(F118-E118))-I118</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="H118" s="8" t="s">
@@ -7378,7 +7382,7 @@
         <v>1966</v>
       </c>
       <c r="G119" s="9">
-        <f>(1+(F119-E119))-I119</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="H119" s="8" t="s">
@@ -7415,7 +7419,7 @@
         <v>1818</v>
       </c>
       <c r="G120" s="9">
-        <f>(1+(F120-E120))-I120</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="H120" s="8" t="s">
@@ -7452,7 +7456,7 @@
         <v>1840</v>
       </c>
       <c r="G121" s="9">
-        <f>(1+(F121-E121))-I121</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H121" s="8">
@@ -7489,7 +7493,7 @@
         <v>1932</v>
       </c>
       <c r="G122" s="9">
-        <f>(1+(F122-E122))-I122</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H122" s="8" t="s">
@@ -7526,7 +7530,7 @@
         <v>1818</v>
       </c>
       <c r="G123" s="9">
-        <f>(1+(F123-E123))-I123</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H123" s="8" t="s">
@@ -7563,7 +7567,7 @@
         <v>1948</v>
       </c>
       <c r="G124" s="9">
-        <f>(1+(F124-E124))-I124</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H124" s="8" t="s">
@@ -7600,7 +7604,7 @@
         <v>1816</v>
       </c>
       <c r="G125" s="9">
-        <f>(1+(F125-E125))-I125</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H125" s="8" t="s">
@@ -7637,7 +7641,7 @@
         <v>1954</v>
       </c>
       <c r="G126" s="9">
-        <f>(1+(F126-E126))-I126</f>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="H126" s="8" t="s">
@@ -7674,7 +7678,7 @@
         <v>1840</v>
       </c>
       <c r="G127" s="9">
-        <f>(1+(F127-E127))-I127</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="H127" s="8" t="s">
@@ -7711,7 +7715,7 @@
         <v>1840</v>
       </c>
       <c r="G128" s="9">
-        <f>(1+(F128-E128))-I128</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="H128" s="8" t="s">
@@ -7748,7 +7752,7 @@
         <v>1960</v>
       </c>
       <c r="G129" s="9">
-        <f>(1+(F129-E129))-I129</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H129" s="8" t="s">
@@ -7785,7 +7789,7 @@
         <v>1967</v>
       </c>
       <c r="G130" s="9">
-        <f>(1+(F130-E130))-I130</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H130" s="8" t="s">
@@ -7822,7 +7826,7 @@
         <v>1904</v>
       </c>
       <c r="G131" s="9">
-        <f>(1+(F131-E131))-I131</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H131" s="8">
@@ -7859,7 +7863,7 @@
         <v>1902</v>
       </c>
       <c r="G132" s="9">
-        <f>(1+(F132-E132))-I132</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H132" s="8" t="s">
@@ -7896,7 +7900,7 @@
         <v>1840</v>
       </c>
       <c r="G133" s="9">
-        <f>(1+(F133-E133))-I133</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="H133" s="8" t="s">
@@ -7933,7 +7937,7 @@
         <v>1903</v>
       </c>
       <c r="G134" s="9">
-        <f>(1+(F134-E134))-I134</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H134" s="8" t="s">
@@ -7970,7 +7974,7 @@
         <v>1905</v>
       </c>
       <c r="G135" s="9">
-        <f>(1+(F135-E135))-I135</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="H135" s="8" t="s">
@@ -8007,7 +8011,7 @@
         <v>1902</v>
       </c>
       <c r="G136" s="9">
-        <f>(1+(F136-E136))-I136</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H136" s="8" t="s">
@@ -8044,7 +8048,7 @@
         <v>1903</v>
       </c>
       <c r="G137" s="9">
-        <f>(1+(F137-E137))-I137</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H137" s="8" t="s">
@@ -8081,7 +8085,7 @@
         <v>1951</v>
       </c>
       <c r="G138" s="9">
-        <f>(1+(F138-E138))-I138</f>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="H138" s="8" t="s">
@@ -8118,7 +8122,7 @@
         <v>1858</v>
       </c>
       <c r="G139" s="9">
-        <f>(1+(F139-E139))-I139</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="H139" s="8" t="s">
@@ -8155,7 +8159,7 @@
         <v>1819</v>
       </c>
       <c r="G140" s="9">
-        <f>(1+(F140-E140))-I140</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H140" s="8" t="s">
@@ -8192,7 +8196,7 @@
         <v>1939</v>
       </c>
       <c r="G141" s="9">
-        <f>(1+(F141-E141))-I141</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H141" s="8" t="s">
@@ -8229,7 +8233,7 @@
         <v>1927</v>
       </c>
       <c r="G142" s="9">
-        <f>(1+(F142-E142))-I142</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H142" s="8" t="s">
@@ -8266,7 +8270,7 @@
         <v>1939</v>
       </c>
       <c r="G143" s="9">
-        <f>(1+(F143-E143))-I143</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="H143" s="8" t="s">
@@ -8303,7 +8307,7 @@
         <v>1967</v>
       </c>
       <c r="G144" s="9">
-        <f>(1+(F144-E144))-I144</f>
+        <f t="shared" ref="G144:G175" si="6">(1+(F144-E144))-I144</f>
         <v>1</v>
       </c>
       <c r="H144" s="8" t="s">
@@ -8340,7 +8344,7 @@
         <v>1967</v>
       </c>
       <c r="G145" s="9">
-        <f>(1+(F145-E145))-I145</f>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="H145" s="8" t="s">
@@ -8377,7 +8381,7 @@
         <v>1893</v>
       </c>
       <c r="G146" s="9">
-        <f>(1+(F146-E146))-I146</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="H146" s="8" t="s">
@@ -8414,7 +8418,7 @@
         <v>1956</v>
       </c>
       <c r="G147" s="9">
-        <f>(1+(F147-E147))-I147</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="H147" s="8" t="s">
@@ -8451,7 +8455,7 @@
         <v>1967</v>
       </c>
       <c r="G148" s="9">
-        <f>(1+(F148-E148))-I148</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H148" s="8" t="s">
@@ -8488,7 +8492,7 @@
         <v>1967</v>
       </c>
       <c r="G149" s="9">
-        <f>(1+(F149-E149))-I149</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="H149" s="8" t="s">
@@ -8525,7 +8529,7 @@
         <v>1891</v>
       </c>
       <c r="G150" s="9">
-        <f>(1+(F150-E150))-I150</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H150" s="8" t="s">
@@ -8562,7 +8566,7 @@
         <v>1963</v>
       </c>
       <c r="G151" s="9">
-        <f>(1+(F151-E151))-I151</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H151" s="8" t="s">
@@ -8599,7 +8603,7 @@
         <v>1889</v>
       </c>
       <c r="G152" s="9">
-        <f>(1+(F152-E152))-I152</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="H152" s="8" t="s">
@@ -8636,7 +8640,7 @@
         <v>1964</v>
       </c>
       <c r="G153" s="9">
-        <f>(1+(F153-E153))-I153</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H153" s="8" t="s">
@@ -8673,7 +8677,7 @@
         <v>1867</v>
       </c>
       <c r="G154" s="9">
-        <f>(1+(F154-E154))-I154</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H154" s="8" t="s">
@@ -8710,7 +8714,7 @@
         <v>1908</v>
       </c>
       <c r="G155" s="9">
-        <f>(1+(F155-E155))-I155</f>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="H155" s="8" t="s">
@@ -8747,7 +8751,7 @@
         <v>1858</v>
       </c>
       <c r="G156" s="9">
-        <f>(1+(F156-E156))-I156</f>
+        <f t="shared" si="6"/>
         <v>28</v>
       </c>
       <c r="H156" s="8" t="s">
@@ -8784,7 +8788,7 @@
         <v>1918</v>
       </c>
       <c r="G157" s="9">
-        <f>(1+(F157-E157))-I157</f>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="H157" s="8" t="s">
@@ -8821,7 +8825,7 @@
         <v>1918</v>
       </c>
       <c r="G158" s="9">
-        <f>(1+(F158-E158))-I158</f>
+        <f t="shared" si="6"/>
         <v>44</v>
       </c>
       <c r="H158" s="8" t="s">
@@ -8858,7 +8862,7 @@
         <v>1860</v>
       </c>
       <c r="G159" s="9">
-        <f>(1+(F159-E159))-I159</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H159" s="8" t="s">
@@ -8895,7 +8899,7 @@
         <v>1824</v>
       </c>
       <c r="G160" s="9">
-        <f>(1+(F160-E160))-I160</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H160" s="8" t="s">
@@ -8932,7 +8936,7 @@
         <v>1878</v>
       </c>
       <c r="G161" s="9">
-        <f>(1+(F161-E161))-I161</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H161" s="8" t="s">
@@ -8969,7 +8973,7 @@
         <v>1878</v>
       </c>
       <c r="G162" s="9">
-        <f>(1+(F162-E162))-I162</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H162" s="8" t="s">
@@ -9006,7 +9010,7 @@
         <v>1924</v>
       </c>
       <c r="G163" s="9">
-        <f>(1+(F163-E163))-I163</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="H163" s="8" t="s">
@@ -9043,7 +9047,7 @@
         <v>1964</v>
       </c>
       <c r="G164" s="9">
-        <f>(1+(F164-E164))-I164</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="H164" s="8" t="s">
@@ -9080,7 +9084,7 @@
         <v>1882</v>
       </c>
       <c r="G165" s="9">
-        <f>(1+(F165-E165))-I165</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H165" s="8" t="s">
@@ -9117,7 +9121,7 @@
         <v>1882</v>
       </c>
       <c r="G166" s="9">
-        <f>(1+(F166-E166))-I166</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H166" s="8" t="s">
@@ -9154,7 +9158,7 @@
         <v>1882</v>
       </c>
       <c r="G167" s="9">
-        <f>(1+(F167-E167))-I167</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H167" s="8" t="s">
@@ -9191,7 +9195,7 @@
         <v>1882</v>
       </c>
       <c r="G168" s="9">
-        <f>(1+(F168-E168))-I168</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H168" s="8" t="s">
@@ -9228,7 +9232,7 @@
         <v>1946</v>
       </c>
       <c r="G169" s="9">
-        <f>(1+(F169-E169))-I169</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H169" s="8" t="s">
@@ -9265,7 +9269,7 @@
         <v>1813</v>
       </c>
       <c r="G170" s="9">
-        <f>(1+(F170-E170))-I170</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H170" s="8" t="s">
@@ -9302,7 +9306,7 @@
         <v>1924</v>
       </c>
       <c r="G171" s="9">
-        <f>(1+(F171-E171))-I171</f>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="H171" s="8" t="s">
@@ -9339,7 +9343,7 @@
         <v>1892</v>
       </c>
       <c r="G172" s="9">
-        <f>(1+(F172-E172))-I172</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H172" s="8" t="s">
@@ -9376,7 +9380,7 @@
         <v>1892</v>
       </c>
       <c r="G173" s="9">
-        <f>(1+(F173-E173))-I173</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="H173" s="8" t="s">
@@ -9413,7 +9417,7 @@
         <v>1950</v>
       </c>
       <c r="G174" s="9">
-        <f>(1+(F174-E174))-I174</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H174" s="8" t="s">
@@ -9450,7 +9454,7 @@
         <v>1892</v>
       </c>
       <c r="G175" s="9">
-        <f>(1+(F175-E175))-I175</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H175" s="8" t="s">
@@ -9487,7 +9491,7 @@
         <v>1892</v>
       </c>
       <c r="G176" s="9">
-        <f>(1+(F176-E176))-I176</f>
+        <f t="shared" ref="G176:G207" si="7">(1+(F176-E176))-I176</f>
         <v>2</v>
       </c>
       <c r="H176" s="8" t="s">
@@ -9524,7 +9528,7 @@
         <v>1874</v>
       </c>
       <c r="G177" s="9">
-        <f>(1+(F177-E177))-I177</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H177" s="8" t="s">
@@ -9561,7 +9565,7 @@
         <v>1892</v>
       </c>
       <c r="G178" s="9">
-        <f>(1+(F178-E178))-I178</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="H178" s="8" t="s">
@@ -9598,7 +9602,7 @@
         <v>1874</v>
       </c>
       <c r="G179" s="9">
-        <f>(1+(F179-E179))-I179</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="H179" s="8" t="s">
@@ -9635,7 +9639,7 @@
         <v>1825</v>
       </c>
       <c r="G180" s="9">
-        <f>(1+(F180-E180))-I180</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="H180" s="8" t="s">
@@ -9672,7 +9676,7 @@
         <v>1892</v>
       </c>
       <c r="G181" s="9">
-        <f>(1+(F181-E181))-I181</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="H181" s="8" t="s">
@@ -9709,7 +9713,7 @@
         <v>1892</v>
       </c>
       <c r="G182" s="9">
-        <f>(1+(F182-E182))-I182</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="H182" s="8" t="s">
@@ -9746,7 +9750,7 @@
         <v>1892</v>
       </c>
       <c r="G183" s="9">
-        <f>(1+(F183-E183))-I183</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="H183" s="8" t="s">
@@ -9783,7 +9787,7 @@
         <v>1961</v>
       </c>
       <c r="G184" s="9">
-        <f>(1+(F184-E184))-I184</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="H184" s="8" t="s">
@@ -9820,7 +9824,7 @@
         <v>1924</v>
       </c>
       <c r="G185" s="9">
-        <f>(1+(F185-E185))-I185</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="H185" s="8" t="s">
@@ -9857,7 +9861,7 @@
         <v>1917</v>
       </c>
       <c r="G186" s="9">
-        <f>(1+(F186-E186))-I186</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="H186" s="8" t="s">
@@ -9894,7 +9898,7 @@
         <v>1931</v>
       </c>
       <c r="G187" s="9">
-        <f>(1+(F187-E187))-I187</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="H187" s="8" t="s">
@@ -9931,7 +9935,7 @@
         <v>1967</v>
       </c>
       <c r="G188" s="9">
-        <f>(1+(F188-E188))-I188</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="H188" s="8" t="s">
@@ -9968,7 +9972,7 @@
         <v>1964</v>
       </c>
       <c r="G189" s="9">
-        <f>(1+(F189-E189))-I189</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H189" s="8" t="s">
@@ -10005,7 +10009,7 @@
         <v>1919</v>
       </c>
       <c r="G190" s="9">
-        <f>(1+(F190-E190))-I190</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H190" s="8" t="s">
@@ -10042,7 +10046,7 @@
         <v>1904</v>
       </c>
       <c r="G191" s="9">
-        <f>(1+(F191-E191))-I191</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="H191" s="8" t="s">
@@ -10079,7 +10083,7 @@
         <v>1979</v>
       </c>
       <c r="G192" s="9">
-        <f>(1+(F192-E192))-I192</f>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="H192" s="8" t="s">
@@ -10116,7 +10120,7 @@
         <v>1917</v>
       </c>
       <c r="G193" s="9">
-        <f>(1+(F193-E193))-I193</f>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="H193" s="8" t="s">
@@ -10153,7 +10157,7 @@
         <v>1963</v>
       </c>
       <c r="G194" s="9">
-        <f>(1+(F194-E194))-I194</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="H194" s="8" t="s">
@@ -10190,7 +10194,7 @@
         <v>1960</v>
       </c>
       <c r="G195" s="9">
-        <f>(1+(F195-E195))-I195</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="H195" s="8" t="s">
@@ -10227,7 +10231,7 @@
         <v>1937</v>
       </c>
       <c r="G196" s="9">
-        <f>(1+(F196-E196))-I196</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H196" s="8" t="s">
@@ -10264,7 +10268,7 @@
         <v>1963</v>
       </c>
       <c r="G197" s="9">
-        <f>(1+(F197-E197))-I197</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H197" s="8" t="s">
@@ -10301,7 +10305,7 @@
         <v>1951</v>
       </c>
       <c r="G198" s="9">
-        <f>(1+(F198-E198))-I198</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="H198" s="8" t="s">
@@ -10338,7 +10342,7 @@
         <v>1932</v>
       </c>
       <c r="G199" s="9">
-        <f>(1+(F199-E199))-I199</f>
+        <f t="shared" si="7"/>
         <v>45</v>
       </c>
       <c r="H199" s="8" t="s">
@@ -10375,7 +10379,7 @@
         <v>1979</v>
       </c>
       <c r="G200" s="9">
-        <f>(1+(F200-E200))-I200</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="H200" s="8" t="s">
@@ -10412,7 +10416,7 @@
         <v>1961</v>
       </c>
       <c r="G201" s="9">
-        <f>(1+(F201-E201))-I201</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H201" s="8" t="s">
@@ -10449,7 +10453,7 @@
         <v>1975</v>
       </c>
       <c r="G202" s="9">
-        <f>(1+(F202-E202))-I202</f>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="H202" s="8" t="s">
@@ -10486,7 +10490,7 @@
         <v>1983</v>
       </c>
       <c r="G203" s="9">
-        <f>(1+(F203-E203))-I203</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="H203" s="8" t="s">
@@ -10523,7 +10527,7 @@
         <v>1966</v>
       </c>
       <c r="G204" s="9">
-        <f>(1+(F204-E204))-I204</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H204" s="8" t="s">
@@ -10560,7 +10564,7 @@
         <v>1980</v>
       </c>
       <c r="G205" s="9">
-        <f>(1+(F205-E205))-I205</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="H205" s="8" t="s">
@@ -10597,7 +10601,7 @@
         <v>1975</v>
       </c>
       <c r="G206" s="9">
-        <f>(1+(F206-E206))-I206</f>
+        <f t="shared" si="7"/>
         <v>49</v>
       </c>
       <c r="H206" s="8" t="s">
@@ -10634,7 +10638,7 @@
         <v>1836</v>
       </c>
       <c r="G207" s="9">
-        <f>(1+(F207-E207))-I207</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="H207" s="8" t="s">
@@ -10671,7 +10675,7 @@
         <v>1954</v>
       </c>
       <c r="G208" s="9">
-        <f>(1+(F208-E208))-I208</f>
+        <f t="shared" ref="G208:G239" si="8">(1+(F208-E208))-I208</f>
         <v>1</v>
       </c>
       <c r="H208" s="8" t="s">
@@ -10708,7 +10712,7 @@
         <v>1898</v>
       </c>
       <c r="G209" s="9">
-        <f>(1+(F209-E209))-I209</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="H209" s="8" t="s">
@@ -10745,7 +10749,7 @@
         <v>1990</v>
       </c>
       <c r="G210" s="9">
-        <f>(1+(F210-E210))-I210</f>
+        <f t="shared" si="8"/>
         <v>38</v>
       </c>
       <c r="H210" s="8" t="s">
@@ -10782,7 +10786,7 @@
         <v>1890</v>
       </c>
       <c r="G211" s="9">
-        <f>(1+(F211-E211))-I211</f>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="H211" s="8" t="s">
@@ -10819,7 +10823,7 @@
         <v>1957</v>
       </c>
       <c r="G212" s="9">
-        <f>(1+(F212-E212))-I212</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H212" s="8" t="s">
@@ -10856,7 +10860,7 @@
         <v>1891</v>
       </c>
       <c r="G213" s="9">
-        <f>(1+(F213-E213))-I213</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="H213" s="8" t="s">
@@ -10893,7 +10897,7 @@
         <v>1977</v>
       </c>
       <c r="G214" s="9">
-        <f>(1+(F214-E214))-I214</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H214" s="8" t="s">
@@ -10930,7 +10934,7 @@
         <v>1978</v>
       </c>
       <c r="G215" s="9">
-        <f>(1+(F215-E215))-I215</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="H215" s="8" t="s">
@@ -11003,7 +11007,7 @@
         <v>1956</v>
       </c>
       <c r="G217" s="9">
-        <f>(1+(F217-E217))-I217</f>
+        <f t="shared" ref="G217:G280" si="9">(1+(F217-E217))-I217</f>
         <v>3</v>
       </c>
       <c r="H217" s="8" t="s">
@@ -11040,7 +11044,7 @@
         <v>1964</v>
       </c>
       <c r="G218" s="9">
-        <f>(1+(F218-E218))-I218</f>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="H218" s="8" t="s">
@@ -11077,7 +11081,7 @@
         <v>1963</v>
       </c>
       <c r="G219" s="9">
-        <f>(1+(F219-E219))-I219</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="H219" s="8" t="s">
@@ -11114,7 +11118,7 @@
         <v>1963</v>
       </c>
       <c r="G220" s="9">
-        <f>(1+(F220-E220))-I220</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H220" s="8" t="s">
@@ -11151,7 +11155,7 @@
         <v>1912</v>
       </c>
       <c r="G221" s="9">
-        <f>(1+(F221-E221))-I221</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="H221" s="8" t="s">
@@ -11188,7 +11192,7 @@
         <v>1965</v>
       </c>
       <c r="G222" s="9">
-        <f>(1+(F222-E222))-I222</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="H222" s="8" t="s">
@@ -11225,7 +11229,7 @@
         <v>1985</v>
       </c>
       <c r="G223" s="9">
-        <f>(1+(F223-E223))-I223</f>
+        <f t="shared" si="9"/>
         <v>60</v>
       </c>
       <c r="H223" s="8" t="s">
@@ -11262,7 +11266,7 @@
         <v>1960</v>
       </c>
       <c r="G224" s="9">
-        <f>(1+(F224-E224))-I224</f>
+        <f t="shared" si="9"/>
         <v>33</v>
       </c>
       <c r="H224" s="8" t="s">
@@ -11299,7 +11303,7 @@
         <v>1960</v>
       </c>
       <c r="G225" s="9">
-        <f>(1+(F225-E225))-I225</f>
+        <f t="shared" si="9"/>
         <v>33</v>
       </c>
       <c r="H225" s="8" t="s">
@@ -11336,7 +11340,7 @@
         <v>1811</v>
       </c>
       <c r="G226" s="9">
-        <f>(1+(F226-E226))-I226</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H226" s="8" t="s">
@@ -11373,7 +11377,7 @@
         <v>1812</v>
       </c>
       <c r="G227" s="9">
-        <f>(1+(F227-E227))-I227</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H227" s="8" t="s">
@@ -11410,7 +11414,7 @@
         <v>1964</v>
       </c>
       <c r="G228" s="9">
-        <f>(1+(F228-E228))-I228</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="H228" s="8" t="s">
@@ -11447,7 +11451,7 @@
         <v>1855</v>
       </c>
       <c r="G229" s="9">
-        <f>(1+(F229-E229))-I229</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="H229" s="8" t="s">
@@ -11484,7 +11488,7 @@
         <v>1999</v>
       </c>
       <c r="G230" s="9">
-        <f>(1+(F230-E230))-I230</f>
+        <f t="shared" si="9"/>
         <v>39</v>
       </c>
       <c r="H230" s="8" t="s">
@@ -11521,7 +11525,7 @@
         <v>1869</v>
       </c>
       <c r="G231" s="9">
-        <f>(1+(F231-E231))-I231</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="H231" s="8" t="s">
@@ -11558,7 +11562,7 @@
         <v>1959</v>
       </c>
       <c r="G232" s="9">
-        <f>(1+(F232-E232))-I232</f>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="H232" s="8" t="s">
@@ -11595,7 +11599,7 @@
         <v>1943</v>
       </c>
       <c r="G233" s="9">
-        <f>(1+(F233-E233))-I233</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="H233" s="8" t="s">
@@ -11632,7 +11636,7 @@
         <v>1938</v>
       </c>
       <c r="G234" s="9">
-        <f>(1+(F234-E234))-I234</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="H234" s="8" t="s">
@@ -11669,7 +11673,7 @@
         <v>1950</v>
       </c>
       <c r="G235" s="9">
-        <f>(1+(F235-E235))-I235</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="H235" s="8" t="s">
@@ -11706,7 +11710,7 @@
         <v>1943</v>
       </c>
       <c r="G236" s="9">
-        <f>(1+(F236-E236))-I236</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="H236" s="8" t="s">
@@ -11743,7 +11747,7 @@
         <v>1948</v>
       </c>
       <c r="G237" s="9">
-        <f>(1+(F237-E237))-I237</f>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="H237" s="8" t="s">
@@ -11780,7 +11784,7 @@
         <v>1897</v>
       </c>
       <c r="G238" s="9">
-        <f>(1+(F238-E238))-I238</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="H238" s="8" t="s">
@@ -11817,7 +11821,7 @@
         <v>1937</v>
       </c>
       <c r="G239" s="9">
-        <f>(1+(F239-E239))-I239</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="H239" s="8" t="s">
@@ -11854,7 +11858,7 @@
         <v>1830</v>
       </c>
       <c r="G240" s="9">
-        <f>(1+(F240-E240))-I240</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H240" s="8" t="s">
@@ -11891,7 +11895,7 @@
         <v>1937</v>
       </c>
       <c r="G241" s="9">
-        <f>(1+(F241-E241))-I241</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="H241" s="8" t="s">
@@ -11928,7 +11932,7 @@
         <v>1937</v>
       </c>
       <c r="G242" s="9">
-        <f>(1+(F242-E242))-I242</f>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="H242" s="8" t="s">
@@ -11965,7 +11969,7 @@
         <v>1937</v>
       </c>
       <c r="G243" s="9">
-        <f>(1+(F243-E243))-I243</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="H243" s="8" t="s">
@@ -12002,7 +12006,7 @@
         <v>1937</v>
       </c>
       <c r="G244" s="9">
-        <f>(1+(F244-E244))-I244</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="H244" s="8" t="s">
@@ -12039,7 +12043,7 @@
         <v>1851</v>
       </c>
       <c r="G245" s="9">
-        <f>(1+(F245-E245))-I245</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H245" s="8" t="s">
@@ -12076,7 +12080,7 @@
         <v>1963</v>
       </c>
       <c r="G246" s="9">
-        <f>(1+(F246-E246))-I246</f>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
       <c r="H246" s="8" t="s">
@@ -12113,7 +12117,7 @@
         <v>1956</v>
       </c>
       <c r="G247" s="9">
-        <f>(1+(F247-E247))-I247</f>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="H247" s="8" t="s">
@@ -12150,7 +12154,7 @@
         <v>1936</v>
       </c>
       <c r="G248" s="9">
-        <f>(1+(F248-E248))-I248</f>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="H248" s="8" t="s">
@@ -12187,7 +12191,7 @@
         <v>1932</v>
       </c>
       <c r="G249" s="9">
-        <f>(1+(F249-E249))-I249</f>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="H249" s="8">
@@ -12224,7 +12228,7 @@
         <v>1842</v>
       </c>
       <c r="G250" s="9">
-        <f>(1+(F250-E250))-I250</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H250" s="8" t="s">
@@ -12261,7 +12265,7 @@
         <v>1842</v>
       </c>
       <c r="G251" s="9">
-        <f>(1+(F251-E251))-I251</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H251" s="8" t="s">
@@ -12298,7 +12302,7 @@
         <v>1842</v>
       </c>
       <c r="G252" s="9">
-        <f>(1+(F252-E252))-I252</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H252" s="8" t="s">
@@ -12335,7 +12339,7 @@
         <v>1842</v>
       </c>
       <c r="G253" s="9">
-        <f>(1+(F253-E253))-I253</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H253" s="8" t="s">
@@ -12372,7 +12376,7 @@
         <v>1842</v>
       </c>
       <c r="G254" s="9">
-        <f>(1+(F254-E254))-I254</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H254" s="8" t="s">
@@ -12409,7 +12413,7 @@
         <v>1842</v>
       </c>
       <c r="G255" s="9">
-        <f>(1+(F255-E255))-I255</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H255" s="8" t="s">
@@ -12446,7 +12450,7 @@
         <v>1842</v>
       </c>
       <c r="G256" s="9">
-        <f>(1+(F256-E256))-I256</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H256" s="8" t="s">
@@ -12483,7 +12487,7 @@
         <v>1842</v>
       </c>
       <c r="G257" s="9">
-        <f>(1+(F257-E257))-I257</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H257" s="8" t="s">
@@ -12520,7 +12524,7 @@
         <v>1842</v>
       </c>
       <c r="G258" s="9">
-        <f>(1+(F258-E258))-I258</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H258" s="8" t="s">
@@ -12557,7 +12561,7 @@
         <v>1842</v>
       </c>
       <c r="G259" s="9">
-        <f>(1+(F259-E259))-I259</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H259" s="8" t="s">
@@ -12595,7 +12599,7 @@
         <v>1842</v>
       </c>
       <c r="G260" s="9">
-        <f>(1+(F260-E260))-I260</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H260" s="8" t="s">
@@ -12633,7 +12637,7 @@
         <v>1842</v>
       </c>
       <c r="G261" s="9">
-        <f>(1+(F261-E261))-I261</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H261" s="8" t="s">
@@ -12671,7 +12675,7 @@
         <v>1842</v>
       </c>
       <c r="G262" s="9">
-        <f>(1+(F262-E262))-I262</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H262" s="8" t="s">
@@ -12709,7 +12713,7 @@
         <v>1842</v>
       </c>
       <c r="G263" s="9">
-        <f>(1+(F263-E263))-I263</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H263" s="8" t="s">
@@ -12747,7 +12751,7 @@
         <v>1842</v>
       </c>
       <c r="G264" s="9">
-        <f>(1+(F264-E264))-I264</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H264" s="8" t="s">
@@ -12785,7 +12789,7 @@
         <v>1842</v>
       </c>
       <c r="G265" s="9">
-        <f>(1+(F265-E265))-I265</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H265" s="8" t="s">
@@ -12823,7 +12827,7 @@
         <v>1842</v>
       </c>
       <c r="G266" s="9">
-        <f>(1+(F266-E266))-I266</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H266" s="8" t="s">
@@ -12861,7 +12865,7 @@
         <v>1842</v>
       </c>
       <c r="G267" s="9">
-        <f>(1+(F267-E267))-I267</f>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="H267" s="8" t="s">
@@ -12898,7 +12902,7 @@
         <v>1969</v>
       </c>
       <c r="G268" s="9">
-        <f>(1+(F268-E268))-I268</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="H268" s="8" t="s">
@@ -12935,7 +12939,7 @@
         <v>1874</v>
       </c>
       <c r="G269" s="9">
-        <f>(1+(F269-E269))-I269</f>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="H269" s="8" t="s">
@@ -12972,7 +12976,7 @@
         <v>1858</v>
       </c>
       <c r="G270" s="9">
-        <f>(1+(F270-E270))-I270</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H270" s="8" t="s">
@@ -13009,7 +13013,7 @@
         <v>1965</v>
       </c>
       <c r="G271" s="9">
-        <f>(1+(F271-E271))-I271</f>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="H271" s="8" t="s">
@@ -13046,7 +13050,7 @@
         <v>1952</v>
       </c>
       <c r="G272" s="9">
-        <f>(1+(F272-E272))-I272</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="H272" s="8" t="s">
@@ -13083,7 +13087,7 @@
         <v>1953</v>
       </c>
       <c r="G273" s="9">
-        <f>(1+(F273-E273))-I273</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H273" s="8" t="s">
@@ -13120,7 +13124,7 @@
         <v>1965</v>
       </c>
       <c r="G274" s="9">
-        <f>(1+(F274-E274))-I274</f>
+        <f t="shared" si="9"/>
         <v>8.1420260095824801</v>
       </c>
       <c r="H274" s="9" t="s">
@@ -13158,7 +13162,7 @@
         <v>1967</v>
       </c>
       <c r="G275" s="9">
-        <f>(1+(F275-E275))-I275</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="H275" s="8" t="s">
@@ -13195,7 +13199,7 @@
         <v>1948</v>
       </c>
       <c r="G276" s="9">
-        <f>(1+(F276-E276))-I276</f>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="H276" s="8" t="s">
@@ -13232,7 +13236,7 @@
         <v>1964</v>
       </c>
       <c r="G277" s="9">
-        <f>(1+(F277-E277))-I277</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="H277" s="8" t="s">
@@ -13269,7 +13273,7 @@
         <v>1960</v>
       </c>
       <c r="G278" s="9">
-        <f>(1+(F278-E278))-I278</f>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="H278" s="8" t="s">
@@ -13306,7 +13310,7 @@
         <v>1937</v>
       </c>
       <c r="G279" s="9">
-        <f>(1+(F279-E279))-I279</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="H279" s="8" t="s">
@@ -13343,7 +13347,7 @@
         <v>1962</v>
       </c>
       <c r="G280" s="9">
-        <f>(1+(F280-E280))-I280</f>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="H280" s="8" t="s">
@@ -13380,7 +13384,7 @@
         <v>1907</v>
       </c>
       <c r="G281" s="9">
-        <f>(1+(F281-E281))-I281</f>
+        <f t="shared" ref="G281:G344" si="10">(1+(F281-E281))-I281</f>
         <v>7</v>
       </c>
       <c r="H281" s="8" t="s">
@@ -13417,7 +13421,7 @@
         <v>1908</v>
       </c>
       <c r="G282" s="9">
-        <f>(1+(F282-E282))-I282</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="H282" s="8" t="s">
@@ -13454,7 +13458,7 @@
         <v>1937</v>
       </c>
       <c r="G283" s="9">
-        <f>(1+(F283-E283))-I283</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="H283" s="8" t="s">
@@ -13491,7 +13495,7 @@
         <v>1952</v>
       </c>
       <c r="G284" s="9">
-        <f>(1+(F284-E284))-I284</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="H284" s="8" t="s">
@@ -13528,7 +13532,7 @@
         <v>1949</v>
       </c>
       <c r="G285" s="9">
-        <f>(1+(F285-E285))-I285</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="H285" s="8" t="s">
@@ -13565,7 +13569,7 @@
         <v>1952</v>
       </c>
       <c r="G286" s="9">
-        <f>(1+(F286-E286))-I286</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="H286" s="8" t="s">
@@ -13602,7 +13606,7 @@
         <v>1962</v>
       </c>
       <c r="G287" s="9">
-        <f>(1+(F287-E287))-I287</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="H287" s="8" t="s">
@@ -13639,7 +13643,7 @@
         <v>1899</v>
       </c>
       <c r="G288" s="9">
-        <f>(1+(F288-E288))-I288</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H288" s="8" t="s">
@@ -13676,7 +13680,7 @@
         <v>1900</v>
       </c>
       <c r="G289" s="9">
-        <f>(1+(F289-E289))-I289</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H289" s="8" t="s">
@@ -13713,7 +13717,7 @@
         <v>1962</v>
       </c>
       <c r="G290" s="9">
-        <f>(1+(F290-E290))-I290</f>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="H290" s="8" t="s">
@@ -13750,7 +13754,7 @@
         <v>1909</v>
       </c>
       <c r="G291" s="9">
-        <f>(1+(F291-E291))-I291</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="H291" s="8" t="s">
@@ -13787,7 +13791,7 @@
         <v>1962</v>
       </c>
       <c r="G292" s="9">
-        <f>(1+(F292-E292))-I292</f>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="H292" s="8" t="s">
@@ -13824,7 +13828,7 @@
         <v>1901</v>
       </c>
       <c r="G293" s="9">
-        <f>(1+(F293-E293))-I293</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H293" s="8" t="s">
@@ -13861,7 +13865,7 @@
         <v>1903</v>
       </c>
       <c r="G294" s="9">
-        <f>(1+(F294-E294))-I294</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H294" s="8" t="s">
@@ -13898,7 +13902,7 @@
         <v>1955</v>
       </c>
       <c r="G295" s="9">
-        <f>(1+(F295-E295))-I295</f>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="H295" s="16">
@@ -13935,7 +13939,7 @@
         <v>1962</v>
       </c>
       <c r="G296" s="9">
-        <f>(1+(F296-E296))-I296</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="H296" s="8" t="s">
@@ -13972,7 +13976,7 @@
         <v>1907</v>
       </c>
       <c r="G297" s="9">
-        <f>(1+(F297-E297))-I297</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H297" s="8" t="s">
@@ -14009,7 +14013,7 @@
         <v>1949</v>
       </c>
       <c r="G298" s="9">
-        <f>(1+(F298-E298))-I298</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="H298" s="8" t="s">
@@ -14046,7 +14050,7 @@
         <v>1952</v>
       </c>
       <c r="G299" s="9">
-        <f>(1+(F299-E299))-I299</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="H299" s="8" t="s">
@@ -14083,7 +14087,7 @@
         <v>1926</v>
       </c>
       <c r="G300" s="9">
-        <f>(1+(F300-E300))-I300</f>
+        <f t="shared" si="10"/>
         <v>26</v>
       </c>
       <c r="H300" s="8" t="s">
@@ -14120,7 +14124,7 @@
         <v>1825</v>
       </c>
       <c r="G301" s="9">
-        <f>(1+(F301-E301))-I301</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="H301" s="8" t="s">
@@ -14157,7 +14161,7 @@
         <v>1939</v>
       </c>
       <c r="G302" s="9">
-        <f>(1+(F302-E302))-I302</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="H302" s="8" t="s">
@@ -14194,7 +14198,7 @@
         <v>1939</v>
       </c>
       <c r="G303" s="9">
-        <f>(1+(F303-E303))-I303</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="H303" s="8" t="s">
@@ -14231,7 +14235,7 @@
         <v>1942</v>
       </c>
       <c r="G304" s="9">
-        <f>(1+(F304-E304))-I304</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="H304" s="8" t="s">
@@ -14268,7 +14272,7 @@
         <v>1906</v>
       </c>
       <c r="G305" s="9">
-        <f>(1+(F305-E305))-I305</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="H305" s="8" t="s">
@@ -14305,7 +14309,7 @@
         <v>1965</v>
       </c>
       <c r="G306" s="9">
-        <f>(1+(F306-E306))-I306</f>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="H306" s="8" t="s">
@@ -14342,7 +14346,7 @@
         <v>1962</v>
       </c>
       <c r="G307" s="9">
-        <f>(1+(F307-E307))-I307</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H307" s="8" t="s">
@@ -14379,7 +14383,7 @@
         <v>1900</v>
       </c>
       <c r="G308" s="9">
-        <f>(1+(F308-E308))-I308</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H308" s="8" t="s">
@@ -14416,7 +14420,7 @@
         <v>1963</v>
       </c>
       <c r="G309" s="9">
-        <f>(1+(F309-E309))-I309</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="H309" s="8" t="s">
@@ -14453,7 +14457,7 @@
         <v>1861</v>
       </c>
       <c r="G310" s="9">
-        <f>(1+(F310-E310))-I310</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="H310" s="8" t="s">
@@ -14490,7 +14494,7 @@
         <v>1955</v>
       </c>
       <c r="G311" s="9">
-        <f>(1+(F311-E311))-I311</f>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="H311" s="8" t="s">
@@ -14527,7 +14531,7 @@
         <v>1939</v>
       </c>
       <c r="G312" s="9">
-        <f>(1+(F312-E312))-I312</f>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="H312" s="8" t="s">
@@ -14564,7 +14568,7 @@
         <v>1954</v>
       </c>
       <c r="G313" s="9">
-        <f>(1+(F313-E313))-I313</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="H313" s="8" t="s">
@@ -14601,7 +14605,7 @@
         <v>1953</v>
       </c>
       <c r="G314" s="9">
-        <f>(1+(F314-E314))-I314</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H314" s="8" t="s">
@@ -14638,7 +14642,7 @@
         <v>1954</v>
       </c>
       <c r="G315" s="9">
-        <f>(1+(F315-E315))-I315</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H315" s="8" t="s">
@@ -14675,7 +14679,7 @@
         <v>1954</v>
       </c>
       <c r="G316" s="9">
-        <f>(1+(F316-E316))-I316</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="H316" s="8" t="s">
@@ -14712,7 +14716,7 @@
         <v>1952</v>
       </c>
       <c r="G317" s="9">
-        <f>(1+(F317-E317))-I317</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H317" s="8" t="s">
@@ -14749,7 +14753,7 @@
         <v>1954</v>
       </c>
       <c r="G318" s="9">
-        <f>(1+(F318-E318))-I318</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="H318" s="8" t="s">
@@ -14786,7 +14790,7 @@
         <v>1920</v>
       </c>
       <c r="G319" s="9">
-        <f>(1+(F319-E319))-I319</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H319" s="8" t="s">
@@ -14823,7 +14827,7 @@
         <v>1956</v>
       </c>
       <c r="G320" s="9">
-        <f>(1+(F320-E320))-I320</f>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="H320" s="8" t="s">
@@ -14860,7 +14864,7 @@
         <v>1942</v>
       </c>
       <c r="G321" s="9">
-        <f>(1+(F321-E321))-I321</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H321" s="8" t="s">
@@ -14897,7 +14901,7 @@
         <v>1957</v>
       </c>
       <c r="G322" s="9">
-        <f>(1+(F322-E322))-I322</f>
+        <f t="shared" si="10"/>
         <v>26</v>
       </c>
       <c r="H322" s="8" t="s">
@@ -14934,7 +14938,7 @@
         <v>1811</v>
       </c>
       <c r="G323" s="9">
-        <f>(1+(F323-E323))-I323</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H323" s="8" t="s">
@@ -14971,7 +14975,7 @@
         <v>1808</v>
       </c>
       <c r="G324" s="9">
-        <f>(1+(F324-E324))-I324</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="H324" s="8" t="s">
@@ -15008,7 +15012,7 @@
         <v>1936</v>
       </c>
       <c r="G325" s="9">
-        <f>(1+(F325-E325))-I325</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H325" s="8" t="s">
@@ -15045,7 +15049,7 @@
         <v>1965</v>
       </c>
       <c r="G326" s="9">
-        <f>(1+(F326-E326))-I326</f>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="H326" s="8" t="s">
@@ -15082,7 +15086,7 @@
         <v>1907</v>
       </c>
       <c r="G327" s="9">
-        <f>(1+(F327-E327))-I327</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="H327" s="8" t="s">
@@ -15119,7 +15123,7 @@
         <v>1937</v>
       </c>
       <c r="G328" s="9">
-        <f>(1+(F328-E328))-I328</f>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="H328" s="8" t="s">
@@ -15156,7 +15160,7 @@
         <v>1938</v>
       </c>
       <c r="G329" s="9">
-        <f>(1+(F329-E329))-I329</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H329" s="8" t="s">
@@ -15193,7 +15197,7 @@
         <v>1844</v>
       </c>
       <c r="G330" s="9">
-        <f>(1+(F330-E330))-I330</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H330" s="8" t="s">
@@ -15230,7 +15234,7 @@
         <v>1844</v>
       </c>
       <c r="G331" s="9">
-        <f>(1+(F331-E331))-I331</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="H331" s="8" t="s">
@@ -15267,7 +15271,7 @@
         <v>1890</v>
       </c>
       <c r="G332" s="9">
-        <f>(1+(F332-E332))-I332</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="H332" s="8" t="s">
@@ -15304,7 +15308,7 @@
         <v>1923</v>
       </c>
       <c r="G333" s="9">
-        <f>(1+(F333-E333))-I333</f>
+        <f t="shared" si="10"/>
         <v>41</v>
       </c>
       <c r="H333" s="8" t="s">
@@ -15341,7 +15345,7 @@
         <v>1899</v>
       </c>
       <c r="G334" s="9">
-        <f>(1+(F334-E334))-I334</f>
+        <f t="shared" si="10"/>
         <v>17</v>
       </c>
       <c r="H334" s="8" t="s">
@@ -15378,7 +15382,7 @@
         <v>1981</v>
       </c>
       <c r="G335" s="9">
-        <f>(1+(F335-E335))-I335</f>
+        <f t="shared" si="10"/>
         <v>81</v>
       </c>
       <c r="H335" s="8" t="s">
@@ -15415,7 +15419,7 @@
         <v>1894</v>
       </c>
       <c r="G336" s="9">
-        <f>(1+(F336-E336))-I336</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H336" s="8" t="s">
@@ -15452,7 +15456,7 @@
         <v>1900</v>
       </c>
       <c r="G337" s="9">
-        <f>(1+(F337-E337))-I337</f>
+        <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="H337" s="8" t="s">
@@ -15489,7 +15493,7 @@
         <v>1898</v>
       </c>
       <c r="G338" s="9">
-        <f>(1+(F338-E338))-I338</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H338" s="8" t="s">
@@ -15526,7 +15530,7 @@
         <v>1967</v>
       </c>
       <c r="G339" s="9">
-        <f>(1+(F339-E339))-I339</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="H339" s="8" t="s">
@@ -15563,7 +15567,7 @@
         <v>1970</v>
       </c>
       <c r="G340" s="9">
-        <f>(1+(F340-E340))-I340</f>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="H340" s="8" t="s">
@@ -15600,7 +15604,7 @@
         <v>1970</v>
       </c>
       <c r="G341" s="9">
-        <f>(1+(F341-E341))-I341</f>
+        <f t="shared" si="10"/>
         <v>17</v>
       </c>
       <c r="H341" s="8" t="s">
@@ -15637,7 +15641,7 @@
         <v>1962</v>
       </c>
       <c r="G342" s="9">
-        <f>(1+(F342-E342))-I342</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="H342" s="8" t="s">
@@ -15674,7 +15678,7 @@
         <v>1967</v>
       </c>
       <c r="G343" s="9">
-        <f>(1+(F343-E343))-I343</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="H343" s="8" t="s">
@@ -15711,7 +15715,7 @@
         <v>1969</v>
       </c>
       <c r="G344" s="9">
-        <f>(1+(F344-E344))-I344</f>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="H344" s="8" t="s">
@@ -15748,7 +15752,7 @@
         <v>1926</v>
       </c>
       <c r="G345" s="9">
-        <f>(1+(F345-E345))-I345</f>
+        <f t="shared" ref="G345:G408" si="11">(1+(F345-E345))-I345</f>
         <v>12</v>
       </c>
       <c r="H345" s="8" t="s">
@@ -15785,7 +15789,7 @@
         <v>1892</v>
       </c>
       <c r="G346" s="9">
-        <f>(1+(F346-E346))-I346</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H346" s="8" t="s">
@@ -15822,7 +15826,7 @@
         <v>1882</v>
       </c>
       <c r="G347" s="9">
-        <f>(1+(F347-E347))-I347</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H347" s="8" t="s">
@@ -15859,13 +15863,15 @@
         <v>1882</v>
       </c>
       <c r="G348" s="9">
-        <f>(1+(F348-E348))-I348</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H348" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I348" s="9"/>
+      <c r="I348" s="9">
+        <v>0</v>
+      </c>
       <c r="J348" s="8" t="s">
         <v>770</v>
       </c>
@@ -15894,7 +15900,7 @@
         <v>1888</v>
       </c>
       <c r="G349" s="9">
-        <f>(1+(F349-E349))-I349</f>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
       <c r="H349" s="8" t="s">
@@ -15931,7 +15937,7 @@
         <v>1938</v>
       </c>
       <c r="G350" s="9">
-        <f>(1+(F350-E350))-I350</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="H350" s="8" t="s">
@@ -15969,7 +15975,7 @@
         <v>1968</v>
       </c>
       <c r="G351" s="9">
-        <f>(1+(F351-E351))-I351</f>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
       <c r="H351" s="8" t="s">
@@ -16006,7 +16012,7 @@
         <v>1968</v>
       </c>
       <c r="G352" s="9">
-        <f>(1+(F352-E352))-I352</f>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
       <c r="H352" s="8" t="s">
@@ -16043,7 +16049,7 @@
         <v>1968</v>
       </c>
       <c r="G353" s="9">
-        <f>(1+(F353-E353))-I353</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="H353" s="8" t="s">
@@ -16080,7 +16086,7 @@
         <v>1958</v>
       </c>
       <c r="G354" s="9">
-        <f>(1+(F354-E354))-I354</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="H354" s="8" t="s">
@@ -16117,7 +16123,7 @@
         <v>1968</v>
       </c>
       <c r="G355" s="9">
-        <f>(1+(F355-E355))-I355</f>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="H355" s="8" t="s">
@@ -16154,7 +16160,7 @@
         <v>1968</v>
       </c>
       <c r="G356" s="9">
-        <f>(1+(F356-E356))-I356</f>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
       <c r="H356" s="8" t="s">
@@ -16191,7 +16197,7 @@
         <v>1924</v>
       </c>
       <c r="G357" s="9">
-        <f>(1+(F357-E357))-I357</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H357" s="8" t="s">
@@ -16228,7 +16234,7 @@
         <v>1957</v>
       </c>
       <c r="G358" s="9">
-        <f>(1+(F358-E358))-I358</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H358" s="8" t="s">
@@ -16265,7 +16271,7 @@
         <v>1969</v>
       </c>
       <c r="G359" s="9">
-        <f>(1+(F359-E359))-I359</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="H359" s="8" t="s">
@@ -16302,7 +16308,7 @@
         <v>1957</v>
       </c>
       <c r="G360" s="9">
-        <f>(1+(F360-E360))-I360</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H360" s="8" t="s">
@@ -16339,7 +16345,7 @@
         <v>1967</v>
       </c>
       <c r="G361" s="9">
-        <f>(1+(F361-E361))-I361</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="H361" s="8" t="s">
@@ -16377,7 +16383,7 @@
         <v>1936</v>
       </c>
       <c r="G362" s="9">
-        <f>(1+(F362-E362))-I362</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H362" s="8" t="s">
@@ -16414,7 +16420,7 @@
         <v>1960</v>
       </c>
       <c r="G363" s="9">
-        <f>(1+(F363-E363))-I363</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H363" s="8" t="s">
@@ -16451,7 +16457,7 @@
         <v>1918</v>
       </c>
       <c r="G364" s="9">
-        <f>(1+(F364-E364))-I364</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H364" s="8" t="s">
@@ -16488,7 +16494,7 @@
         <v>1940</v>
       </c>
       <c r="G365" s="9">
-        <f>(1+(F365-E365))-I365</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H365" s="8" t="s">
@@ -16525,7 +16531,7 @@
         <v>1965</v>
       </c>
       <c r="G366" s="9">
-        <f>(1+(F366-E366))-I366</f>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="H366" s="8" t="s">
@@ -16561,7 +16567,7 @@
         <v>1964</v>
       </c>
       <c r="G367" s="9">
-        <f>(1+(F367-E367))-I367</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H367" s="8" t="s">
@@ -16597,7 +16603,7 @@
         <v>1948</v>
       </c>
       <c r="G368" s="9">
-        <f>(1+(F368-E368))-I368</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H368" s="8" t="s">
@@ -16633,7 +16639,7 @@
         <v>1932</v>
       </c>
       <c r="G369" s="9">
-        <f>(1+(F369-E369))-I369</f>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="H369" s="8" t="s">
@@ -16669,7 +16675,7 @@
         <v>1937</v>
       </c>
       <c r="G370" s="9">
-        <f>(1+(F370-E370))-I370</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H370" s="8" t="s">
@@ -16705,7 +16711,7 @@
         <v>1931</v>
       </c>
       <c r="G371" s="9">
-        <f>(1+(F371-E371))-I371</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H371" s="8" t="s">
@@ -16741,7 +16747,7 @@
         <v>1931</v>
       </c>
       <c r="G372" s="9">
-        <f>(1+(F372-E372))-I372</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H372" s="8" t="s">
@@ -16777,7 +16783,7 @@
         <v>1968</v>
       </c>
       <c r="G373" s="9">
-        <f>(1+(F373-E373))-I373</f>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
       <c r="H373" s="8" t="s">
@@ -16813,7 +16819,7 @@
         <v>1968</v>
       </c>
       <c r="G374" s="9">
-        <f>(1+(F374-E374))-I374</f>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="H374" s="8" t="s">
@@ -16849,7 +16855,7 @@
         <v>1935</v>
       </c>
       <c r="G375" s="9">
-        <f>(1+(F375-E375))-I375</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H375" s="8" t="s">
@@ -16885,7 +16891,7 @@
         <v>1908</v>
       </c>
       <c r="G376" s="9">
-        <f>(1+(F376-E376))-I376</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H376" s="8" t="s">
@@ -16921,7 +16927,7 @@
         <v>1958</v>
       </c>
       <c r="G377" s="9">
-        <f>(1+(F377-E377))-I377</f>
+        <f t="shared" si="11"/>
         <v>70</v>
       </c>
       <c r="H377" s="8" t="s">
@@ -16957,7 +16963,7 @@
         <v>1956</v>
       </c>
       <c r="G378" s="9">
-        <f>(1+(F378-E378))-I378</f>
+        <f t="shared" si="11"/>
         <v>75</v>
       </c>
       <c r="H378" s="8" t="s">
@@ -16993,7 +16999,7 @@
         <v>1972</v>
       </c>
       <c r="G379" s="9">
-        <f>(1+(F379-E379))-I379</f>
+        <f t="shared" si="11"/>
         <v>68</v>
       </c>
       <c r="H379" s="8" t="s">
@@ -17029,7 +17035,7 @@
         <v>1959</v>
       </c>
       <c r="G380" s="9">
-        <f>(1+(F380-E380))-I380</f>
+        <f t="shared" si="11"/>
         <v>56</v>
       </c>
       <c r="H380" s="8" t="s">
@@ -17065,7 +17071,7 @@
         <v>1969</v>
       </c>
       <c r="G381" s="9">
-        <f>(1+(F381-E381))-I381</f>
+        <f t="shared" si="11"/>
         <v>41</v>
       </c>
       <c r="H381" s="8" t="s">
@@ -17101,7 +17107,7 @@
         <v>1998</v>
       </c>
       <c r="G382" s="9">
-        <f>(1+(F382-E382))-I382</f>
+        <f t="shared" si="11"/>
         <v>22</v>
       </c>
       <c r="H382" s="8" t="s">
@@ -17137,7 +17143,7 @@
         <v>1989</v>
       </c>
       <c r="G383" s="9">
-        <f>(1+(F383-E383))-I383</f>
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
       <c r="H383" s="8" t="s">
@@ -17173,7 +17179,7 @@
         <v>1983</v>
       </c>
       <c r="G384" s="9">
-        <f>(1+(F384-E384))-I384</f>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="H384" s="8" t="s">
@@ -17209,7 +17215,7 @@
         <v>1962</v>
       </c>
       <c r="G385" s="9">
-        <f>(1+(F385-E385))-I385</f>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="H385" s="8" t="s">
@@ -17245,7 +17251,7 @@
         <v>1957</v>
       </c>
       <c r="G386" s="9">
-        <f>(1+(F386-E386))-I386</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H386" s="8" t="s">
@@ -17281,7 +17287,7 @@
         <v>1962</v>
       </c>
       <c r="G387" s="9">
-        <f>(1+(F387-E387))-I387</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H387" s="8" t="s">
@@ -17317,7 +17323,7 @@
         <v>1952</v>
       </c>
       <c r="G388" s="9">
-        <f>(1+(F388-E388))-I388</f>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
       <c r="H388" s="8" t="s">
@@ -17353,7 +17359,7 @@
         <v>1903</v>
       </c>
       <c r="G389" s="9">
-        <f>(1+(F389-E389))-I389</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H389" s="8" t="s">
@@ -17389,7 +17395,7 @@
         <v>1952</v>
       </c>
       <c r="G390" s="9">
-        <f>(1+(F390-E390))-I390</f>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="H390" s="8" t="s">
@@ -17425,7 +17431,7 @@
         <v>1955</v>
       </c>
       <c r="G391" s="9">
-        <f>(1+(F391-E391))-I391</f>
+        <f t="shared" si="11"/>
         <v>24</v>
       </c>
       <c r="H391" s="8" t="s">
@@ -17461,7 +17467,7 @@
         <v>1885</v>
       </c>
       <c r="G392" s="9">
-        <f>(1+(F392-E392))-I392</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H392" s="8" t="s">
@@ -17497,7 +17503,7 @@
         <v>1949</v>
       </c>
       <c r="G393" s="9">
-        <f>(1+(F393-E393))-I393</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="H393" s="8" t="s">
@@ -17533,7 +17539,7 @@
         <v>1886</v>
       </c>
       <c r="G394" s="9">
-        <f>(1+(F394-E394))-I394</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="H394" s="8" t="s">
@@ -17569,7 +17575,7 @@
         <v>1947</v>
       </c>
       <c r="G395" s="9">
-        <f>(1+(F395-E395))-I395</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H395" s="8" t="s">
@@ -17605,7 +17611,7 @@
         <v>1933</v>
       </c>
       <c r="G396" s="9">
-        <f>(1+(F396-E396))-I396</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H396" s="8" t="s">
@@ -17641,7 +17647,7 @@
         <v>1891</v>
       </c>
       <c r="G397" s="9">
-        <f>(1+(F397-E397))-I397</f>
+        <f t="shared" si="11"/>
         <v>29</v>
       </c>
       <c r="H397" s="8" t="s">
@@ -17677,7 +17683,7 @@
         <v>1996</v>
       </c>
       <c r="G398" s="9">
-        <f>(1+(F398-E398))-I398</f>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="H398" s="8" t="s">
@@ -17713,7 +17719,7 @@
         <v>1996</v>
       </c>
       <c r="G399" s="9">
-        <f>(1+(F399-E399))-I399</f>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="H399" s="8" t="s">
@@ -17749,7 +17755,7 @@
         <v>1992</v>
       </c>
       <c r="G400" s="9">
-        <f>(1+(F400-E400))-I400</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H400" s="8" t="s">
@@ -17785,7 +17791,7 @@
         <v>1990</v>
       </c>
       <c r="G401" s="9">
-        <f>(1+(F401-E401))-I401</f>
+        <f t="shared" si="11"/>
         <v>17</v>
       </c>
       <c r="H401" s="8" t="s">
@@ -17821,7 +17827,7 @@
         <v>1988</v>
       </c>
       <c r="G402" s="9">
-        <f>(1+(F402-E402))-I402</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="H402" s="8" t="s">
@@ -17857,7 +17863,7 @@
         <v>1987</v>
       </c>
       <c r="G403" s="9">
-        <f>(1+(F403-E403))-I403</f>
+        <f t="shared" si="11"/>
         <v>19</v>
       </c>
       <c r="H403" s="8">
@@ -17893,7 +17899,7 @@
         <v>1979</v>
       </c>
       <c r="G404" s="9">
-        <f>(1+(F404-E404))-I404</f>
+        <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="H404" s="8" t="s">
@@ -17929,7 +17935,7 @@
         <v>1992</v>
       </c>
       <c r="G405" s="9">
-        <f>(1+(F405-E405))-I405</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H405" s="8" t="s">
@@ -17965,7 +17971,7 @@
         <v>1996</v>
       </c>
       <c r="G406" s="9">
-        <f>(1+(F406-E406))-I406</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="H406" s="8" t="s">
@@ -18001,7 +18007,7 @@
         <v>1993</v>
       </c>
       <c r="G407" s="9">
-        <f>(1+(F407-E407))-I407</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="H407" s="8" t="s">
@@ -18037,7 +18043,7 @@
         <v>1989</v>
       </c>
       <c r="G408" s="9">
-        <f>(1+(F408-E408))-I408</f>
+        <f t="shared" si="11"/>
         <v>17</v>
       </c>
       <c r="H408" s="8">
@@ -18073,7 +18079,7 @@
         <v>1982</v>
       </c>
       <c r="G409" s="9">
-        <f>(1+(F409-E409))-I409</f>
+        <f t="shared" ref="G409:G472" si="12">(1+(F409-E409))-I409</f>
         <v>1</v>
       </c>
       <c r="H409" s="8" t="s">
@@ -18109,7 +18115,7 @@
         <v>1992</v>
       </c>
       <c r="G410" s="9">
-        <f>(1+(F410-E410))-I410</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="H410" s="8" t="s">
@@ -18145,7 +18151,7 @@
         <v>1971</v>
       </c>
       <c r="G411" s="9">
-        <f>(1+(F411-E411))-I411</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="H411" s="8" t="s">
@@ -18181,7 +18187,7 @@
         <v>1918</v>
       </c>
       <c r="G412" s="9">
-        <f>(1+(F412-E412))-I412</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="H412" s="8" t="s">
@@ -18217,7 +18223,7 @@
         <v>1995</v>
       </c>
       <c r="G413" s="9">
-        <f>(1+(F413-E413))-I413</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H413" s="8" t="s">
@@ -18253,7 +18259,7 @@
         <v>1969</v>
       </c>
       <c r="G414" s="9">
-        <f>(1+(F414-E414))-I414</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="H414" s="8" t="s">
@@ -18289,7 +18295,7 @@
         <v>1988</v>
       </c>
       <c r="G415" s="9">
-        <f>(1+(F415-E415))-I415</f>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
       <c r="H415" s="8" t="s">
@@ -18325,7 +18331,7 @@
         <v>1984</v>
       </c>
       <c r="G416" s="9">
-        <f>(1+(F416-E416))-I416</f>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="H416" s="8" t="s">
@@ -18361,7 +18367,7 @@
         <v>1935</v>
       </c>
       <c r="G417" s="9">
-        <f>(1+(F417-E417))-I417</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="H417" s="8" t="s">
@@ -18397,7 +18403,7 @@
         <v>1996</v>
       </c>
       <c r="G418" s="9">
-        <f>(1+(F418-E418))-I418</f>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
       <c r="H418" s="8" t="s">
@@ -18433,7 +18439,7 @@
         <v>1972</v>
       </c>
       <c r="G419" s="9">
-        <f>(1+(F419-E419))-I419</f>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="H419" s="8" t="s">
@@ -18469,7 +18475,7 @@
         <v>1961</v>
       </c>
       <c r="G420" s="9">
-        <f>(1+(F420-E420))-I420</f>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
       <c r="H420" s="8" t="s">
@@ -18505,7 +18511,7 @@
         <v>1987</v>
       </c>
       <c r="G421" s="9">
-        <f>(1+(F421-E421))-I421</f>
+        <f t="shared" si="12"/>
         <v>22</v>
       </c>
       <c r="H421" s="8" t="s">
@@ -18541,7 +18547,7 @@
         <v>1958</v>
       </c>
       <c r="G422" s="9">
-        <f>(1+(F422-E422))-I422</f>
+        <f t="shared" si="12"/>
         <v>22</v>
       </c>
       <c r="H422" s="8">
@@ -18577,7 +18583,7 @@
         <v>1991</v>
       </c>
       <c r="G423" s="9">
-        <f>(1+(F423-E423))-I423</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="H423" s="8" t="s">
@@ -18613,7 +18619,7 @@
         <v>1964</v>
       </c>
       <c r="G424" s="9">
-        <f>(1+(F424-E424))-I424</f>
+        <f t="shared" si="12"/>
         <v>29</v>
       </c>
       <c r="H424" s="8" t="s">
@@ -18649,7 +18655,7 @@
         <v>1967</v>
       </c>
       <c r="G425" s="9">
-        <f>(1+(F425-E425))-I425</f>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="H425" s="8" t="s">
@@ -18685,7 +18691,7 @@
         <v>1976</v>
       </c>
       <c r="G426" s="9">
-        <f>(1+(F426-E426))-I426</f>
+        <f t="shared" si="12"/>
         <v>11</v>
       </c>
       <c r="H426" s="8" t="s">
@@ -18721,7 +18727,7 @@
         <v>1997</v>
       </c>
       <c r="G427" s="9">
-        <f>(1+(F427-E427))-I427</f>
+        <f t="shared" si="12"/>
         <v>16</v>
       </c>
       <c r="H427" s="8" t="s">
@@ -18757,7 +18763,7 @@
         <v>1912</v>
       </c>
       <c r="G428" s="9">
-        <f>(1+(F428-E428))-I428</f>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
       <c r="H428" s="8" t="s">
@@ -18793,7 +18799,7 @@
         <v>1978</v>
       </c>
       <c r="G429" s="9">
-        <f>(1+(F429-E429))-I429</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="H429" s="8" t="s">
@@ -18829,7 +18835,7 @@
         <v>1981</v>
       </c>
       <c r="G430" s="9">
-        <f>(1+(F430-E430))-I430</f>
+        <f t="shared" si="12"/>
         <v>1.3333333333333335</v>
       </c>
       <c r="H430" s="8" t="s">
@@ -18866,7 +18872,7 @@
         <v>1956</v>
       </c>
       <c r="G431" s="9">
-        <f>(1+(F431-E431))-I431</f>
+        <f t="shared" si="12"/>
         <v>4.3141025641025639</v>
       </c>
       <c r="H431" s="8" t="s">
@@ -18903,7 +18909,7 @@
         <v>1981</v>
       </c>
       <c r="G432" s="9">
-        <f>(1+(F432-E432))-I432</f>
+        <f t="shared" si="12"/>
         <v>1.3333333333333333</v>
       </c>
       <c r="H432" s="8" t="s">
@@ -18940,7 +18946,7 @@
         <v>1996</v>
       </c>
       <c r="G433" s="9">
-        <f>(1+(F433-E433))-I433</f>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="H433" s="8" t="s">
@@ -18976,7 +18982,7 @@
         <v>1997</v>
       </c>
       <c r="G434" s="9">
-        <f>(1+(F434-E434))-I434</f>
+        <f t="shared" si="12"/>
         <v>28</v>
       </c>
       <c r="H434" s="8" t="s">
@@ -19012,7 +19018,7 @@
         <v>1988</v>
       </c>
       <c r="G435" s="9">
-        <f>(1+(F435-E435))-I435</f>
+        <f t="shared" si="12"/>
         <v>25</v>
       </c>
       <c r="H435" s="8" t="s">
@@ -19048,7 +19054,7 @@
         <v>1997</v>
       </c>
       <c r="G436" s="9">
-        <f>(1+(F436-E436))-I436</f>
+        <f t="shared" si="12"/>
         <v>69</v>
       </c>
       <c r="H436" s="8" t="s">
@@ -19084,7 +19090,7 @@
         <v>1983</v>
       </c>
       <c r="G437" s="9">
-        <f>(1+(F437-E437))-I437</f>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="H437" s="8" t="s">
@@ -19120,7 +19126,7 @@
         <v>1989</v>
       </c>
       <c r="G438" s="9">
-        <f>(1+(F438-E438))-I438</f>
+        <f t="shared" si="12"/>
         <v>61</v>
       </c>
       <c r="H438" s="8" t="s">
@@ -19156,7 +19162,7 @@
         <v>1990</v>
       </c>
       <c r="G439" s="9">
-        <f>(1+(F439-E439))-I439</f>
+        <f t="shared" si="12"/>
         <v>41</v>
       </c>
       <c r="H439" s="8" t="s">
@@ -19192,7 +19198,7 @@
         <v>1990</v>
       </c>
       <c r="G440" s="9">
-        <f>(1+(F440-E440))-I440</f>
+        <f t="shared" si="12"/>
         <v>41</v>
       </c>
       <c r="H440" s="8" t="s">
@@ -19228,7 +19234,7 @@
         <v>1997</v>
       </c>
       <c r="G441" s="9">
-        <f>(1+(F441-E441))-I441</f>
+        <f t="shared" si="12"/>
         <v>69</v>
       </c>
       <c r="H441" s="8" t="s">
@@ -19264,7 +19270,7 @@
         <v>1997</v>
       </c>
       <c r="G442" s="9">
-        <f>(1+(F442-E442))-I442</f>
+        <f t="shared" si="12"/>
         <v>69</v>
       </c>
       <c r="H442" s="8" t="s">
@@ -19300,7 +19306,7 @@
         <v>1997</v>
       </c>
       <c r="G443" s="9">
-        <f>(1+(F443-E443))-I443</f>
+        <f t="shared" si="12"/>
         <v>36</v>
       </c>
       <c r="H443" s="8" t="s">
@@ -19336,7 +19342,7 @@
         <v>1972</v>
       </c>
       <c r="G444" s="9">
-        <f>(1+(F444-E444))-I444</f>
+        <f t="shared" si="12"/>
         <v>79.400000000000006</v>
       </c>
       <c r="H444" s="9" t="s">
@@ -19372,7 +19378,7 @@
         <v>1952</v>
       </c>
       <c r="G445" s="9">
-        <f>(1+(F445-E445))-I445</f>
+        <f t="shared" si="12"/>
         <v>43.3</v>
       </c>
       <c r="H445" s="9" t="s">
@@ -19408,7 +19414,7 @@
         <v>1972</v>
       </c>
       <c r="G446" s="9">
-        <f>(1+(F446-E446))-I446</f>
+        <f t="shared" si="12"/>
         <v>62.3</v>
       </c>
       <c r="H446" s="9" t="s">
@@ -19444,7 +19450,7 @@
         <v>1966</v>
       </c>
       <c r="G447" s="9">
-        <f>(1+(F447-E447))-I447</f>
+        <f t="shared" si="12"/>
         <v>45</v>
       </c>
       <c r="H447" s="9" t="s">
@@ -19480,7 +19486,7 @@
         <v>1890</v>
       </c>
       <c r="G448" s="9">
-        <f>(1+(F448-E448))-I448</f>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
       <c r="H448" s="9" t="s">
@@ -19516,7 +19522,7 @@
         <v>1966</v>
       </c>
       <c r="G449" s="9">
-        <f>(1+(F449-E449))-I449</f>
+        <f t="shared" si="12"/>
         <v>55.8</v>
       </c>
       <c r="H449" s="9" t="s">
@@ -19552,7 +19558,7 @@
         <v>1906</v>
       </c>
       <c r="G450" s="9">
-        <f>(1+(F450-E450))-I450</f>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="H450" s="9" t="s">
@@ -19588,7 +19594,7 @@
         <v>1910</v>
       </c>
       <c r="G451" s="9">
-        <f>(1+(F451-E451))-I451</f>
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
       <c r="H451" s="9" t="s">
@@ -19624,7 +19630,7 @@
         <v>1907</v>
       </c>
       <c r="G452" s="9">
-        <f>(1+(F452-E452))-I452</f>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
       <c r="H452" s="9" t="s">
@@ -19660,7 +19666,7 @@
         <v>1921</v>
       </c>
       <c r="G453" s="9">
-        <f>(1+(F453-E453))-I453</f>
+        <f t="shared" si="12"/>
         <v>16</v>
       </c>
       <c r="H453" s="9" t="s">
@@ -19696,7 +19702,7 @@
         <v>1982</v>
       </c>
       <c r="G454" s="9">
-        <f>(1+(F454-E454))-I454</f>
+        <f t="shared" si="12"/>
         <v>54.4</v>
       </c>
       <c r="H454" s="9" t="s">
@@ -19732,7 +19738,7 @@
         <v>1966</v>
       </c>
       <c r="G455" s="9">
-        <f>(1+(F455-E455))-I455</f>
+        <f t="shared" si="12"/>
         <v>56.2</v>
       </c>
       <c r="H455" s="9" t="s">
@@ -19768,7 +19774,7 @@
         <v>1906</v>
       </c>
       <c r="G456" s="9">
-        <f>(1+(F456-E456))-I456</f>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="H456" s="9" t="s">
@@ -19804,7 +19810,7 @@
         <v>1982</v>
       </c>
       <c r="G457" s="9">
-        <f>(1+(F457-E457))-I457</f>
+        <f t="shared" si="12"/>
         <v>31.799999999999997</v>
       </c>
       <c r="H457" s="9" t="s">
@@ -19840,7 +19846,7 @@
         <v>1906</v>
       </c>
       <c r="G458" s="9">
-        <f>(1+(F458-E458))-I458</f>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="H458" s="9" t="s">
@@ -19876,7 +19882,7 @@
         <v>1971</v>
       </c>
       <c r="G459" s="9">
-        <f>(1+(F459-E459))-I459</f>
+        <f t="shared" si="12"/>
         <v>63</v>
       </c>
       <c r="H459" s="9" t="s">
@@ -19912,7 +19918,7 @@
         <v>1881</v>
       </c>
       <c r="G460" s="9">
-        <f>(1+(F460-E460))-I460</f>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="H460" s="9" t="s">
@@ -19948,7 +19954,7 @@
         <v>1881</v>
       </c>
       <c r="G461" s="9">
-        <f>(1+(F461-E461))-I461</f>
+        <f t="shared" si="12"/>
         <v>21</v>
       </c>
       <c r="H461" s="9" t="s">
@@ -19984,7 +19990,7 @@
         <v>1881</v>
       </c>
       <c r="G462" s="9">
-        <f>(1+(F462-E462))-I462</f>
+        <f t="shared" si="12"/>
         <v>21</v>
       </c>
       <c r="H462" s="9" t="s">
@@ -20020,7 +20026,7 @@
         <v>1980</v>
       </c>
       <c r="G463" s="9">
-        <f>(1+(F463-E463))-I463</f>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="H463" s="9" t="s">
@@ -20056,7 +20062,7 @@
         <v>1906</v>
       </c>
       <c r="G464" s="9">
-        <f>(1+(F464-E464))-I464</f>
+        <f t="shared" si="12"/>
         <v>6</v>
       </c>
       <c r="H464" s="9" t="s">
@@ -20092,7 +20098,7 @@
         <v>1974</v>
       </c>
       <c r="G465" s="9">
-        <f>(1+(F465-E465))-I465</f>
+        <f t="shared" si="12"/>
         <v>53</v>
       </c>
       <c r="H465" s="9" t="s">
@@ -20128,7 +20134,7 @@
         <v>1878</v>
       </c>
       <c r="G466" s="9">
-        <f>(1+(F466-E466))-I466</f>
+        <f t="shared" si="12"/>
         <v>19</v>
       </c>
       <c r="H466" s="9" t="s">
@@ -20164,7 +20170,7 @@
         <v>1980</v>
       </c>
       <c r="G467" s="9">
-        <f>(1+(F467-E467))-I467</f>
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
       <c r="H467" s="8" t="s">
@@ -20200,7 +20206,7 @@
         <v>1962</v>
       </c>
       <c r="G468" s="9">
-        <f>(1+(F468-E468))-I468</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="H468" s="8" t="s">
@@ -20236,7 +20242,7 @@
         <v>1853</v>
       </c>
       <c r="G469" s="9">
-        <f>(1+(F469-E469))-I469</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H469" s="8" t="s">
@@ -20272,7 +20278,7 @@
         <v>1853</v>
       </c>
       <c r="G470" s="9">
-        <f>(1+(F470-E470))-I470</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H470" s="8" t="s">
@@ -20308,7 +20314,7 @@
         <v>1918</v>
       </c>
       <c r="G471" s="9">
-        <f>(1+(F471-E471))-I471</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="H471" s="8" t="s">
@@ -20344,7 +20350,7 @@
         <v>1888</v>
       </c>
       <c r="G472" s="9">
-        <f>(1+(F472-E472))-I472</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H472" s="8" t="s">
@@ -20380,7 +20386,7 @@
         <v>1995</v>
       </c>
       <c r="G473" s="9">
-        <f>(1+(F473-E473))-I473</f>
+        <f t="shared" ref="G473:G536" si="13">(1+(F473-E473))-I473</f>
         <v>4</v>
       </c>
       <c r="H473" s="8" t="s">
@@ -20416,7 +20422,7 @@
         <v>1936</v>
       </c>
       <c r="G474" s="9">
-        <f>(1+(F474-E474))-I474</f>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="H474" s="8" t="s">
@@ -20452,7 +20458,7 @@
         <v>1886</v>
       </c>
       <c r="G475" s="9">
-        <f>(1+(F475-E475))-I475</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="H475" s="8" t="s">
@@ -20488,7 +20494,7 @@
         <v>1896</v>
       </c>
       <c r="G476" s="9">
-        <f>(1+(F476-E476))-I476</f>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
       <c r="H476" s="8" t="s">
@@ -20524,7 +20530,7 @@
         <v>1839</v>
       </c>
       <c r="G477" s="9">
-        <f>(1+(F477-E477))-I477</f>
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
       <c r="H477" s="8" t="s">
@@ -20560,7 +20566,7 @@
         <v>1939</v>
       </c>
       <c r="G478" s="9">
-        <f>(1+(F478-E478))-I478</f>
+        <f t="shared" si="13"/>
         <v>29</v>
       </c>
       <c r="H478" s="8" t="s">
@@ -20596,7 +20602,7 @@
         <v>1937</v>
       </c>
       <c r="G479" s="9">
-        <f>(1+(F479-E479))-I479</f>
+        <f t="shared" si="13"/>
         <v>48</v>
       </c>
       <c r="H479" s="8" t="s">
@@ -20704,7 +20710,7 @@
         <v>1910</v>
       </c>
       <c r="G482" s="9">
-        <f>(1+(F482-E482))-I482</f>
+        <f t="shared" ref="G482:G513" si="14">(1+(F482-E482))-I482</f>
         <v>5</v>
       </c>
       <c r="H482" s="8" t="s">
@@ -20740,7 +20746,7 @@
         <v>1882</v>
       </c>
       <c r="G483" s="9">
-        <f>(1+(F483-E483))-I483</f>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="H483" s="8" t="s">
@@ -20776,7 +20782,7 @@
         <v>1913</v>
       </c>
       <c r="G484" s="9">
-        <f>(1+(F484-E484))-I484</f>
+        <f t="shared" si="14"/>
         <v>41</v>
       </c>
       <c r="H484" s="8" t="s">
@@ -20812,7 +20818,7 @@
         <v>1852</v>
       </c>
       <c r="G485" s="9">
-        <f>(1+(F485-E485))-I485</f>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="H485" s="8" t="s">
@@ -20848,7 +20854,7 @@
         <v>1879</v>
       </c>
       <c r="G486" s="9">
-        <f>(1+(F486-E486))-I486</f>
+        <f t="shared" si="14"/>
         <v>6</v>
       </c>
       <c r="H486" s="8" t="s">
@@ -20884,7 +20890,7 @@
         <v>1939</v>
       </c>
       <c r="G487" s="9">
-        <f>(1+(F487-E487))-I487</f>
+        <f t="shared" si="14"/>
         <v>41</v>
       </c>
       <c r="H487" s="8" t="s">
@@ -20920,7 +20926,7 @@
         <v>1939</v>
       </c>
       <c r="G488" s="9">
-        <f>(1+(F488-E488))-I488</f>
+        <f t="shared" si="14"/>
         <v>50</v>
       </c>
       <c r="H488" s="8" t="s">
@@ -20956,7 +20962,7 @@
         <v>1920</v>
       </c>
       <c r="G489" s="9">
-        <f>(1+(F489-E489))-I489</f>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="H489" s="8" t="s">
@@ -20992,7 +20998,7 @@
         <v>1939</v>
       </c>
       <c r="G490" s="9">
-        <f>(1+(F490-E490))-I490</f>
+        <f t="shared" si="14"/>
         <v>88</v>
       </c>
       <c r="H490" s="8" t="s">
@@ -21028,7 +21034,7 @@
         <v>1939</v>
       </c>
       <c r="G491" s="9">
-        <f>(1+(F491-E491))-I491</f>
+        <f t="shared" si="14"/>
         <v>16</v>
       </c>
       <c r="H491" s="8" t="s">
@@ -21064,7 +21070,7 @@
         <v>1937</v>
       </c>
       <c r="G492" s="9">
-        <f>(1+(F492-E492))-I492</f>
+        <f t="shared" si="14"/>
         <v>86</v>
       </c>
       <c r="H492" s="8" t="s">
@@ -21100,7 +21106,7 @@
         <v>1853</v>
       </c>
       <c r="G493" s="9">
-        <f>(1+(F493-E493))-I493</f>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="H493" s="8" t="s">
@@ -21136,7 +21142,7 @@
         <v>1870</v>
       </c>
       <c r="G494" s="9">
-        <f>(1+(F494-E494))-I494</f>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="H494" s="8" t="s">
@@ -21172,7 +21178,7 @@
         <v>1941</v>
       </c>
       <c r="G495" s="9">
-        <f>(1+(F495-E495))-I495</f>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="H495" s="8" t="s">
@@ -21208,7 +21214,7 @@
         <v>1892</v>
       </c>
       <c r="G496" s="9">
-        <f>(1+(F496-E496))-I496</f>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="H496" s="8" t="s">
@@ -21244,7 +21250,7 @@
         <v>1913</v>
       </c>
       <c r="G497" s="9">
-        <f>(1+(F497-E497))-I497</f>
+        <f t="shared" si="14"/>
         <v>28</v>
       </c>
       <c r="H497" s="8" t="s">
@@ -21280,7 +21286,7 @@
         <v>1925</v>
       </c>
       <c r="G498" s="9">
-        <f>(1+(F498-E498))-I498</f>
+        <f t="shared" si="14"/>
         <v>29</v>
       </c>
       <c r="H498" s="8" t="s">
@@ -21316,7 +21322,7 @@
         <v>1891</v>
       </c>
       <c r="G499" s="9">
-        <f>(1+(F499-E499))-I499</f>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="H499" s="8" t="s">
@@ -21352,7 +21358,7 @@
         <v>1899</v>
       </c>
       <c r="G500" s="9">
-        <f>(1+(F500-E500))-I500</f>
+        <f t="shared" si="14"/>
         <v>7</v>
       </c>
       <c r="H500" s="8">
@@ -21388,7 +21394,7 @@
         <v>1935</v>
       </c>
       <c r="G501" s="9">
-        <f>(1+(F501-E501))-I501</f>
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
       <c r="H501" s="8" t="s">
@@ -21424,7 +21430,7 @@
         <v>1938</v>
       </c>
       <c r="G502" s="9">
-        <f>(1+(F502-E502))-I502</f>
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
       <c r="H502" s="8" t="s">
@@ -21460,7 +21466,7 @@
         <v>1938</v>
       </c>
       <c r="G503" s="9">
-        <f>(1+(F503-E503))-I503</f>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="H503" s="8" t="s">
@@ -21496,7 +21502,7 @@
         <v>1853</v>
       </c>
       <c r="G504" s="9">
-        <f>(1+(F504-E504))-I504</f>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="H504" s="8" t="s">
@@ -21532,7 +21538,7 @@
         <v>1892</v>
       </c>
       <c r="G505" s="9">
-        <f>(1+(F505-E505))-I505</f>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="H505" s="8" t="s">
@@ -21568,7 +21574,7 @@
         <v>1957</v>
       </c>
       <c r="G506" s="9">
-        <f>(1+(F506-E506))-I506</f>
+        <f t="shared" si="14"/>
         <v>32</v>
       </c>
       <c r="H506" s="8" t="s">
@@ -21604,7 +21610,7 @@
         <v>1829</v>
       </c>
       <c r="G507" s="9">
-        <f>(1+(F507-E507))-I507</f>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="H507" s="8" t="s">
@@ -21640,7 +21646,7 @@
         <v>1912</v>
       </c>
       <c r="G508" s="9">
-        <f>(1+(F508-E508))-I508</f>
+        <f t="shared" si="14"/>
         <v>10</v>
       </c>
       <c r="H508" s="8" t="s">
@@ -21676,7 +21682,7 @@
         <v>1916</v>
       </c>
       <c r="G509" s="9">
-        <f>(1+(F509-E509))-I509</f>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="H509" s="8" t="s">
@@ -21712,7 +21718,7 @@
         <v>1928</v>
       </c>
       <c r="G510" s="9">
-        <f>(1+(F510-E510))-I510</f>
+        <f t="shared" si="14"/>
         <v>8</v>
       </c>
       <c r="H510" s="8" t="s">
@@ -21748,7 +21754,7 @@
         <v>1901</v>
       </c>
       <c r="G511" s="9">
-        <f>(1+(F511-E511))-I511</f>
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
       <c r="H511" s="8" t="s">
@@ -21784,7 +21790,7 @@
         <v>1847</v>
       </c>
       <c r="G512" s="9">
-        <f>(1+(F512-E512))-I512</f>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="H512" s="8" t="s">
@@ -21820,7 +21826,7 @@
         <v>1902</v>
       </c>
       <c r="G513" s="9">
-        <f>(1+(F513-E513))-I513</f>
+        <f t="shared" si="14"/>
         <v>13</v>
       </c>
       <c r="H513" s="8" t="s">
@@ -21856,7 +21862,7 @@
         <v>1915</v>
       </c>
       <c r="G514" s="9">
-        <f>(1+(F514-E514))-I514</f>
+        <f t="shared" ref="G514:G545" si="15">(1+(F514-E514))-I514</f>
         <v>3</v>
       </c>
       <c r="H514" s="8" t="s">
@@ -21892,7 +21898,7 @@
         <v>1951</v>
       </c>
       <c r="G515" s="9">
-        <f>(1+(F515-E515))-I515</f>
+        <f t="shared" si="15"/>
         <v>10</v>
       </c>
       <c r="H515" s="8" t="s">
@@ -21928,7 +21934,7 @@
         <v>1910</v>
       </c>
       <c r="G516" s="9">
-        <f>(1+(F516-E516))-I516</f>
+        <f t="shared" si="15"/>
         <v>9</v>
       </c>
       <c r="H516" s="8" t="s">
@@ -21964,7 +21970,7 @@
         <v>1972</v>
       </c>
       <c r="G517" s="9">
-        <f>(1+(F517-E517))-I517</f>
+        <f t="shared" si="15"/>
         <v>81</v>
       </c>
       <c r="H517" s="8" t="s">
@@ -22000,7 +22006,7 @@
         <v>1974</v>
       </c>
       <c r="G518" s="9">
-        <f>(1+(F518-E518))-I518</f>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="H518" s="8" t="s">
@@ -22036,7 +22042,7 @@
         <v>1915</v>
       </c>
       <c r="G519" s="9">
-        <f>(1+(F519-E519))-I519</f>
+        <f t="shared" si="15"/>
         <v>8</v>
       </c>
       <c r="H519" s="8" t="s">
@@ -22072,7 +22078,7 @@
         <v>1963</v>
       </c>
       <c r="G520" s="9">
-        <f>(1+(F520-E520))-I520</f>
+        <f t="shared" si="15"/>
         <v>12</v>
       </c>
       <c r="H520" s="8" t="s">
@@ -22108,7 +22114,7 @@
         <v>1916</v>
       </c>
       <c r="G521" s="9">
-        <f>(1+(F521-E521))-I521</f>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
       <c r="H521" s="8" t="s">
@@ -22144,7 +22150,7 @@
         <v>1934</v>
       </c>
       <c r="G522" s="9">
-        <f>(1+(F522-E522))-I522</f>
+        <f t="shared" si="15"/>
         <v>27</v>
       </c>
       <c r="H522" s="8" t="s">
@@ -22180,7 +22186,7 @@
         <v>1897</v>
       </c>
       <c r="G523" s="9">
-        <f>(1+(F523-E523))-I523</f>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="H523" s="8" t="s">
@@ -22216,7 +22222,7 @@
         <v>1957</v>
       </c>
       <c r="G524" s="9">
-        <f>(1+(F524-E524))-I524</f>
+        <f t="shared" si="15"/>
         <v>55</v>
       </c>
       <c r="H524" s="8" t="s">
@@ -22252,7 +22258,7 @@
         <v>1892</v>
       </c>
       <c r="G525" s="9">
-        <f>(1+(F525-E525))-I525</f>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="H525" s="8" t="s">
@@ -22288,7 +22294,7 @@
         <v>1878</v>
       </c>
       <c r="G526" s="9">
-        <f>(1+(F526-E526))-I526</f>
+        <f t="shared" si="15"/>
         <v>8</v>
       </c>
       <c r="H526" s="8" t="s">
@@ -22324,7 +22330,7 @@
         <v>1898</v>
       </c>
       <c r="G527" s="9">
-        <f>(1+(F527-E527))-I527</f>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="H527" s="8" t="s">
@@ -22360,7 +22366,7 @@
         <v>1918</v>
       </c>
       <c r="G528" s="9">
-        <f>(1+(F528-E528))-I528</f>
+        <f t="shared" si="15"/>
         <v>17</v>
       </c>
       <c r="H528" s="8" t="s">
@@ -22396,7 +22402,7 @@
         <v>1950</v>
       </c>
       <c r="G529" s="9">
-        <f>(1+(F529-E529))-I529</f>
+        <f t="shared" si="15"/>
         <v>21</v>
       </c>
       <c r="H529" s="8" t="s">
@@ -22432,7 +22438,7 @@
         <v>1858</v>
       </c>
       <c r="G530" s="9">
-        <f>(1+(F530-E530))-I530</f>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="H530" s="8" t="s">
@@ -22468,7 +22474,7 @@
         <v>1861</v>
       </c>
       <c r="G531" s="9">
-        <f>(1+(F531-E531))-I531</f>
+        <f t="shared" si="15"/>
         <v>5</v>
       </c>
       <c r="H531" s="8" t="s">
@@ -22504,7 +22510,7 @@
         <v>1966</v>
       </c>
       <c r="G532" s="9">
-        <f>(1+(F532-E532))-I532</f>
+        <f t="shared" si="15"/>
         <v>5</v>
       </c>
       <c r="H532" s="8" t="s">
@@ -22540,7 +22546,7 @@
         <v>1926</v>
       </c>
       <c r="G533" s="9">
-        <f>(1+(F533-E533))-I533</f>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
       <c r="H533" s="8" t="s">
@@ -22576,7 +22582,7 @@
         <v>1926</v>
       </c>
       <c r="G534" s="9">
-        <f>(1+(F534-E534))-I534</f>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
       <c r="H534" s="8" t="s">
@@ -22612,7 +22618,7 @@
         <v>1893</v>
       </c>
       <c r="G535" s="9">
-        <f>(1+(F535-E535))-I535</f>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="H535" s="8" t="s">
@@ -22648,7 +22654,7 @@
         <v>1859</v>
       </c>
       <c r="G536" s="9">
-        <f>(1+(F536-E536))-I536</f>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="H536" s="8" t="s">
@@ -22684,7 +22690,7 @@
         <v>1937</v>
       </c>
       <c r="G537" s="9">
-        <f>(1+(F537-E537))-I537</f>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="H537" s="8" t="s">
@@ -22720,7 +22726,7 @@
         <v>1919</v>
       </c>
       <c r="G538" s="9">
-        <f>(1+(F538-E538))-I538</f>
+        <f t="shared" si="15"/>
         <v>8</v>
       </c>
       <c r="H538" s="8" t="s">
@@ -22756,7 +22762,7 @@
         <v>1954</v>
       </c>
       <c r="G539" s="9">
-        <f>(1+(F539-E539))-I539</f>
+        <f t="shared" si="15"/>
         <v>19</v>
       </c>
       <c r="H539" s="8" t="s">
@@ -22792,7 +22798,7 @@
         <v>1947</v>
       </c>
       <c r="G540" s="9">
-        <f>(1+(F540-E540))-I540</f>
+        <f t="shared" si="15"/>
         <v>73</v>
       </c>
       <c r="H540" s="8" t="s">
@@ -22828,7 +22834,7 @@
         <v>1943</v>
       </c>
       <c r="G541" s="9">
-        <f>(1+(F541-E541))-I541</f>
+        <f t="shared" si="15"/>
         <v>69</v>
       </c>
       <c r="H541" s="8" t="s">
@@ -22864,7 +22870,7 @@
         <v>1953</v>
       </c>
       <c r="G542" s="9">
-        <f>(1+(F542-E542))-I542</f>
+        <f t="shared" si="15"/>
         <v>13</v>
       </c>
       <c r="H542" s="8" t="s">
@@ -22900,7 +22906,7 @@
         <v>1943</v>
       </c>
       <c r="G543" s="9">
-        <f>(1+(F543-E543))-I543</f>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
       <c r="H543" s="8" t="s">
@@ -22936,7 +22942,7 @@
         <v>1953</v>
       </c>
       <c r="G544" s="9">
-        <f>(1+(F544-E544))-I544</f>
+        <f t="shared" si="15"/>
         <v>13</v>
       </c>
       <c r="H544" s="8" t="s">
@@ -22972,7 +22978,7 @@
         <v>1952</v>
       </c>
       <c r="G545" s="9">
-        <f>(1+(F545-E545))-I545</f>
+        <f t="shared" si="15"/>
         <v>9</v>
       </c>
       <c r="H545" s="8" t="s">
@@ -23008,7 +23014,7 @@
         <v>1960</v>
       </c>
       <c r="G546" s="9">
-        <f>(1+(F546-E546))-I546</f>
+        <f t="shared" ref="G546:G577" si="16">(1+(F546-E546))-I546</f>
         <v>52</v>
       </c>
       <c r="H546" s="8" t="s">
@@ -23044,7 +23050,7 @@
         <v>1979</v>
       </c>
       <c r="G547" s="9">
-        <f>(1+(F547-E547))-I547</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="H547" s="8" t="s">
@@ -23080,7 +23086,7 @@
         <v>1974</v>
       </c>
       <c r="G548" s="9">
-        <f>(1+(F548-E548))-I548</f>
+        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="H548" s="8" t="s">
@@ -23116,7 +23122,7 @@
         <v>1969</v>
       </c>
       <c r="G549" s="9">
-        <f>(1+(F549-E549))-I549</f>
+        <f t="shared" si="16"/>
         <v>15</v>
       </c>
       <c r="H549" s="8" t="s">
@@ -23152,7 +23158,7 @@
         <v>1947</v>
       </c>
       <c r="G550" s="9">
-        <f>(1+(F550-E550))-I550</f>
+        <f t="shared" si="16"/>
         <v>7</v>
       </c>
       <c r="H550" s="8" t="s">
@@ -23188,7 +23194,7 @@
         <v>1976</v>
       </c>
       <c r="G551" s="9">
-        <f>(1+(F551-E551))-I551</f>
+        <f t="shared" si="16"/>
         <v>33</v>
       </c>
       <c r="H551" s="8" t="s">
@@ -23224,7 +23230,7 @@
         <v>1923</v>
       </c>
       <c r="G552" s="9">
-        <f>(1+(F552-E552))-I552</f>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="H552" s="8" t="s">
@@ -23260,7 +23266,7 @@
         <v>1985</v>
       </c>
       <c r="G553" s="9">
-        <f>(1+(F553-E553))-I553</f>
+        <f t="shared" si="16"/>
         <v>17</v>
       </c>
       <c r="H553" s="8" t="s">
@@ -23296,7 +23302,7 @@
         <v>1956</v>
       </c>
       <c r="G554" s="9">
-        <f>(1+(F554-E554))-I554</f>
+        <f t="shared" si="16"/>
         <v>26</v>
       </c>
       <c r="H554" s="8" t="s">
@@ -23332,7 +23338,7 @@
         <v>1981</v>
       </c>
       <c r="G555" s="9">
-        <f>(1+(F555-E555))-I555</f>
+        <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="H555" s="8" t="s">
@@ -23368,7 +23374,7 @@
         <v>1956</v>
       </c>
       <c r="G556" s="9">
-        <f>(1+(F556-E556))-I556</f>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="H556" s="8" t="s">
@@ -23404,7 +23410,7 @@
         <v>1957</v>
       </c>
       <c r="G557" s="9">
-        <f>(1+(F557-E557))-I557</f>
+        <f t="shared" si="16"/>
         <v>8</v>
       </c>
       <c r="H557" s="8" t="s">
@@ -23440,7 +23446,7 @@
         <v>1904</v>
       </c>
       <c r="G558" s="9">
-        <f>(1+(F558-E558))-I558</f>
+        <f t="shared" si="16"/>
         <v>22</v>
       </c>
       <c r="H558" s="8" t="s">
@@ -23476,7 +23482,7 @@
         <v>1935</v>
       </c>
       <c r="G559" s="9">
-        <f>(1+(F559-E559))-I559</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="H559" s="8" t="s">
@@ -23512,7 +23518,7 @@
         <v>1962</v>
       </c>
       <c r="G560" s="9">
-        <f>(1+(F560-E560))-I560</f>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="H560" s="8" t="s">
@@ -23548,7 +23554,7 @@
         <v>1985</v>
       </c>
       <c r="G561" s="9">
-        <f>(1+(F561-E561))-I561</f>
+        <f t="shared" si="16"/>
         <v>62</v>
       </c>
       <c r="H561" s="8" t="s">
@@ -23584,7 +23590,7 @@
         <v>1994</v>
       </c>
       <c r="G562" s="9">
-        <f>(1+(F562-E562))-I562</f>
+        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="H562" s="8" t="s">
@@ -23620,7 +23626,7 @@
         <v>1935</v>
       </c>
       <c r="G563" s="9">
-        <f>(1+(F563-E563))-I563</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="H563" s="8" t="s">
@@ -23656,7 +23662,7 @@
         <v>1923</v>
       </c>
       <c r="G564" s="9">
-        <f>(1+(F564-E564))-I564</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="H564" s="8" t="s">
@@ -23692,7 +23698,7 @@
         <v>1875</v>
       </c>
       <c r="G565" s="9">
-        <f>(1+(F565-E565))-I565</f>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="H565" s="8" t="s">
@@ -23728,7 +23734,7 @@
         <v>1952</v>
       </c>
       <c r="G566" s="9">
-        <f>(1+(F566-E566))-I566</f>
+        <f t="shared" si="16"/>
         <v>24</v>
       </c>
       <c r="H566" s="8" t="s">
@@ -23764,7 +23770,7 @@
         <v>1953</v>
       </c>
       <c r="G567" s="9">
-        <f>(1+(F567-E567))-I567</f>
+        <f t="shared" si="16"/>
         <v>11</v>
       </c>
       <c r="H567" s="8" t="s">
@@ -23800,7 +23806,7 @@
         <v>1954</v>
       </c>
       <c r="G568" s="9">
-        <f>(1+(F568-E568))-I568</f>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="H568" s="8" t="s">
@@ -23836,7 +23842,7 @@
         <v>1907</v>
       </c>
       <c r="G569" s="9">
-        <f>(1+(F569-E569))-I569</f>
+        <f t="shared" si="16"/>
         <v>25</v>
       </c>
       <c r="H569" s="8" t="s">
@@ -23872,7 +23878,7 @@
         <v>1934</v>
       </c>
       <c r="G570" s="9">
-        <f>(1+(F570-E570))-I570</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="H570" s="8" t="s">
@@ -23908,7 +23914,7 @@
         <v>1924</v>
       </c>
       <c r="G571" s="9">
-        <f>(1+(F571-E571))-I571</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="H571" s="8" t="s">
@@ -23944,7 +23950,7 @@
         <v>1920</v>
       </c>
       <c r="G572" s="9">
-        <f>(1+(F572-E572))-I572</f>
+        <f t="shared" si="16"/>
         <v>7</v>
       </c>
       <c r="H572" s="8" t="s">
@@ -23980,7 +23986,7 @@
         <v>1980</v>
       </c>
       <c r="G573" s="9">
-        <f>(1+(F573-E573))-I573</f>
+        <f t="shared" si="16"/>
         <v>50</v>
       </c>
       <c r="H573" s="8" t="s">
@@ -24016,7 +24022,7 @@
         <v>1970</v>
       </c>
       <c r="G574" s="9">
-        <f>(1+(F574-E574))-I574</f>
+        <f t="shared" si="16"/>
         <v>33</v>
       </c>
       <c r="H574" s="8" t="s">
@@ -24052,7 +24058,7 @@
         <v>1954</v>
       </c>
       <c r="G575" s="9">
-        <f>(1+(F575-E575))-I575</f>
+        <f t="shared" si="16"/>
         <v>10</v>
       </c>
       <c r="H575" s="8" t="s">
@@ -24088,7 +24094,7 @@
         <v>1931</v>
       </c>
       <c r="G576" s="9">
-        <f>(1+(F576-E576))-I576</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="H576" s="8" t="s">
@@ -24124,7 +24130,7 @@
         <v>1968</v>
       </c>
       <c r="G577" s="9">
-        <f>(1+(F577-E577))-I577</f>
+        <f t="shared" si="16"/>
         <v>11</v>
       </c>
       <c r="H577" s="8" t="s">
@@ -24160,7 +24166,7 @@
         <v>1974</v>
       </c>
       <c r="G578" s="9">
-        <f>(1+(F578-E578))-I578</f>
+        <f t="shared" ref="G578:G609" si="17">(1+(F578-E578))-I578</f>
         <v>16</v>
       </c>
       <c r="H578" s="8" t="s">
@@ -24196,7 +24202,7 @@
         <v>1929</v>
       </c>
       <c r="G579" s="9">
-        <f>(1+(F579-E579))-I579</f>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="H579" s="8" t="s">
@@ -24232,7 +24238,7 @@
         <v>1976</v>
       </c>
       <c r="G580" s="9">
-        <f>(1+(F580-E580))-I580</f>
+        <f t="shared" si="17"/>
         <v>9</v>
       </c>
       <c r="H580" s="8" t="s">
@@ -24268,7 +24274,7 @@
         <v>1979</v>
       </c>
       <c r="G581" s="9">
-        <f>(1+(F581-E581))-I581</f>
+        <f t="shared" si="17"/>
         <v>22</v>
       </c>
       <c r="H581" s="8" t="s">
@@ -24304,7 +24310,7 @@
         <v>1964</v>
       </c>
       <c r="G582" s="9">
-        <f>(1+(F582-E582))-I582</f>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="H582" s="8" t="s">
@@ -24340,7 +24346,7 @@
         <v>1960</v>
       </c>
       <c r="G583" s="9">
-        <f>(1+(F583-E583))-I583</f>
+        <f t="shared" si="17"/>
         <v>10</v>
       </c>
       <c r="H583" s="8" t="s">
@@ -24376,7 +24382,7 @@
         <v>1943</v>
       </c>
       <c r="G584" s="9">
-        <f>(1+(F584-E584))-I584</f>
+        <f t="shared" si="17"/>
         <v>11</v>
       </c>
       <c r="H584" s="8" t="s">
@@ -24412,7 +24418,7 @@
         <v>1889</v>
       </c>
       <c r="G585" s="9">
-        <f>(1+(F585-E585))-I585</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H585" s="8" t="s">
@@ -24448,7 +24454,7 @@
         <v>1852</v>
       </c>
       <c r="G586" s="9">
-        <f>(1+(F586-E586))-I586</f>
+        <f t="shared" si="17"/>
         <v>0.42000000000000004</v>
       </c>
       <c r="H586" s="8" t="s">
@@ -24484,7 +24490,7 @@
         <v>1970</v>
       </c>
       <c r="G587" s="9">
-        <f>(1+(F587-E587))-I587</f>
+        <f t="shared" si="17"/>
         <v>26</v>
       </c>
       <c r="H587" s="8" t="s">
@@ -24520,7 +24526,7 @@
         <v>1968</v>
       </c>
       <c r="G588" s="9">
-        <f>(1+(F588-E588))-I588</f>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="H588" s="8" t="s">
@@ -24556,7 +24562,7 @@
         <v>1908</v>
       </c>
       <c r="G589" s="9">
-        <f>(1+(F589-E589))-I589</f>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="H589" s="8" t="s">
@@ -24592,7 +24598,7 @@
         <v>1885</v>
       </c>
       <c r="G590" s="9">
-        <f>(1+(F590-E590))-I590</f>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="H590" s="8" t="s">
@@ -24628,7 +24634,7 @@
         <v>1950</v>
       </c>
       <c r="G591" s="9">
-        <f>(1+(F591-E591))-I591</f>
+        <f t="shared" si="17"/>
         <v>9</v>
       </c>
       <c r="H591" s="8" t="s">
@@ -24664,7 +24670,7 @@
         <v>1929</v>
       </c>
       <c r="G592" s="9">
-        <f>(1+(F592-E592))-I592</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H592" s="8" t="s">
@@ -24700,7 +24706,7 @@
         <v>1938</v>
       </c>
       <c r="G593" s="9">
-        <f>(1+(F593-E593))-I593</f>
+        <f t="shared" si="17"/>
         <v>6</v>
       </c>
       <c r="H593" s="8" t="s">
@@ -24736,7 +24742,7 @@
         <v>1868</v>
       </c>
       <c r="G594" s="9">
-        <f>(1+(F594-E594))-I594</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H594" s="8" t="s">
@@ -24772,7 +24778,7 @@
         <v>1905</v>
       </c>
       <c r="G595" s="9">
-        <f>(1+(F595-E595))-I595</f>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="H595" s="8" t="s">
@@ -24808,7 +24814,7 @@
         <v>1937</v>
       </c>
       <c r="G596" s="9">
-        <f>(1+(F596-E596))-I596</f>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="H596" s="8" t="s">
@@ -24844,7 +24850,7 @@
         <v>1869</v>
       </c>
       <c r="G597" s="9">
-        <f>(1+(F597-E597))-I597</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H597" s="8" t="s">
@@ -24880,7 +24886,7 @@
         <v>1943</v>
       </c>
       <c r="G598" s="9">
-        <f>(1+(F598-E598))-I598</f>
+        <f t="shared" si="17"/>
         <v>17</v>
       </c>
       <c r="H598" s="8">
@@ -24916,7 +24922,7 @@
         <v>1944</v>
       </c>
       <c r="G599" s="9">
-        <f>(1+(F599-E599))-I599</f>
+        <f t="shared" si="17"/>
         <v>15</v>
       </c>
       <c r="H599" s="8" t="s">
@@ -24952,7 +24958,7 @@
         <v>1930</v>
       </c>
       <c r="G600" s="9">
-        <f>(1+(F600-E600))-I600</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H600" s="8" t="s">
@@ -24988,7 +24994,7 @@
         <v>1866</v>
       </c>
       <c r="G601" s="9">
-        <f>(1+(F601-E601))-I601</f>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="H601" s="8" t="s">
@@ -25024,7 +25030,7 @@
         <v>1863</v>
       </c>
       <c r="G602" s="9">
-        <f>(1+(F602-E602))-I602</f>
+        <f t="shared" si="17"/>
         <v>3</v>
       </c>
       <c r="H602" s="8" t="s">
@@ -25060,7 +25066,7 @@
         <v>1898</v>
       </c>
       <c r="G603" s="9">
-        <f>(1+(F603-E603))-I603</f>
+        <f t="shared" si="17"/>
         <v>6</v>
       </c>
       <c r="H603" s="8" t="s">
@@ -25096,7 +25102,7 @@
         <v>1925</v>
       </c>
       <c r="G604" s="9">
-        <f>(1+(F604-E604))-I604</f>
+        <f t="shared" si="17"/>
         <v>5</v>
       </c>
       <c r="H604" s="8" t="s">
@@ -25132,7 +25138,7 @@
         <v>1862</v>
       </c>
       <c r="G605" s="9">
-        <f>(1+(F605-E605))-I605</f>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="H605" s="8" t="s">
@@ -25168,7 +25174,7 @@
         <v>1867</v>
       </c>
       <c r="G606" s="9">
-        <f>(1+(F606-E606))-I606</f>
+        <f t="shared" si="17"/>
         <v>6</v>
       </c>
       <c r="H606" s="8">
@@ -25204,7 +25210,7 @@
         <v>1898</v>
       </c>
       <c r="G607" s="9">
-        <f>(1+(F607-E607))-I607</f>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="H607" s="8">
@@ -25240,7 +25246,7 @@
         <v>1868</v>
       </c>
       <c r="G608" s="9">
-        <f>(1+(F608-E608))-I608</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H608" s="8" t="s">
@@ -25276,7 +25282,7 @@
         <v>1937</v>
       </c>
       <c r="G609" s="9">
-        <f>(1+(F609-E609))-I609</f>
+        <f t="shared" si="17"/>
         <v>7</v>
       </c>
       <c r="H609" s="8" t="s">
@@ -25312,7 +25318,7 @@
         <v>1936</v>
       </c>
       <c r="G610" s="9">
-        <f>(1+(F610-E610))-I610</f>
+        <f t="shared" ref="G610:G641" si="18">(1+(F610-E610))-I610</f>
         <v>12</v>
       </c>
       <c r="H610" s="8" t="s">
@@ -25348,7 +25354,7 @@
         <v>1929</v>
       </c>
       <c r="G611" s="9">
-        <f>(1+(F611-E611))-I611</f>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="H611" s="8" t="s">
@@ -25384,7 +25390,7 @@
         <v>1874</v>
       </c>
       <c r="G612" s="9">
-        <f>(1+(F612-E612))-I612</f>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="H612" s="8" t="s">
@@ -25420,7 +25426,7 @@
         <v>1950</v>
       </c>
       <c r="G613" s="9">
-        <f>(1+(F613-E613))-I613</f>
+        <f t="shared" si="18"/>
         <v>11</v>
       </c>
       <c r="H613" s="8" t="s">
@@ -25456,7 +25462,7 @@
         <v>1933</v>
       </c>
       <c r="G614" s="9">
-        <f>(1+(F614-E614))-I614</f>
+        <f t="shared" si="18"/>
         <v>11</v>
       </c>
       <c r="H614" s="8" t="s">
@@ -25492,7 +25498,7 @@
         <v>1925</v>
       </c>
       <c r="G615" s="9">
-        <f>(1+(F615-E615))-I615</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H615" s="8" t="s">
@@ -25528,7 +25534,7 @@
         <v>1937</v>
       </c>
       <c r="G616" s="9">
-        <f>(1+(F616-E616))-I616</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="H616" s="8" t="s">
@@ -25564,7 +25570,7 @@
         <v>1950</v>
       </c>
       <c r="G617" s="9">
-        <f>(1+(F617-E617))-I617</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="H617" s="8" t="s">
@@ -25600,7 +25606,7 @@
         <v>1909</v>
       </c>
       <c r="G618" s="9">
-        <f>(1+(F618-E618))-I618</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H618" s="8" t="s">
@@ -25636,7 +25642,7 @@
         <v>1930</v>
       </c>
       <c r="G619" s="9">
-        <f>(1+(F619-E619))-I619</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H619" s="8" t="s">
@@ -25672,7 +25678,7 @@
         <v>1936</v>
       </c>
       <c r="G620" s="9">
-        <f>(1+(F620-E620))-I620</f>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="H620" s="8" t="s">
@@ -25708,7 +25714,7 @@
         <v>1944</v>
       </c>
       <c r="G621" s="9">
-        <f>(1+(F621-E621))-I621</f>
+        <f t="shared" si="18"/>
         <v>18</v>
       </c>
       <c r="H621" s="8" t="s">
@@ -25744,7 +25750,7 @@
         <v>1908</v>
       </c>
       <c r="G622" s="9">
-        <f>(1+(F622-E622))-I622</f>
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
       <c r="H622" s="8" t="s">
@@ -25780,7 +25786,7 @@
         <v>1949</v>
       </c>
       <c r="G623" s="9">
-        <f>(1+(F623-E623))-I623</f>
+        <f t="shared" si="18"/>
         <v>21</v>
       </c>
       <c r="H623" s="8" t="s">
@@ -25816,7 +25822,7 @@
         <v>1930</v>
       </c>
       <c r="G624" s="9">
-        <f>(1+(F624-E624))-I624</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H624" s="8" t="s">
@@ -25852,7 +25858,7 @@
         <v>1902</v>
       </c>
       <c r="G625" s="9">
-        <f>(1+(F625-E625))-I625</f>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="H625" s="8" t="s">
@@ -25888,7 +25894,7 @@
         <v>1913</v>
       </c>
       <c r="G626" s="9">
-        <f>(1+(F626-E626))-I626</f>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="H626" s="8" t="s">
@@ -25924,7 +25930,7 @@
         <v>1902</v>
       </c>
       <c r="G627" s="9">
-        <f>(1+(F627-E627))-I627</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H627" s="8" t="s">
@@ -25960,7 +25966,7 @@
         <v>1938</v>
       </c>
       <c r="G628" s="9">
-        <f>(1+(F628-E628))-I628</f>
+        <f t="shared" si="18"/>
         <v>11</v>
       </c>
       <c r="H628" s="8" t="s">
@@ -25996,7 +26002,7 @@
         <v>1926</v>
       </c>
       <c r="G629" s="9">
-        <f>(1+(F629-E629))-I629</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H629" s="8" t="s">
@@ -26032,7 +26038,7 @@
         <v>1944</v>
       </c>
       <c r="G630" s="9">
-        <f>(1+(F630-E630))-I630</f>
+        <f t="shared" si="18"/>
         <v>15</v>
       </c>
       <c r="H630" s="8" t="s">
@@ -26068,7 +26074,7 @@
         <v>1926</v>
       </c>
       <c r="G631" s="9">
-        <f>(1+(F631-E631))-I631</f>
+        <f t="shared" si="18"/>
         <v>8</v>
       </c>
       <c r="H631" s="8" t="s">

--- a/Undigitised_Records.xlsx
+++ b/Undigitised_Records.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sotonac-my.sharepoint.com/personal/ck1g20_soton_ac_uk/Documents/Documents/PhD/20_Historical_record_catalogue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="338" documentId="8_{2EBFFBB5-AA1D-4DD9-A43A-243907206CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8FBCDB3-144D-4813-A1C6-BBF44877CCDB}"/>
+  <xr:revisionPtr revIDLastSave="339" documentId="8_{2EBFFBB5-AA1D-4DD9-A43A-243907206CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F70B046-14D9-49F0-9D4D-B051C299B247}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B145EA35-1BD5-495C-A7E0-BAB6ECA9BC95}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3169" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3169" uniqueCount="823">
   <si>
     <t>Rough location</t>
   </si>
@@ -2337,9 +2337,6 @@
   </si>
   <si>
     <t>Quai Nord</t>
-  </si>
-  <si>
-    <t>Marirgams</t>
   </si>
   <si>
     <t>Walvis Bay</t>
@@ -3030,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>7</v>
@@ -3047,7 +3044,7 @@
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>259</v>
@@ -3075,10 +3072,10 @@
         <v>30</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3111,10 +3108,10 @@
         <v>0</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3147,10 +3144,10 @@
         <v>0</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3183,10 +3180,10 @@
         <v>3</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3219,10 +3216,10 @@
         <v>0</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3255,10 +3252,10 @@
         <v>0</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3275,25 +3272,25 @@
         <v>-62.100169999999999</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G8" s="9">
         <v>10</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3326,10 +3323,10 @@
         <v>0</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3362,10 +3359,10 @@
         <v>66</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3398,10 +3395,10 @@
         <v>69</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3434,10 +3431,10 @@
         <v>3</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3470,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3506,10 +3503,10 @@
         <v>28</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3526,25 +3523,25 @@
         <v>-88.185248999999999</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3577,10 +3574,10 @@
         <v>0</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="17" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3613,10 +3610,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="18" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3649,10 +3646,10 @@
         <v>4</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="19" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -3685,10 +3682,10 @@
         <v>0</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
@@ -3721,15 +3718,15 @@
         <v>0</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>306</v>
@@ -3757,10 +3754,10 @@
         <v>6</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
@@ -3793,10 +3790,10 @@
         <v>15</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N22" s="12"/>
     </row>
@@ -3830,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N23" s="13"/>
     </row>
@@ -3867,10 +3864,10 @@
         <v>9</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N24" s="13"/>
     </row>
@@ -3904,10 +3901,10 @@
         <v>0</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N25" s="14"/>
     </row>
@@ -3941,10 +3938,10 @@
         <v>15</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N26" s="14"/>
     </row>
@@ -3978,10 +3975,10 @@
         <v>9</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N27" s="14"/>
     </row>
@@ -4015,10 +4012,10 @@
         <v>36</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N28" s="14"/>
     </row>
@@ -4052,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N29" s="14"/>
     </row>
@@ -4089,16 +4086,16 @@
         <v>10</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N30" s="14"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>453</v>
@@ -4126,16 +4123,16 @@
         <v>0</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N31" s="14"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>453</v>
@@ -4163,16 +4160,16 @@
         <v>0</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N32" s="14"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>453</v>
@@ -4200,10 +4197,10 @@
         <v>0</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N33" s="14"/>
     </row>
@@ -4237,10 +4234,10 @@
         <v>26</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N34" s="14"/>
     </row>
@@ -4274,10 +4271,10 @@
         <v>0</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N35" s="14"/>
     </row>
@@ -4311,10 +4308,10 @@
         <v>0</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K36" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N36" s="14"/>
     </row>
@@ -4348,10 +4345,10 @@
         <v>18</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K37" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N37" s="14"/>
     </row>
@@ -4385,10 +4382,10 @@
         <v>15</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N38" s="14"/>
     </row>
@@ -4422,10 +4419,10 @@
         <v>0</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N39" s="14"/>
     </row>
@@ -4459,10 +4456,10 @@
         <v>116</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N40" s="14"/>
     </row>
@@ -4496,10 +4493,10 @@
         <v>114</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K41" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N41" s="14"/>
     </row>
@@ -4533,10 +4530,10 @@
         <v>0</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N42" s="14"/>
     </row>
@@ -4570,10 +4567,10 @@
         <v>0</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N43" s="14"/>
     </row>
@@ -4607,10 +4604,10 @@
         <v>0</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K44" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N44" s="14"/>
     </row>
@@ -4644,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K45" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N45" s="14"/>
     </row>
@@ -4681,10 +4678,10 @@
         <v>0</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K46" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N46" s="14"/>
     </row>
@@ -4718,10 +4715,10 @@
         <v>0</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K47" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N47" s="14"/>
     </row>
@@ -4755,10 +4752,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K48" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N48" s="14"/>
     </row>
@@ -4792,10 +4789,10 @@
         <v>0</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K49" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N49" s="14"/>
     </row>
@@ -4829,10 +4826,10 @@
         <v>0</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N50" s="14"/>
     </row>
@@ -4866,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K51" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N51" s="14"/>
     </row>
@@ -4903,10 +4900,10 @@
         <v>0</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K52" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N52" s="14"/>
     </row>
@@ -4940,10 +4937,10 @@
         <v>0</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K53" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N53" s="14"/>
     </row>
@@ -4977,10 +4974,10 @@
         <v>0</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K54" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N54" s="14"/>
     </row>
@@ -5014,10 +5011,10 @@
         <v>0</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K55" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N55" s="14"/>
     </row>
@@ -5051,10 +5048,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K56" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N56" s="14"/>
     </row>
@@ -5088,10 +5085,10 @@
         <v>29</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K57" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N57" s="14"/>
     </row>
@@ -5125,10 +5122,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K58" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N58" s="14"/>
     </row>
@@ -5163,10 +5160,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K59" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N59" s="14"/>
     </row>
@@ -5200,10 +5197,10 @@
         <v>0</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K60" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N60" s="14"/>
     </row>
@@ -5237,10 +5234,10 @@
         <v>0</v>
       </c>
       <c r="J61" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K61" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N61" s="14"/>
     </row>
@@ -5274,10 +5271,10 @@
         <v>0</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K62" s="12" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="N62" s="14"/>
     </row>
@@ -5311,10 +5308,10 @@
         <v>20</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K63" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N63" s="14"/>
     </row>
@@ -5349,10 +5346,10 @@
         <v>135</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K64" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N64" s="14"/>
     </row>
@@ -5386,10 +5383,10 @@
         <v>0</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K65" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N65" s="14"/>
     </row>
@@ -5424,10 +5421,10 @@
         <v>54</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K66" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N66" s="14"/>
     </row>
@@ -5461,10 +5458,10 @@
         <v>42</v>
       </c>
       <c r="J67" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K67" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N67" s="14"/>
     </row>
@@ -5498,10 +5495,10 @@
         <v>0</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K68" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N68" s="14"/>
     </row>
@@ -5535,10 +5532,10 @@
         <v>0</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K69" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N69" s="14"/>
     </row>
@@ -5573,10 +5570,10 @@
         <v>110</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K70" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N70" s="14"/>
     </row>
@@ -5611,10 +5608,10 @@
         <v>50</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K71" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N71" s="14"/>
     </row>
@@ -5648,10 +5645,10 @@
         <v>0</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K72" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N72" s="14"/>
     </row>
@@ -5685,10 +5682,10 @@
         <v>37</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K73" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N73" s="14"/>
     </row>
@@ -5722,10 +5719,10 @@
         <v>6</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K74" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N74" s="14"/>
     </row>
@@ -5759,10 +5756,10 @@
         <v>40</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K75" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N75" s="14"/>
     </row>
@@ -5796,10 +5793,10 @@
         <v>0</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K76" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N76" s="14"/>
     </row>
@@ -5833,10 +5830,10 @@
         <v>189</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K77" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N77" s="14"/>
     </row>
@@ -5870,16 +5867,16 @@
         <v>0</v>
       </c>
       <c r="J78" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K78" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N78" s="14"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B79" s="11" t="s">
         <v>33</v>
@@ -5907,16 +5904,16 @@
         <v>0</v>
       </c>
       <c r="J79" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K79" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N79" s="14"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="11" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>33</v>
@@ -5944,10 +5941,10 @@
         <v>0</v>
       </c>
       <c r="J80" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K80" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N80" s="14"/>
     </row>
@@ -5981,10 +5978,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K81" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N81" s="14"/>
     </row>
@@ -6018,10 +6015,10 @@
         <v>1</v>
       </c>
       <c r="J82" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K82" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N82" s="14"/>
     </row>
@@ -6055,10 +6052,10 @@
         <v>0</v>
       </c>
       <c r="J83" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K83" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N83" s="14"/>
     </row>
@@ -6092,10 +6089,10 @@
         <v>83</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K84" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N84" s="14"/>
     </row>
@@ -6129,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="J85" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K85" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N85" s="14"/>
     </row>
@@ -6166,10 +6163,10 @@
         <v>0</v>
       </c>
       <c r="J86" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K86" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N86" s="14"/>
     </row>
@@ -6203,10 +6200,10 @@
         <v>0</v>
       </c>
       <c r="J87" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K87" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N87" s="14"/>
     </row>
@@ -6240,10 +6237,10 @@
         <v>0</v>
       </c>
       <c r="J88" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K88" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N88" s="14"/>
     </row>
@@ -6277,10 +6274,10 @@
         <v>9</v>
       </c>
       <c r="J89" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K89" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N89" s="14"/>
     </row>
@@ -6314,10 +6311,10 @@
         <v>102</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K90" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N90" s="14"/>
     </row>
@@ -6351,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K91" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N91" s="14"/>
     </row>
@@ -6388,10 +6385,10 @@
         <v>0</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K92" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N92" s="14"/>
     </row>
@@ -6425,10 +6422,10 @@
         <v>0</v>
       </c>
       <c r="J93" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K93" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N93" s="14"/>
     </row>
@@ -6462,10 +6459,10 @@
         <v>0</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K94" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N94" s="14"/>
     </row>
@@ -6499,10 +6496,10 @@
         <v>0</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K95" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N95" s="14"/>
     </row>
@@ -6536,10 +6533,10 @@
         <v>0</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K96" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N96" s="14"/>
     </row>
@@ -6573,10 +6570,10 @@
         <v>0</v>
       </c>
       <c r="J97" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K97" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N97" s="14"/>
     </row>
@@ -6610,10 +6607,10 @@
         <v>0</v>
       </c>
       <c r="J98" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K98" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N98" s="14"/>
     </row>
@@ -6647,10 +6644,10 @@
         <v>90</v>
       </c>
       <c r="J99" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K99" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N99" s="14"/>
     </row>
@@ -6684,10 +6681,10 @@
         <v>2</v>
       </c>
       <c r="J100" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K100" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N100" s="14"/>
     </row>
@@ -6721,10 +6718,10 @@
         <v>0</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K101" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N101" s="14"/>
     </row>
@@ -6758,10 +6755,10 @@
         <v>0</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K102" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N102" s="14"/>
     </row>
@@ -6795,16 +6792,16 @@
         <v>0</v>
       </c>
       <c r="J103" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K103" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N103" s="14"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" s="11" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>33</v>
@@ -6832,16 +6829,16 @@
         <v>5</v>
       </c>
       <c r="J104" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K104" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N104" s="14"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" s="11" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>33</v>
@@ -6869,16 +6866,16 @@
         <v>51</v>
       </c>
       <c r="J105" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K105" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N105" s="14"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" s="11" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>33</v>
@@ -6906,10 +6903,10 @@
         <v>0</v>
       </c>
       <c r="J106" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K106" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N106" s="14"/>
     </row>
@@ -6943,10 +6940,10 @@
         <v>0</v>
       </c>
       <c r="J107" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K107" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N107" s="14"/>
     </row>
@@ -6980,10 +6977,10 @@
         <v>0</v>
       </c>
       <c r="J108" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K108" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N108" s="14"/>
     </row>
@@ -7017,10 +7014,10 @@
         <v>0</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K109" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N109" s="14"/>
     </row>
@@ -7054,10 +7051,10 @@
         <v>3</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K110" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N110" s="14"/>
     </row>
@@ -7091,10 +7088,10 @@
         <v>0</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K111" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N111" s="14"/>
     </row>
@@ -7128,10 +7125,10 @@
         <v>35</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K112" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N112" s="14"/>
     </row>
@@ -7165,10 +7162,10 @@
         <v>3</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K113" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N113" s="14"/>
     </row>
@@ -7202,10 +7199,10 @@
         <v>0</v>
       </c>
       <c r="J114" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K114" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N114" s="14"/>
     </row>
@@ -7239,10 +7236,10 @@
         <v>0</v>
       </c>
       <c r="J115" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K115" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N115" s="14"/>
     </row>
@@ -7276,10 +7273,10 @@
         <v>91</v>
       </c>
       <c r="J116" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K116" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N116" s="14"/>
     </row>
@@ -7313,10 +7310,10 @@
         <v>0</v>
       </c>
       <c r="J117" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K117" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N117" s="14"/>
     </row>
@@ -7350,10 +7347,10 @@
         <v>91</v>
       </c>
       <c r="J118" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K118" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N118" s="14"/>
     </row>
@@ -7387,10 +7384,10 @@
         <v>0</v>
       </c>
       <c r="J119" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K119" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N119" s="14"/>
     </row>
@@ -7424,10 +7421,10 @@
         <v>0</v>
       </c>
       <c r="J120" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K120" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N120" s="14"/>
     </row>
@@ -7461,10 +7458,10 @@
         <v>1</v>
       </c>
       <c r="J121" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K121" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N121" s="14"/>
     </row>
@@ -7498,10 +7495,10 @@
         <v>112</v>
       </c>
       <c r="J122" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K122" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N122" s="14"/>
     </row>
@@ -7535,10 +7532,10 @@
         <v>0</v>
       </c>
       <c r="J123" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K123" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N123" s="14"/>
     </row>
@@ -7572,10 +7569,10 @@
         <v>0</v>
       </c>
       <c r="J124" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K124" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N124" s="14"/>
     </row>
@@ -7609,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="J125" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K125" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N125" s="14"/>
     </row>
@@ -7646,10 +7643,10 @@
         <v>113</v>
       </c>
       <c r="J126" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K126" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N126" s="14"/>
     </row>
@@ -7683,10 +7680,10 @@
         <v>0</v>
       </c>
       <c r="J127" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K127" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N127" s="14"/>
     </row>
@@ -7720,10 +7717,10 @@
         <v>0</v>
       </c>
       <c r="J128" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K128" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N128" s="14"/>
     </row>
@@ -7757,10 +7754,10 @@
         <v>54</v>
       </c>
       <c r="J129" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K129" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N129" s="14"/>
     </row>
@@ -7794,10 +7791,10 @@
         <v>9</v>
       </c>
       <c r="J130" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K130" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N130" s="14"/>
     </row>
@@ -7831,10 +7828,10 @@
         <v>1</v>
       </c>
       <c r="J131" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K131" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N131" s="14"/>
     </row>
@@ -7868,10 +7865,10 @@
         <v>0</v>
       </c>
       <c r="J132" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K132" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N132" s="14"/>
     </row>
@@ -7905,10 +7902,10 @@
         <v>0</v>
       </c>
       <c r="J133" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K133" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N133" s="14"/>
     </row>
@@ -7942,10 +7939,10 @@
         <v>0</v>
       </c>
       <c r="J134" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K134" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N134" s="14"/>
     </row>
@@ -7979,10 +7976,10 @@
         <v>84</v>
       </c>
       <c r="J135" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K135" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N135" s="14"/>
     </row>
@@ -8016,10 +8013,10 @@
         <v>0</v>
       </c>
       <c r="J136" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K136" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N136" s="14"/>
     </row>
@@ -8053,10 +8050,10 @@
         <v>0</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K137" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N137" s="14"/>
     </row>
@@ -8090,10 +8087,10 @@
         <v>221</v>
       </c>
       <c r="J138" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K138" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N138" s="14"/>
     </row>
@@ -8127,10 +8124,10 @@
         <v>0</v>
       </c>
       <c r="J139" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K139" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N139" s="14"/>
     </row>
@@ -8164,10 +8161,10 @@
         <v>0</v>
       </c>
       <c r="J140" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K140" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N140" s="14"/>
     </row>
@@ -8201,10 +8198,10 @@
         <v>0</v>
       </c>
       <c r="J141" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K141" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N141" s="14"/>
     </row>
@@ -8238,10 +8235,10 @@
         <v>0</v>
       </c>
       <c r="J142" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K142" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N142" s="14"/>
     </row>
@@ -8275,10 +8272,10 @@
         <v>28</v>
       </c>
       <c r="J143" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K143" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N143" s="14"/>
     </row>
@@ -8312,10 +8309,10 @@
         <v>0</v>
       </c>
       <c r="J144" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K144" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N144" s="14"/>
     </row>
@@ -8349,10 +8346,10 @@
         <v>56</v>
       </c>
       <c r="J145" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K145" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N145" s="14"/>
     </row>
@@ -8386,10 +8383,10 @@
         <v>56</v>
       </c>
       <c r="J146" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K146" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N146" s="14"/>
     </row>
@@ -8423,10 +8420,10 @@
         <v>88</v>
       </c>
       <c r="J147" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K147" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N147" s="14"/>
     </row>
@@ -8460,10 +8457,10 @@
         <v>0</v>
       </c>
       <c r="J148" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K148" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N148" s="14"/>
     </row>
@@ -8497,10 +8494,10 @@
         <v>141</v>
       </c>
       <c r="J149" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K149" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N149" s="14"/>
     </row>
@@ -8534,10 +8531,10 @@
         <v>0</v>
       </c>
       <c r="J150" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K150" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N150" s="14"/>
     </row>
@@ -8571,16 +8568,16 @@
         <v>0</v>
       </c>
       <c r="J151" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K151" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N151" s="14"/>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A152" s="11" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B152" s="11" t="s">
         <v>33</v>
@@ -8608,10 +8605,10 @@
         <v>0</v>
       </c>
       <c r="J152" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K152" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N152" s="14"/>
     </row>
@@ -8645,10 +8642,10 @@
         <v>3</v>
       </c>
       <c r="J153" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K153" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N153" s="14"/>
     </row>
@@ -8682,10 +8679,10 @@
         <v>1</v>
       </c>
       <c r="J154" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K154" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N154" s="14"/>
     </row>
@@ -8719,10 +8716,10 @@
         <v>20</v>
       </c>
       <c r="J155" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K155" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N155" s="14"/>
     </row>
@@ -8756,10 +8753,10 @@
         <v>20</v>
       </c>
       <c r="J156" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K156" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N156" s="14"/>
     </row>
@@ -8793,10 +8790,10 @@
         <v>0</v>
       </c>
       <c r="J157" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K157" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N157" s="14"/>
     </row>
@@ -8830,10 +8827,10 @@
         <v>16</v>
       </c>
       <c r="J158" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K158" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N158" s="14"/>
     </row>
@@ -8867,10 +8864,10 @@
         <v>0</v>
       </c>
       <c r="J159" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K159" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N159" s="14"/>
     </row>
@@ -8904,10 +8901,10 @@
         <v>0</v>
       </c>
       <c r="J160" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K160" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N160" s="14"/>
     </row>
@@ -8941,10 +8938,10 @@
         <v>0</v>
       </c>
       <c r="J161" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K161" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N161" s="14"/>
     </row>
@@ -8978,10 +8975,10 @@
         <v>0</v>
       </c>
       <c r="J162" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K162" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N162" s="14"/>
     </row>
@@ -9015,10 +9012,10 @@
         <v>48</v>
       </c>
       <c r="J163" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K163" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N163" s="14"/>
     </row>
@@ -9052,10 +9049,10 @@
         <v>84</v>
       </c>
       <c r="J164" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K164" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N164" s="14"/>
     </row>
@@ -9089,10 +9086,10 @@
         <v>0</v>
       </c>
       <c r="J165" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K165" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N165" s="14"/>
     </row>
@@ -9126,10 +9123,10 @@
         <v>0</v>
       </c>
       <c r="J166" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K166" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N166" s="14"/>
     </row>
@@ -9163,10 +9160,10 @@
         <v>3</v>
       </c>
       <c r="J167" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K167" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N167" s="14"/>
     </row>
@@ -9200,10 +9197,10 @@
         <v>0</v>
       </c>
       <c r="J168" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K168" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N168" s="14"/>
     </row>
@@ -9237,10 +9234,10 @@
         <v>0</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K169" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N169" s="14"/>
     </row>
@@ -9274,10 +9271,10 @@
         <v>0</v>
       </c>
       <c r="J170" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K170" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N170" s="14"/>
     </row>
@@ -9311,10 +9308,10 @@
         <v>104</v>
       </c>
       <c r="J171" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K171" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N171" s="14"/>
     </row>
@@ -9348,10 +9345,10 @@
         <v>13</v>
       </c>
       <c r="J172" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K172" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N172" s="14"/>
     </row>
@@ -9385,10 +9382,10 @@
         <v>22</v>
       </c>
       <c r="J173" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K173" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N173" s="14"/>
     </row>
@@ -9422,10 +9419,10 @@
         <v>0</v>
       </c>
       <c r="J174" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K174" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N174" s="14"/>
     </row>
@@ -9459,10 +9456,10 @@
         <v>0</v>
       </c>
       <c r="J175" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K175" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N175" s="14"/>
     </row>
@@ -9496,10 +9493,10 @@
         <v>66</v>
       </c>
       <c r="J176" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K176" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N176" s="14"/>
     </row>
@@ -9533,10 +9530,10 @@
         <v>0</v>
       </c>
       <c r="J177" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K177" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N177" s="14"/>
     </row>
@@ -9570,10 +9567,10 @@
         <v>17</v>
       </c>
       <c r="J178" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K178" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N178" s="14"/>
     </row>
@@ -9607,10 +9604,10 @@
         <v>48</v>
       </c>
       <c r="J179" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K179" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N179" s="14"/>
     </row>
@@ -9644,10 +9641,10 @@
         <v>11</v>
       </c>
       <c r="J180" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K180" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N180" s="14"/>
     </row>
@@ -9681,10 +9678,10 @@
         <v>22</v>
       </c>
       <c r="J181" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K181" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N181" s="14"/>
     </row>
@@ -9718,10 +9715,10 @@
         <v>76</v>
       </c>
       <c r="J182" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K182" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N182" s="14"/>
     </row>
@@ -9755,10 +9752,10 @@
         <v>17</v>
       </c>
       <c r="J183" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K183" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N183" s="14"/>
     </row>
@@ -9792,10 +9789,10 @@
         <v>89</v>
       </c>
       <c r="J184" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K184" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N184" s="14"/>
     </row>
@@ -9829,10 +9826,10 @@
         <v>104</v>
       </c>
       <c r="J185" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K185" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N185" s="14"/>
     </row>
@@ -9866,10 +9863,10 @@
         <v>0</v>
       </c>
       <c r="J186" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K186" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N186" s="14"/>
     </row>
@@ -9903,10 +9900,10 @@
         <v>102</v>
       </c>
       <c r="J187" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K187" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N187" s="14"/>
     </row>
@@ -9940,10 +9937,10 @@
         <v>74</v>
       </c>
       <c r="J188" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K188" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N188" s="14"/>
     </row>
@@ -9977,10 +9974,10 @@
         <v>0</v>
       </c>
       <c r="J189" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K189" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N189" s="14"/>
     </row>
@@ -10014,10 +10011,10 @@
         <v>0</v>
       </c>
       <c r="J190" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K190" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N190" s="14"/>
     </row>
@@ -10051,10 +10048,10 @@
         <v>0</v>
       </c>
       <c r="J191" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K191" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N191" s="14"/>
     </row>
@@ -10088,10 +10085,10 @@
         <v>128</v>
       </c>
       <c r="J192" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K192" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N192" s="14"/>
     </row>
@@ -10125,10 +10122,10 @@
         <v>0</v>
       </c>
       <c r="J193" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K193" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N193" s="14"/>
     </row>
@@ -10162,10 +10159,10 @@
         <v>135</v>
       </c>
       <c r="J194" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K194" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N194" s="14"/>
     </row>
@@ -10199,10 +10196,10 @@
         <v>0</v>
       </c>
       <c r="J195" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K195" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N195" s="14"/>
     </row>
@@ -10236,10 +10233,10 @@
         <v>0</v>
       </c>
       <c r="J196" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K196" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N196" s="14"/>
     </row>
@@ -10273,10 +10270,10 @@
         <v>0</v>
       </c>
       <c r="J197" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K197" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N197" s="14"/>
     </row>
@@ -10310,10 +10307,10 @@
         <v>54</v>
       </c>
       <c r="J198" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K198" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N198" s="14"/>
     </row>
@@ -10347,10 +10344,10 @@
         <v>0</v>
       </c>
       <c r="J199" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K199" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N199" s="14"/>
     </row>
@@ -10384,10 +10381,10 @@
         <v>0</v>
       </c>
       <c r="J200" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K200" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N200" s="14"/>
     </row>
@@ -10421,10 +10418,10 @@
         <v>0</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K201" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N201" s="14"/>
     </row>
@@ -10458,10 +10455,10 @@
         <v>0</v>
       </c>
       <c r="J202" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K202" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N202" s="14"/>
     </row>
@@ -10495,10 +10492,10 @@
         <v>59</v>
       </c>
       <c r="J203" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K203" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N203" s="14"/>
     </row>
@@ -10532,10 +10529,10 @@
         <v>0</v>
       </c>
       <c r="J204" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K204" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N204" s="14"/>
     </row>
@@ -10569,10 +10566,10 @@
         <v>0</v>
       </c>
       <c r="J205" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K205" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N205" s="14"/>
     </row>
@@ -10606,10 +10603,10 @@
         <v>150</v>
       </c>
       <c r="J206" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K206" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N206" s="14"/>
     </row>
@@ -10643,10 +10640,10 @@
         <v>0</v>
       </c>
       <c r="J207" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K207" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N207" s="14"/>
     </row>
@@ -10680,10 +10677,10 @@
         <v>0</v>
       </c>
       <c r="J208" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K208" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N208" s="14"/>
     </row>
@@ -10717,10 +10714,10 @@
         <v>0</v>
       </c>
       <c r="J209" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K209" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N209" s="14"/>
     </row>
@@ -10754,10 +10751,10 @@
         <v>57</v>
       </c>
       <c r="J210" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K210" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N210" s="14"/>
     </row>
@@ -10791,10 +10788,10 @@
         <v>3</v>
       </c>
       <c r="J211" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K211" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N211" s="14"/>
     </row>
@@ -10828,10 +10825,10 @@
         <v>0</v>
       </c>
       <c r="J212" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K212" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N212" s="14"/>
     </row>
@@ -10865,10 +10862,10 @@
         <v>2</v>
       </c>
       <c r="J213" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K213" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N213" s="14"/>
     </row>
@@ -10902,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="J214" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K214" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N214" s="14"/>
     </row>
@@ -10939,10 +10936,10 @@
         <v>156</v>
       </c>
       <c r="J215" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K215" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N215" s="14"/>
     </row>
@@ -10975,10 +10972,10 @@
         <v>0</v>
       </c>
       <c r="J216" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K216" s="12" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="N216" s="14"/>
     </row>
@@ -11012,16 +11009,16 @@
         <v>5</v>
       </c>
       <c r="J217" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K217" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N217" s="14"/>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A218" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B218" s="11" t="s">
         <v>300</v>
@@ -11049,10 +11046,10 @@
         <v>64</v>
       </c>
       <c r="J218" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K218" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N218" s="14"/>
     </row>
@@ -11086,10 +11083,10 @@
         <v>12</v>
       </c>
       <c r="J219" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K219" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N219" s="14"/>
     </row>
@@ -11123,10 +11120,10 @@
         <v>0</v>
       </c>
       <c r="J220" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K220" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N220" s="14"/>
     </row>
@@ -11160,16 +11157,16 @@
         <v>0</v>
       </c>
       <c r="J221" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K221" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N221" s="14"/>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A222" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B222" s="11" t="s">
         <v>288</v>
@@ -11197,10 +11194,10 @@
         <v>0</v>
       </c>
       <c r="J222" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K222" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N222" s="14"/>
     </row>
@@ -11234,10 +11231,10 @@
         <v>0</v>
       </c>
       <c r="J223" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K223" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N223" s="14"/>
     </row>
@@ -11271,10 +11268,10 @@
         <v>0</v>
       </c>
       <c r="J224" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K224" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N224" s="14"/>
     </row>
@@ -11308,10 +11305,10 @@
         <v>0</v>
       </c>
       <c r="J225" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K225" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N225" s="14"/>
     </row>
@@ -11345,10 +11342,10 @@
         <v>0</v>
       </c>
       <c r="J226" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K226" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N226" s="14"/>
     </row>
@@ -11382,10 +11379,10 @@
         <v>0</v>
       </c>
       <c r="J227" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K227" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N227" s="14"/>
     </row>
@@ -11419,10 +11416,10 @@
         <v>0</v>
       </c>
       <c r="J228" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K228" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N228" s="14"/>
     </row>
@@ -11456,10 +11453,10 @@
         <v>0</v>
       </c>
       <c r="J229" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K229" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N229" s="14"/>
     </row>
@@ -11493,16 +11490,16 @@
         <v>0</v>
       </c>
       <c r="J230" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K230" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N230" s="14"/>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A231" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B231" s="8" t="s">
         <v>444</v>
@@ -11530,16 +11527,16 @@
         <v>0</v>
       </c>
       <c r="J231" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K231" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N231" s="14"/>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A232" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B232" s="11" t="s">
         <v>289</v>
@@ -11567,10 +11564,10 @@
         <v>7</v>
       </c>
       <c r="J232" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K232" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N232" s="14"/>
     </row>
@@ -11604,10 +11601,10 @@
         <v>0</v>
       </c>
       <c r="J233" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K233" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N233" s="14"/>
     </row>
@@ -11641,10 +11638,10 @@
         <v>37</v>
       </c>
       <c r="J234" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K234" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N234" s="14"/>
     </row>
@@ -11678,10 +11675,10 @@
         <v>11</v>
       </c>
       <c r="J235" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K235" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N235" s="14"/>
     </row>
@@ -11715,16 +11712,16 @@
         <v>0</v>
       </c>
       <c r="J236" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K236" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N236" s="14"/>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A237" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B237" s="11" t="s">
         <v>437</v>
@@ -11752,10 +11749,10 @@
         <v>14</v>
       </c>
       <c r="J237" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K237" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N237" s="14"/>
     </row>
@@ -11789,10 +11786,10 @@
         <v>0</v>
       </c>
       <c r="J238" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K238" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N238" s="14"/>
     </row>
@@ -11826,10 +11823,10 @@
         <v>39</v>
       </c>
       <c r="J239" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K239" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N239" s="14"/>
     </row>
@@ -11863,10 +11860,10 @@
         <v>0</v>
       </c>
       <c r="J240" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K240" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N240" s="14"/>
     </row>
@@ -11900,10 +11897,10 @@
         <v>0</v>
       </c>
       <c r="J241" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K241" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N241" s="14"/>
     </row>
@@ -11937,10 +11934,10 @@
         <v>2</v>
       </c>
       <c r="J242" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K242" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N242" s="14"/>
     </row>
@@ -11974,10 +11971,10 @@
         <v>0</v>
       </c>
       <c r="J243" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K243" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N243" s="14"/>
     </row>
@@ -12011,10 +12008,10 @@
         <v>0</v>
       </c>
       <c r="J244" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K244" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N244" s="14"/>
     </row>
@@ -12048,10 +12045,10 @@
         <v>0</v>
       </c>
       <c r="J245" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K245" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N245" s="14"/>
     </row>
@@ -12085,16 +12082,16 @@
         <v>0</v>
       </c>
       <c r="J246" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K246" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N246" s="14"/>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A247" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B247" s="11" t="s">
         <v>348</v>
@@ -12122,10 +12119,10 @@
         <v>33</v>
       </c>
       <c r="J247" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K247" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N247" s="14"/>
     </row>
@@ -12159,10 +12156,10 @@
         <v>0</v>
       </c>
       <c r="J248" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K248" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N248" s="14"/>
     </row>
@@ -12196,10 +12193,10 @@
         <v>1</v>
       </c>
       <c r="J249" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K249" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N249" s="14"/>
     </row>
@@ -12233,10 +12230,10 @@
         <v>0.75</v>
       </c>
       <c r="J250" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K250" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N250" s="14"/>
     </row>
@@ -12270,10 +12267,10 @@
         <v>0.75</v>
       </c>
       <c r="J251" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K251" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N251" s="14"/>
     </row>
@@ -12307,10 +12304,10 @@
         <v>0.75</v>
       </c>
       <c r="J252" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K252" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N252" s="14"/>
     </row>
@@ -12344,10 +12341,10 @@
         <v>0.75</v>
       </c>
       <c r="J253" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K253" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N253" s="14"/>
     </row>
@@ -12381,10 +12378,10 @@
         <v>0.75</v>
       </c>
       <c r="J254" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K254" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N254" s="14"/>
     </row>
@@ -12418,10 +12415,10 @@
         <v>0.75</v>
       </c>
       <c r="J255" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K255" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N255" s="14"/>
     </row>
@@ -12455,10 +12452,10 @@
         <v>0.75</v>
       </c>
       <c r="J256" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K256" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N256" s="14"/>
     </row>
@@ -12492,10 +12489,10 @@
         <v>0.75</v>
       </c>
       <c r="J257" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K257" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N257" s="14"/>
     </row>
@@ -12529,10 +12526,10 @@
         <v>0.75</v>
       </c>
       <c r="J258" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K258" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N258" s="14"/>
     </row>
@@ -12566,10 +12563,10 @@
         <v>0.75</v>
       </c>
       <c r="J259" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K259" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N259" s="14"/>
     </row>
@@ -12604,10 +12601,10 @@
         <v>0.75</v>
       </c>
       <c r="J260" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K260" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N260" s="14"/>
     </row>
@@ -12642,10 +12639,10 @@
         <v>0.75</v>
       </c>
       <c r="J261" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K261" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N261" s="14"/>
     </row>
@@ -12680,10 +12677,10 @@
         <v>0.75</v>
       </c>
       <c r="J262" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K262" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N262" s="14"/>
     </row>
@@ -12718,10 +12715,10 @@
         <v>0.75</v>
       </c>
       <c r="J263" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K263" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N263" s="14"/>
     </row>
@@ -12756,10 +12753,10 @@
         <v>0.75</v>
       </c>
       <c r="J264" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K264" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N264" s="14"/>
     </row>
@@ -12794,10 +12791,10 @@
         <v>0.75</v>
       </c>
       <c r="J265" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K265" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N265" s="14"/>
     </row>
@@ -12832,10 +12829,10 @@
         <v>0.75</v>
       </c>
       <c r="J266" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K266" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N266" s="14"/>
     </row>
@@ -12870,10 +12867,10 @@
         <v>0.75</v>
       </c>
       <c r="J267" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K267" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N267" s="14"/>
     </row>
@@ -12907,10 +12904,10 @@
         <v>0</v>
       </c>
       <c r="J268" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K268" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N268" s="14"/>
     </row>
@@ -12944,10 +12941,10 @@
         <v>0</v>
       </c>
       <c r="J269" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K269" s="12" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="N269" s="14"/>
     </row>
@@ -12981,16 +12978,16 @@
         <v>0</v>
       </c>
       <c r="J270" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K270" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N270" s="14"/>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A271" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B271" s="11" t="s">
         <v>296</v>
@@ -13018,10 +13015,10 @@
         <v>0</v>
       </c>
       <c r="J271" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K271" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N271" s="14"/>
     </row>
@@ -13055,10 +13052,10 @@
         <v>0</v>
       </c>
       <c r="J272" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K272" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N272" s="14"/>
     </row>
@@ -13092,10 +13089,10 @@
         <v>0</v>
       </c>
       <c r="J273" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K273" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N273" s="14"/>
     </row>
@@ -13123,17 +13120,17 @@
         <v>8.1420260095824801</v>
       </c>
       <c r="H274" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I274" s="9">
         <f>0.75+(9/365.25)+(1/12)+9+16+20</f>
         <v>45.85797399041752</v>
       </c>
       <c r="J274" s="8" t="s">
-        <v>767</v>
+        <v>798</v>
       </c>
       <c r="K274" s="12" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="N274" s="14"/>
     </row>
@@ -13167,16 +13164,16 @@
         <v>0</v>
       </c>
       <c r="J275" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K275" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N275" s="14"/>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A276" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B276" s="11" t="s">
         <v>337</v>
@@ -13204,16 +13201,16 @@
         <v>100</v>
       </c>
       <c r="J276" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K276" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N276" s="14"/>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A277" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B277" s="11" t="s">
         <v>339</v>
@@ -13241,16 +13238,16 @@
         <v>0</v>
       </c>
       <c r="J277" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K277" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N277" s="14"/>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A278" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B278" s="11" t="s">
         <v>314</v>
@@ -13278,10 +13275,10 @@
         <v>45</v>
       </c>
       <c r="J278" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K278" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N278" s="14"/>
     </row>
@@ -13315,10 +13312,10 @@
         <v>0</v>
       </c>
       <c r="J279" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K279" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N279" s="14"/>
     </row>
@@ -13352,10 +13349,10 @@
         <v>58</v>
       </c>
       <c r="J280" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K280" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N280" s="14"/>
     </row>
@@ -13389,10 +13386,10 @@
         <v>0</v>
       </c>
       <c r="J281" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K281" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N281" s="14"/>
     </row>
@@ -13426,10 +13423,10 @@
         <v>5</v>
       </c>
       <c r="J282" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K282" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N282" s="14"/>
     </row>
@@ -13463,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="J283" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K283" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N283" s="14"/>
     </row>
@@ -13500,10 +13497,10 @@
         <v>0</v>
       </c>
       <c r="J284" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K284" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N284" s="14"/>
     </row>
@@ -13537,10 +13534,10 @@
         <v>0</v>
       </c>
       <c r="J285" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K285" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N285" s="14"/>
     </row>
@@ -13574,10 +13571,10 @@
         <v>0</v>
       </c>
       <c r="J286" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K286" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N286" s="14"/>
     </row>
@@ -13611,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="J287" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K287" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N287" s="14"/>
     </row>
@@ -13648,10 +13645,10 @@
         <v>0</v>
       </c>
       <c r="J288" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K288" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N288" s="14"/>
     </row>
@@ -13685,10 +13682,10 @@
         <v>0</v>
       </c>
       <c r="J289" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K289" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N289" s="14"/>
     </row>
@@ -13722,10 +13719,10 @@
         <v>52</v>
       </c>
       <c r="J290" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K290" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N290" s="14"/>
     </row>
@@ -13759,10 +13756,10 @@
         <v>17</v>
       </c>
       <c r="J291" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K291" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N291" s="14"/>
     </row>
@@ -13796,10 +13793,10 @@
         <v>63</v>
       </c>
       <c r="J292" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K292" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N292" s="14"/>
     </row>
@@ -13833,10 +13830,10 @@
         <v>0</v>
       </c>
       <c r="J293" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K293" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N293" s="14"/>
     </row>
@@ -13870,10 +13867,10 @@
         <v>0</v>
       </c>
       <c r="J294" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K294" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N294" s="14"/>
     </row>
@@ -13907,10 +13904,10 @@
         <v>2</v>
       </c>
       <c r="J295" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K295" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N295" s="14"/>
     </row>
@@ -13944,10 +13941,10 @@
         <v>0</v>
       </c>
       <c r="J296" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K296" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N296" s="14"/>
     </row>
@@ -13981,10 +13978,10 @@
         <v>0</v>
       </c>
       <c r="J297" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K297" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N297" s="14"/>
     </row>
@@ -14018,10 +14015,10 @@
         <v>0</v>
       </c>
       <c r="J298" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K298" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N298" s="14"/>
     </row>
@@ -14055,10 +14052,10 @@
         <v>0</v>
       </c>
       <c r="J299" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K299" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N299" s="14"/>
     </row>
@@ -14092,16 +14089,16 @@
         <v>31</v>
       </c>
       <c r="J300" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K300" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N300" s="14"/>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A301" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B301" s="11" t="s">
         <v>445</v>
@@ -14129,10 +14126,10 @@
         <v>0</v>
       </c>
       <c r="J301" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K301" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N301" s="14"/>
     </row>
@@ -14166,10 +14163,10 @@
         <v>25</v>
       </c>
       <c r="J302" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K302" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N302" s="14"/>
     </row>
@@ -14203,10 +14200,10 @@
         <v>0</v>
       </c>
       <c r="J303" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K303" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N303" s="14"/>
     </row>
@@ -14240,10 +14237,10 @@
         <v>0</v>
       </c>
       <c r="J304" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K304" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N304" s="14"/>
     </row>
@@ -14277,16 +14274,16 @@
         <v>0</v>
       </c>
       <c r="J305" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K305" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N305" s="14"/>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A306" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B306" s="11" t="s">
         <v>243</v>
@@ -14314,10 +14311,10 @@
         <v>6</v>
       </c>
       <c r="J306" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K306" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N306" s="14"/>
     </row>
@@ -14351,16 +14348,16 @@
         <v>0</v>
       </c>
       <c r="J307" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K307" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N307" s="14"/>
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A308" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B308" s="11" t="s">
         <v>340</v>
@@ -14388,16 +14385,16 @@
         <v>0</v>
       </c>
       <c r="J308" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K308" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N308" s="14"/>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A309" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B309" s="11" t="s">
         <v>340</v>
@@ -14425,10 +14422,10 @@
         <v>48</v>
       </c>
       <c r="J309" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K309" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N309" s="14"/>
     </row>
@@ -14462,16 +14459,16 @@
         <v>0</v>
       </c>
       <c r="J310" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K310" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N310" s="14"/>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A311" s="11" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B311" s="11" t="s">
         <v>266</v>
@@ -14499,10 +14496,10 @@
         <v>45</v>
       </c>
       <c r="J311" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K311" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N311" s="14"/>
     </row>
@@ -14536,10 +14533,10 @@
         <v>19</v>
       </c>
       <c r="J312" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K312" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N312" s="14"/>
     </row>
@@ -14573,10 +14570,10 @@
         <v>39</v>
       </c>
       <c r="J313" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K313" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N313" s="14"/>
     </row>
@@ -14610,10 +14607,10 @@
         <v>0</v>
       </c>
       <c r="J314" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K314" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N314" s="14"/>
     </row>
@@ -14647,10 +14644,10 @@
         <v>0</v>
       </c>
       <c r="J315" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K315" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N315" s="14"/>
     </row>
@@ -14684,10 +14681,10 @@
         <v>31</v>
       </c>
       <c r="J316" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K316" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N316" s="14"/>
     </row>
@@ -14721,10 +14718,10 @@
         <v>0</v>
       </c>
       <c r="J317" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K317" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N317" s="14"/>
     </row>
@@ -14758,10 +14755,10 @@
         <v>3</v>
       </c>
       <c r="J318" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K318" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N318" s="14"/>
     </row>
@@ -14795,10 +14792,10 @@
         <v>0</v>
       </c>
       <c r="J319" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K319" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N319" s="14"/>
     </row>
@@ -14832,10 +14829,10 @@
         <v>31</v>
       </c>
       <c r="J320" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K320" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N320" s="14"/>
     </row>
@@ -14869,19 +14866,19 @@
         <v>0</v>
       </c>
       <c r="J321" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K321" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N321" s="14"/>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A322" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="B322" s="8" t="s">
         <v>768</v>
-      </c>
-      <c r="B322" s="8" t="s">
-        <v>769</v>
       </c>
       <c r="C322" s="4">
         <v>-22.954810999999999</v>
@@ -14906,10 +14903,10 @@
         <v>0</v>
       </c>
       <c r="J322" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K322" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="N322" s="14"/>
     </row>
@@ -14943,10 +14940,10 @@
         <v>0</v>
       </c>
       <c r="J323" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K323" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N323" s="14"/>
     </row>
@@ -14980,10 +14977,10 @@
         <v>5</v>
       </c>
       <c r="J324" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K324" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N324" s="14"/>
     </row>
@@ -15017,16 +15014,16 @@
         <v>0</v>
       </c>
       <c r="J325" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K325" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N325" s="14"/>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A326" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B326" s="11" t="s">
         <v>424</v>
@@ -15054,10 +15051,10 @@
         <v>88</v>
       </c>
       <c r="J326" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K326" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N326" s="14"/>
     </row>
@@ -15091,10 +15088,10 @@
         <v>0</v>
       </c>
       <c r="J327" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K327" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N327" s="14"/>
     </row>
@@ -15128,10 +15125,10 @@
         <v>0</v>
       </c>
       <c r="J328" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K328" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N328" s="14"/>
     </row>
@@ -15165,10 +15162,10 @@
         <v>0</v>
       </c>
       <c r="J329" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K329" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N329" s="14"/>
     </row>
@@ -15202,10 +15199,10 @@
         <v>0</v>
       </c>
       <c r="J330" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K330" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N330" s="14"/>
     </row>
@@ -15239,10 +15236,10 @@
         <v>0</v>
       </c>
       <c r="J331" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K331" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N331" s="14"/>
     </row>
@@ -15276,10 +15273,10 @@
         <v>0</v>
       </c>
       <c r="J332" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K332" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N332" s="14"/>
     </row>
@@ -15313,10 +15310,10 @@
         <v>0</v>
       </c>
       <c r="J333" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K333" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N333" s="14"/>
     </row>
@@ -15350,10 +15347,10 @@
         <v>0</v>
       </c>
       <c r="J334" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K334" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N334" s="14"/>
     </row>
@@ -15387,10 +15384,10 @@
         <v>0</v>
       </c>
       <c r="J335" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K335" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N335" s="14"/>
     </row>
@@ -15424,10 +15421,10 @@
         <v>0</v>
       </c>
       <c r="J336" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K336" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N336" s="14"/>
     </row>
@@ -15461,10 +15458,10 @@
         <v>0</v>
       </c>
       <c r="J337" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K337" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N337" s="14"/>
     </row>
@@ -15498,10 +15495,10 @@
         <v>0</v>
       </c>
       <c r="J338" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K338" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N338" s="14"/>
     </row>
@@ -15535,10 +15532,10 @@
         <v>0</v>
       </c>
       <c r="J339" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K339" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N339" s="14"/>
     </row>
@@ -15572,10 +15569,10 @@
         <v>0</v>
       </c>
       <c r="J340" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K340" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N340" s="14"/>
     </row>
@@ -15609,10 +15606,10 @@
         <v>14</v>
       </c>
       <c r="J341" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K341" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N341" s="14"/>
     </row>
@@ -15646,10 +15643,10 @@
         <v>0</v>
       </c>
       <c r="J342" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K342" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N342" s="14"/>
     </row>
@@ -15683,10 +15680,10 @@
         <v>0</v>
       </c>
       <c r="J343" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K343" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N343" s="14"/>
     </row>
@@ -15720,10 +15717,10 @@
         <v>0</v>
       </c>
       <c r="J344" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K344" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N344" s="14"/>
     </row>
@@ -15757,10 +15754,10 @@
         <v>0</v>
       </c>
       <c r="J345" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K345" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N345" s="14"/>
     </row>
@@ -15794,10 +15791,10 @@
         <v>0</v>
       </c>
       <c r="J346" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K346" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N346" s="14"/>
     </row>
@@ -15831,10 +15828,10 @@
         <v>0</v>
       </c>
       <c r="J347" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K347" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N347" s="14"/>
     </row>
@@ -15868,10 +15865,10 @@
         <v>0</v>
       </c>
       <c r="J348" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K348" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N348" s="14"/>
     </row>
@@ -15905,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="J349" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K349" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N349" s="14"/>
     </row>
@@ -15942,16 +15939,16 @@
         <v>0</v>
       </c>
       <c r="J350" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K350" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N350" s="14"/>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A351" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B351" s="16" t="s">
         <v>404</v>
@@ -15980,10 +15977,10 @@
         <v>3</v>
       </c>
       <c r="J351" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K351" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N351" s="14"/>
     </row>
@@ -16017,10 +16014,10 @@
         <v>7</v>
       </c>
       <c r="J352" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K352" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N352" s="14"/>
     </row>
@@ -16054,10 +16051,10 @@
         <v>3</v>
       </c>
       <c r="J353" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K353" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N353" s="14"/>
     </row>
@@ -16091,10 +16088,10 @@
         <v>0</v>
       </c>
       <c r="J354" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K354" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N354" s="14"/>
     </row>
@@ -16128,10 +16125,10 @@
         <v>10</v>
       </c>
       <c r="J355" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K355" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N355" s="14"/>
     </row>
@@ -16165,10 +16162,10 @@
         <v>26</v>
       </c>
       <c r="J356" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K356" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N356" s="14"/>
     </row>
@@ -16202,10 +16199,10 @@
         <v>12</v>
       </c>
       <c r="J357" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K357" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N357" s="14"/>
     </row>
@@ -16239,10 +16236,10 @@
         <v>0</v>
       </c>
       <c r="J358" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K358" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N358" s="14"/>
     </row>
@@ -16276,10 +16273,10 @@
         <v>11</v>
       </c>
       <c r="J359" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K359" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N359" s="14"/>
     </row>
@@ -16313,10 +16310,10 @@
         <v>0</v>
       </c>
       <c r="J360" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K360" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N360" s="14"/>
     </row>
@@ -16350,10 +16347,10 @@
         <v>8</v>
       </c>
       <c r="J361" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K361" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N361" s="14"/>
     </row>
@@ -16388,16 +16385,16 @@
         <v>0</v>
       </c>
       <c r="J362" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K362" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N362" s="14"/>
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A363" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B363" s="11" t="s">
         <v>311</v>
@@ -16425,10 +16422,10 @@
         <v>0</v>
       </c>
       <c r="J363" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K363" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N363" s="14"/>
     </row>
@@ -16462,10 +16459,10 @@
         <v>6</v>
       </c>
       <c r="J364" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K364" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N364" s="14"/>
     </row>
@@ -16499,16 +16496,16 @@
         <v>0</v>
       </c>
       <c r="J365" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K365" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N365" s="14"/>
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A366" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B366" s="11" t="s">
         <v>281</v>
@@ -16536,10 +16533,10 @@
         <v>3</v>
       </c>
       <c r="J366" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K366" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.35">
@@ -16572,10 +16569,10 @@
         <v>0</v>
       </c>
       <c r="J367" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K367" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.35">
@@ -16608,10 +16605,10 @@
         <v>0</v>
       </c>
       <c r="J368" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K368" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.35">
@@ -16644,10 +16641,10 @@
         <v>23</v>
       </c>
       <c r="J369" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K369" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.35">
@@ -16680,10 +16677,10 @@
         <v>0</v>
       </c>
       <c r="J370" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K370" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.35">
@@ -16716,10 +16713,10 @@
         <v>0</v>
       </c>
       <c r="J371" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K371" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.35">
@@ -16752,10 +16749,10 @@
         <v>0</v>
       </c>
       <c r="J372" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K372" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.35">
@@ -16788,10 +16785,10 @@
         <v>0</v>
       </c>
       <c r="J373" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K373" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.35">
@@ -16824,15 +16821,15 @@
         <v>3</v>
       </c>
       <c r="J374" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K374" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A375" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B375" s="11" t="s">
         <v>247</v>
@@ -16860,18 +16857,18 @@
         <v>0</v>
       </c>
       <c r="J375" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K375" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A376" s="8" t="s">
+        <v>770</v>
+      </c>
+      <c r="B376" s="8" t="s">
         <v>771</v>
-      </c>
-      <c r="B376" s="8" t="s">
-        <v>772</v>
       </c>
       <c r="C376" s="4">
         <v>-29.265045000000001</v>
@@ -16896,18 +16893,18 @@
         <v>0</v>
       </c>
       <c r="J376" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K376" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A377" s="8" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B377" s="8" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C377" s="4">
         <v>-33.906410999999999</v>
@@ -16926,24 +16923,24 @@
         <v>70</v>
       </c>
       <c r="H377" s="8" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="I377" s="9">
         <v>54</v>
       </c>
       <c r="J377" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K377" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A378" s="8" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B378" s="8" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C378" s="4">
         <v>-34.189658000000001</v>
@@ -16962,24 +16959,24 @@
         <v>75</v>
       </c>
       <c r="H378" s="8" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="I378" s="9">
         <v>51</v>
       </c>
       <c r="J378" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K378" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A379" s="8" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B379" s="8" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C379" s="4">
         <v>-33.961784999999999</v>
@@ -16998,24 +16995,24 @@
         <v>68</v>
       </c>
       <c r="H379" s="8" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="I379" s="9">
         <v>26</v>
       </c>
       <c r="J379" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K379" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A380" s="8" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B380" s="8" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C380" s="4">
         <v>-33.025978000000002</v>
@@ -17034,24 +17031,24 @@
         <v>56</v>
       </c>
       <c r="H380" s="8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="I380" s="9">
         <v>37</v>
       </c>
       <c r="J380" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K380" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A381" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B381" s="8" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C381" s="4">
         <v>-29.873816000000001</v>
@@ -17070,16 +17067,16 @@
         <v>41</v>
       </c>
       <c r="H381" s="8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="I381" s="9">
         <v>44</v>
       </c>
       <c r="J381" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K381" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.35">
@@ -17112,10 +17109,10 @@
         <v>0</v>
       </c>
       <c r="J382" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K382" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.35">
@@ -17148,10 +17145,10 @@
         <v>48</v>
       </c>
       <c r="J383" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K383" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.35">
@@ -17184,10 +17181,10 @@
         <v>0</v>
       </c>
       <c r="J384" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K384" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.35">
@@ -17220,10 +17217,10 @@
         <v>0</v>
       </c>
       <c r="J385" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K385" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.35">
@@ -17256,15 +17253,15 @@
         <v>0</v>
       </c>
       <c r="J386" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K386" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="387" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A387" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B387" s="11" t="s">
         <v>462</v>
@@ -17292,10 +17289,10 @@
         <v>0</v>
       </c>
       <c r="J387" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K387" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="388" spans="1:11" x14ac:dyDescent="0.35">
@@ -17328,10 +17325,10 @@
         <v>43</v>
       </c>
       <c r="J388" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K388" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.35">
@@ -17364,15 +17361,15 @@
         <v>0</v>
       </c>
       <c r="J389" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K389" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A390" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B390" s="11" t="s">
         <v>251</v>
@@ -17400,10 +17397,10 @@
         <v>60</v>
       </c>
       <c r="J390" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K390" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="391" spans="1:11" x14ac:dyDescent="0.35">
@@ -17436,10 +17433,10 @@
         <v>42</v>
       </c>
       <c r="J391" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K391" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.35">
@@ -17472,10 +17469,10 @@
         <v>0</v>
       </c>
       <c r="J392" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K392" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.35">
@@ -17508,10 +17505,10 @@
         <v>63</v>
       </c>
       <c r="J393" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K393" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.35">
@@ -17544,10 +17541,10 @@
         <v>0</v>
       </c>
       <c r="J394" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K394" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.35">
@@ -17580,10 +17577,10 @@
         <v>0</v>
       </c>
       <c r="J395" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K395" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.35">
@@ -17616,10 +17613,10 @@
         <v>0</v>
       </c>
       <c r="J396" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K396" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.35">
@@ -17652,10 +17649,10 @@
         <v>14</v>
       </c>
       <c r="J397" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K397" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.35">
@@ -17688,10 +17685,10 @@
         <v>0</v>
       </c>
       <c r="J398" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K398" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.35">
@@ -17724,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="J399" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K399" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="400" spans="1:11" x14ac:dyDescent="0.35">
@@ -17760,10 +17757,10 @@
         <v>0</v>
       </c>
       <c r="J400" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K400" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.35">
@@ -17796,10 +17793,10 @@
         <v>0</v>
       </c>
       <c r="J401" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K401" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.35">
@@ -17832,10 +17829,10 @@
         <v>0</v>
       </c>
       <c r="J402" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K402" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.35">
@@ -17868,10 +17865,10 @@
         <v>1</v>
       </c>
       <c r="J403" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K403" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.35">
@@ -17904,10 +17901,10 @@
         <v>0</v>
       </c>
       <c r="J404" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K404" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.35">
@@ -17940,10 +17937,10 @@
         <v>0</v>
       </c>
       <c r="J405" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K405" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.35">
@@ -17976,10 +17973,10 @@
         <v>0</v>
       </c>
       <c r="J406" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K406" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.35">
@@ -18012,10 +18009,10 @@
         <v>0</v>
       </c>
       <c r="J407" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K407" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.35">
@@ -18048,10 +18045,10 @@
         <v>1</v>
       </c>
       <c r="J408" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K408" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.35">
@@ -18084,10 +18081,10 @@
         <v>0</v>
       </c>
       <c r="J409" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K409" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.35">
@@ -18120,10 +18117,10 @@
         <v>0</v>
       </c>
       <c r="J410" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K410" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.35">
@@ -18156,10 +18153,10 @@
         <v>0</v>
       </c>
       <c r="J411" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K411" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.35">
@@ -18192,10 +18189,10 @@
         <v>0</v>
       </c>
       <c r="J412" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K412" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.35">
@@ -18228,10 +18225,10 @@
         <v>0</v>
       </c>
       <c r="J413" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K413" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.35">
@@ -18264,10 +18261,10 @@
         <v>0</v>
       </c>
       <c r="J414" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K414" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.35">
@@ -18300,10 +18297,10 @@
         <v>0</v>
       </c>
       <c r="J415" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K415" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.35">
@@ -18336,10 +18333,10 @@
         <v>0</v>
       </c>
       <c r="J416" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K416" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.35">
@@ -18372,10 +18369,10 @@
         <v>0</v>
       </c>
       <c r="J417" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K417" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.35">
@@ -18408,10 +18405,10 @@
         <v>0</v>
       </c>
       <c r="J418" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K418" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.35">
@@ -18444,10 +18441,10 @@
         <v>56</v>
       </c>
       <c r="J419" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K419" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.35">
@@ -18480,10 +18477,10 @@
         <v>0</v>
       </c>
       <c r="J420" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K420" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.35">
@@ -18516,10 +18513,10 @@
         <v>43</v>
       </c>
       <c r="J421" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K421" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.35">
@@ -18552,10 +18549,10 @@
         <v>1</v>
       </c>
       <c r="J422" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K422" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.35">
@@ -18588,10 +18585,10 @@
         <v>0</v>
       </c>
       <c r="J423" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K423" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.35">
@@ -18624,10 +18621,10 @@
         <v>24</v>
       </c>
       <c r="J424" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K424" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.35">
@@ -18660,10 +18657,10 @@
         <v>0</v>
       </c>
       <c r="J425" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K425" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.35">
@@ -18696,10 +18693,10 @@
         <v>0</v>
       </c>
       <c r="J426" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K426" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="427" spans="1:11" x14ac:dyDescent="0.35">
@@ -18732,10 +18729,10 @@
         <v>17</v>
       </c>
       <c r="J427" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K427" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.35">
@@ -18768,10 +18765,10 @@
         <v>0</v>
       </c>
       <c r="J428" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K428" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.35">
@@ -18804,10 +18801,10 @@
         <v>0</v>
       </c>
       <c r="J429" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K429" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.35">
@@ -18841,24 +18838,24 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="J430" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K430" s="12" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A431" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B431" s="8" t="s">
         <v>470</v>
       </c>
       <c r="C431" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D431" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E431" s="8">
         <v>1947</v>
@@ -18878,10 +18875,10 @@
         <v>5.6858974358974361</v>
       </c>
       <c r="J431" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K431" s="12" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.35">
@@ -18915,10 +18912,10 @@
         <v>0.66666666666666674</v>
       </c>
       <c r="J432" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K432" s="12" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.35">
@@ -18951,10 +18948,10 @@
         <v>0</v>
       </c>
       <c r="J433" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K433" s="12" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.35">
@@ -18987,10 +18984,10 @@
         <v>0</v>
       </c>
       <c r="J434" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K434" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="435" spans="1:11" x14ac:dyDescent="0.35">
@@ -19023,10 +19020,10 @@
         <v>0</v>
       </c>
       <c r="J435" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K435" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="436" spans="1:11" x14ac:dyDescent="0.35">
@@ -19059,10 +19056,10 @@
         <v>0</v>
       </c>
       <c r="J436" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K436" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="437" spans="1:11" x14ac:dyDescent="0.35">
@@ -19095,10 +19092,10 @@
         <v>0</v>
       </c>
       <c r="J437" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K437" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.35">
@@ -19131,10 +19128,10 @@
         <v>0</v>
       </c>
       <c r="J438" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K438" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="439" spans="1:11" x14ac:dyDescent="0.35">
@@ -19167,15 +19164,15 @@
         <v>0</v>
       </c>
       <c r="J439" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K439" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="440" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A440" s="8" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B440" s="8" t="s">
         <v>470</v>
@@ -19203,10 +19200,10 @@
         <v>0</v>
       </c>
       <c r="J440" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K440" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.35">
@@ -19239,10 +19236,10 @@
         <v>0</v>
       </c>
       <c r="J441" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K441" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="442" spans="1:11" x14ac:dyDescent="0.35">
@@ -19275,10 +19272,10 @@
         <v>0</v>
       </c>
       <c r="J442" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K442" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="443" spans="1:11" x14ac:dyDescent="0.35">
@@ -19311,15 +19308,15 @@
         <v>0</v>
       </c>
       <c r="J443" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K443" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A444" s="8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B444" s="8" t="s">
         <v>470</v>
@@ -19341,21 +19338,21 @@
         <v>79.400000000000006</v>
       </c>
       <c r="H444" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I444" s="9">
         <v>3.6</v>
       </c>
       <c r="J444" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K444" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="445" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A445" s="8" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B445" s="8" t="s">
         <v>470</v>
@@ -19377,21 +19374,21 @@
         <v>43.3</v>
       </c>
       <c r="H445" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I445" s="9">
         <v>21.7</v>
       </c>
       <c r="J445" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K445" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="446" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A446" s="8" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B446" s="8" t="s">
         <v>470</v>
@@ -19413,21 +19410,21 @@
         <v>62.3</v>
       </c>
       <c r="H446" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I446" s="9">
         <v>2.7</v>
       </c>
       <c r="J446" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K446" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="447" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A447" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B447" s="8" t="s">
         <v>470</v>
@@ -19449,21 +19446,21 @@
         <v>45</v>
       </c>
       <c r="H447" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I447" s="9">
         <v>0</v>
       </c>
       <c r="J447" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K447" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="448" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A448" s="8" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B448" s="8" t="s">
         <v>470</v>
@@ -19485,21 +19482,21 @@
         <v>8</v>
       </c>
       <c r="H448" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I448" s="9">
         <v>0</v>
       </c>
       <c r="J448" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K448" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="449" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A449" s="8" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B449" s="8" t="s">
         <v>470</v>
@@ -19521,21 +19518,21 @@
         <v>55.8</v>
       </c>
       <c r="H449" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I449" s="9">
         <v>5.2</v>
       </c>
       <c r="J449" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K449" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A450" s="8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B450" s="8" t="s">
         <v>470</v>
@@ -19557,21 +19554,21 @@
         <v>4</v>
       </c>
       <c r="H450" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I450" s="9">
         <v>0</v>
       </c>
       <c r="J450" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K450" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="451" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A451" s="8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B451" s="8" t="s">
         <v>470</v>
@@ -19593,21 +19590,21 @@
         <v>13</v>
       </c>
       <c r="H451" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I451" s="9">
         <v>7</v>
       </c>
       <c r="J451" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K451" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A452" s="8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B452" s="8" t="s">
         <v>470</v>
@@ -19629,21 +19626,21 @@
         <v>9</v>
       </c>
       <c r="H452" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I452" s="9">
         <v>0</v>
       </c>
       <c r="J452" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K452" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A453" s="8" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B453" s="8" t="s">
         <v>470</v>
@@ -19665,21 +19662,21 @@
         <v>16</v>
       </c>
       <c r="H453" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I453" s="9">
         <v>0</v>
       </c>
       <c r="J453" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K453" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A454" s="8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B454" s="8" t="s">
         <v>470</v>
@@ -19701,21 +19698,21 @@
         <v>54.4</v>
       </c>
       <c r="H454" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I454" s="9">
         <v>33.6</v>
       </c>
       <c r="J454" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K454" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A455" s="8" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B455" s="8" t="s">
         <v>470</v>
@@ -19737,21 +19734,21 @@
         <v>56.2</v>
       </c>
       <c r="H455" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I455" s="9">
         <v>4.8</v>
       </c>
       <c r="J455" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K455" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A456" s="8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B456" s="8" t="s">
         <v>470</v>
@@ -19773,21 +19770,21 @@
         <v>7</v>
       </c>
       <c r="H456" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I456" s="9">
         <v>5</v>
       </c>
       <c r="J456" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K456" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A457" s="8" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B457" s="8" t="s">
         <v>470</v>
@@ -19809,21 +19806,21 @@
         <v>31.799999999999997</v>
       </c>
       <c r="H457" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I457" s="9">
         <v>92.2</v>
       </c>
       <c r="J457" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K457" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A458" s="8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B458" s="8" t="s">
         <v>470</v>
@@ -19845,21 +19842,21 @@
         <v>10</v>
       </c>
       <c r="H458" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I458" s="9">
         <v>31</v>
       </c>
       <c r="J458" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K458" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A459" s="8" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B459" s="8" t="s">
         <v>470</v>
@@ -19881,21 +19878,21 @@
         <v>63</v>
       </c>
       <c r="H459" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I459" s="9">
         <v>14</v>
       </c>
       <c r="J459" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K459" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A460" s="8" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B460" s="8" t="s">
         <v>470</v>
@@ -19917,21 +19914,21 @@
         <v>20</v>
       </c>
       <c r="H460" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I460" s="9">
         <v>3</v>
       </c>
       <c r="J460" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K460" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A461" s="8" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B461" s="8" t="s">
         <v>470</v>
@@ -19953,21 +19950,21 @@
         <v>21</v>
       </c>
       <c r="H461" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I461" s="9">
         <v>2</v>
       </c>
       <c r="J461" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K461" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A462" s="8" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B462" s="8" t="s">
         <v>470</v>
@@ -19989,21 +19986,21 @@
         <v>21</v>
       </c>
       <c r="H462" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I462" s="9">
         <v>2</v>
       </c>
       <c r="J462" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K462" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A463" s="8" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B463" s="8" t="s">
         <v>470</v>
@@ -20025,21 +20022,21 @@
         <v>15</v>
       </c>
       <c r="H463" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I463" s="9">
         <v>58</v>
       </c>
       <c r="J463" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K463" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A464" s="8" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B464" s="8" t="s">
         <v>470</v>
@@ -20061,21 +20058,21 @@
         <v>6</v>
       </c>
       <c r="H464" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I464" s="9">
         <v>6</v>
       </c>
       <c r="J464" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K464" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A465" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B465" s="8" t="s">
         <v>470</v>
@@ -20097,30 +20094,30 @@
         <v>53</v>
       </c>
       <c r="H465" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I465" s="9">
         <v>0</v>
       </c>
       <c r="J465" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K465" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A466" s="8" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B466" s="8" t="s">
         <v>470</v>
       </c>
       <c r="C466" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D466" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E466" s="8">
         <v>1859</v>
@@ -20133,16 +20130,16 @@
         <v>19</v>
       </c>
       <c r="H466" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I466" s="9">
         <v>1</v>
       </c>
       <c r="J466" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K466" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.35">
@@ -20175,10 +20172,10 @@
         <v>0</v>
       </c>
       <c r="J467" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K467" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.35">
@@ -20186,7 +20183,7 @@
         <v>241</v>
       </c>
       <c r="B468" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C468" s="4">
         <v>35.955260000000003</v>
@@ -20211,10 +20208,10 @@
         <v>0</v>
       </c>
       <c r="J468" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K468" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.35">
@@ -20247,10 +20244,10 @@
         <v>0</v>
       </c>
       <c r="J469" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K469" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.35">
@@ -20283,10 +20280,10 @@
         <v>0</v>
       </c>
       <c r="J470" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K470" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.35">
@@ -20319,10 +20316,10 @@
         <v>57</v>
       </c>
       <c r="J471" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K471" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.35">
@@ -20355,10 +20352,10 @@
         <v>0</v>
       </c>
       <c r="J472" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K472" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.35">
@@ -20391,10 +20388,10 @@
         <v>0</v>
       </c>
       <c r="J473" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K473" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.35">
@@ -20427,15 +20424,15 @@
         <v>0</v>
       </c>
       <c r="J474" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K474" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A475" s="8" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B475" s="8" t="s">
         <v>450</v>
@@ -20463,10 +20460,10 @@
         <v>19</v>
       </c>
       <c r="J475" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K475" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.35">
@@ -20499,10 +20496,10 @@
         <v>5</v>
       </c>
       <c r="J476" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K476" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.35">
@@ -20535,10 +20532,10 @@
         <v>0</v>
       </c>
       <c r="J477" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K477" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.35">
@@ -20571,10 +20568,10 @@
         <v>0</v>
       </c>
       <c r="J478" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K478" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="479" spans="1:11" x14ac:dyDescent="0.35">
@@ -20607,10 +20604,10 @@
         <v>0</v>
       </c>
       <c r="J479" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K479" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.35">
@@ -20643,10 +20640,10 @@
         <v>44</v>
       </c>
       <c r="J480" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K480" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.35">
@@ -20679,10 +20676,10 @@
         <v>16</v>
       </c>
       <c r="J481" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K481" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.35">
@@ -20715,10 +20712,10 @@
         <v>0</v>
       </c>
       <c r="J482" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K482" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="483" spans="1:11" x14ac:dyDescent="0.35">
@@ -20751,10 +20748,10 @@
         <v>0</v>
       </c>
       <c r="J483" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K483" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.35">
@@ -20787,10 +20784,10 @@
         <v>23</v>
       </c>
       <c r="J484" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K484" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.35">
@@ -20823,10 +20820,10 @@
         <v>0</v>
       </c>
       <c r="J485" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K485" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.35">
@@ -20859,10 +20856,10 @@
         <v>19</v>
       </c>
       <c r="J486" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K486" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.35">
@@ -20895,10 +20892,10 @@
         <v>0</v>
       </c>
       <c r="J487" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K487" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.35">
@@ -20931,10 +20928,10 @@
         <v>0</v>
       </c>
       <c r="J488" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K488" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="489" spans="1:11" x14ac:dyDescent="0.35">
@@ -20967,10 +20964,10 @@
         <v>72</v>
       </c>
       <c r="J489" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K489" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.35">
@@ -21003,10 +21000,10 @@
         <v>0</v>
       </c>
       <c r="J490" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K490" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="491" spans="1:11" x14ac:dyDescent="0.35">
@@ -21039,10 +21036,10 @@
         <v>0</v>
       </c>
       <c r="J491" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K491" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.35">
@@ -21075,10 +21072,10 @@
         <v>0</v>
       </c>
       <c r="J492" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K492" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="493" spans="1:11" x14ac:dyDescent="0.35">
@@ -21111,10 +21108,10 @@
         <v>0</v>
       </c>
       <c r="J493" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K493" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="494" spans="1:11" x14ac:dyDescent="0.35">
@@ -21147,10 +21144,10 @@
         <v>0</v>
       </c>
       <c r="J494" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K494" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="495" spans="1:11" x14ac:dyDescent="0.35">
@@ -21183,10 +21180,10 @@
         <v>0</v>
       </c>
       <c r="J495" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K495" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="496" spans="1:11" x14ac:dyDescent="0.35">
@@ -21219,10 +21216,10 @@
         <v>0</v>
       </c>
       <c r="J496" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K496" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="497" spans="1:11" x14ac:dyDescent="0.35">
@@ -21255,10 +21252,10 @@
         <v>4</v>
       </c>
       <c r="J497" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K497" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="498" spans="1:11" x14ac:dyDescent="0.35">
@@ -21291,10 +21288,10 @@
         <v>39</v>
       </c>
       <c r="J498" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K498" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="499" spans="1:11" x14ac:dyDescent="0.35">
@@ -21327,10 +21324,10 @@
         <v>0</v>
       </c>
       <c r="J499" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K499" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="500" spans="1:11" x14ac:dyDescent="0.35">
@@ -21363,10 +21360,10 @@
         <v>1</v>
       </c>
       <c r="J500" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K500" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="501" spans="1:11" x14ac:dyDescent="0.35">
@@ -21399,10 +21396,10 @@
         <v>0</v>
       </c>
       <c r="J501" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K501" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="502" spans="1:11" x14ac:dyDescent="0.35">
@@ -21435,15 +21432,15 @@
         <v>0</v>
       </c>
       <c r="J502" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K502" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A503" s="8" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B503" s="8" t="s">
         <v>450</v>
@@ -21471,10 +21468,10 @@
         <v>0</v>
       </c>
       <c r="J503" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K503" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="504" spans="1:11" x14ac:dyDescent="0.35">
@@ -21507,10 +21504,10 @@
         <v>0</v>
       </c>
       <c r="J504" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K504" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="505" spans="1:11" x14ac:dyDescent="0.35">
@@ -21543,10 +21540,10 @@
         <v>0</v>
       </c>
       <c r="J505" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K505" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="506" spans="1:11" x14ac:dyDescent="0.35">
@@ -21579,10 +21576,10 @@
         <v>0</v>
       </c>
       <c r="J506" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K506" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="507" spans="1:11" x14ac:dyDescent="0.35">
@@ -21615,10 +21612,10 @@
         <v>0</v>
       </c>
       <c r="J507" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K507" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="508" spans="1:11" x14ac:dyDescent="0.35">
@@ -21651,10 +21648,10 @@
         <v>59</v>
       </c>
       <c r="J508" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K508" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="509" spans="1:11" x14ac:dyDescent="0.35">
@@ -21687,10 +21684,10 @@
         <v>0</v>
       </c>
       <c r="J509" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K509" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="510" spans="1:11" x14ac:dyDescent="0.35">
@@ -21723,10 +21720,10 @@
         <v>12</v>
       </c>
       <c r="J510" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K510" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="511" spans="1:11" x14ac:dyDescent="0.35">
@@ -21759,10 +21756,10 @@
         <v>0</v>
       </c>
       <c r="J511" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K511" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="512" spans="1:11" x14ac:dyDescent="0.35">
@@ -21795,10 +21792,10 @@
         <v>0</v>
       </c>
       <c r="J512" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K512" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="513" spans="1:11" x14ac:dyDescent="0.35">
@@ -21831,10 +21828,10 @@
         <v>32</v>
       </c>
       <c r="J513" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K513" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="514" spans="1:11" x14ac:dyDescent="0.35">
@@ -21867,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="J514" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K514" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="515" spans="1:11" x14ac:dyDescent="0.35">
@@ -21903,10 +21900,10 @@
         <v>0</v>
       </c>
       <c r="J515" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K515" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="516" spans="1:11" x14ac:dyDescent="0.35">
@@ -21939,10 +21936,10 @@
         <v>0</v>
       </c>
       <c r="J516" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K516" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="517" spans="1:11" x14ac:dyDescent="0.35">
@@ -21975,15 +21972,15 @@
         <v>0</v>
       </c>
       <c r="J517" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K517" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="518" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A518" s="8" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B518" s="8" t="s">
         <v>450</v>
@@ -22011,10 +22008,10 @@
         <v>0</v>
       </c>
       <c r="J518" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K518" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="519" spans="1:11" x14ac:dyDescent="0.35">
@@ -22047,10 +22044,10 @@
         <v>0</v>
       </c>
       <c r="J519" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K519" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="520" spans="1:11" x14ac:dyDescent="0.35">
@@ -22083,10 +22080,10 @@
         <v>0</v>
       </c>
       <c r="J520" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K520" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="521" spans="1:11" x14ac:dyDescent="0.35">
@@ -22119,10 +22116,10 @@
         <v>0</v>
       </c>
       <c r="J521" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K521" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="522" spans="1:11" x14ac:dyDescent="0.35">
@@ -22155,10 +22152,10 @@
         <v>9</v>
       </c>
       <c r="J522" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K522" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="523" spans="1:11" x14ac:dyDescent="0.35">
@@ -22191,10 +22188,10 @@
         <v>4</v>
       </c>
       <c r="J523" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K523" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="524" spans="1:11" x14ac:dyDescent="0.35">
@@ -22227,10 +22224,10 @@
         <v>0</v>
       </c>
       <c r="J524" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K524" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="525" spans="1:11" x14ac:dyDescent="0.35">
@@ -22263,10 +22260,10 @@
         <v>0</v>
       </c>
       <c r="J525" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K525" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="526" spans="1:11" x14ac:dyDescent="0.35">
@@ -22299,10 +22296,10 @@
         <v>15</v>
       </c>
       <c r="J526" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K526" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="527" spans="1:11" x14ac:dyDescent="0.35">
@@ -22335,10 +22332,10 @@
         <v>3</v>
       </c>
       <c r="J527" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K527" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="528" spans="1:11" x14ac:dyDescent="0.35">
@@ -22371,10 +22368,10 @@
         <v>10</v>
       </c>
       <c r="J528" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K528" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.35">
@@ -22407,10 +22404,10 @@
         <v>5</v>
       </c>
       <c r="J529" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K529" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.35">
@@ -22443,10 +22440,10 @@
         <v>4</v>
       </c>
       <c r="J530" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K530" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="531" spans="1:11" x14ac:dyDescent="0.35">
@@ -22479,10 +22476,10 @@
         <v>0</v>
       </c>
       <c r="J531" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K531" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.35">
@@ -22515,10 +22512,10 @@
         <v>35</v>
       </c>
       <c r="J532" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K532" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="533" spans="1:11" x14ac:dyDescent="0.35">
@@ -22551,10 +22548,10 @@
         <v>0</v>
       </c>
       <c r="J533" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K533" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="534" spans="1:11" x14ac:dyDescent="0.35">
@@ -22587,10 +22584,10 @@
         <v>0</v>
       </c>
       <c r="J534" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K534" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="535" spans="1:11" x14ac:dyDescent="0.35">
@@ -22623,10 +22620,10 @@
         <v>33</v>
       </c>
       <c r="J535" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K535" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.35">
@@ -22659,10 +22656,10 @@
         <v>0</v>
       </c>
       <c r="J536" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K536" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.35">
@@ -22695,10 +22692,10 @@
         <v>0</v>
       </c>
       <c r="J537" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K537" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.35">
@@ -22731,10 +22728,10 @@
         <v>64</v>
       </c>
       <c r="J538" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K538" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.35">
@@ -22767,10 +22764,10 @@
         <v>0</v>
       </c>
       <c r="J539" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K539" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.35">
@@ -22803,10 +22800,10 @@
         <v>0</v>
       </c>
       <c r="J540" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K540" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.35">
@@ -22839,10 +22836,10 @@
         <v>0</v>
       </c>
       <c r="J541" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K541" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="542" spans="1:11" x14ac:dyDescent="0.35">
@@ -22875,10 +22872,10 @@
         <v>0</v>
       </c>
       <c r="J542" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K542" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.35">
@@ -22911,10 +22908,10 @@
         <v>0</v>
       </c>
       <c r="J543" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K543" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.35">
@@ -22947,10 +22944,10 @@
         <v>0</v>
       </c>
       <c r="J544" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K544" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="545" spans="1:11" x14ac:dyDescent="0.35">
@@ -22983,10 +22980,10 @@
         <v>0</v>
       </c>
       <c r="J545" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K545" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="546" spans="1:11" x14ac:dyDescent="0.35">
@@ -23019,10 +23016,10 @@
         <v>0</v>
       </c>
       <c r="J546" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K546" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="547" spans="1:11" x14ac:dyDescent="0.35">
@@ -23055,10 +23052,10 @@
         <v>0</v>
       </c>
       <c r="J547" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K547" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="548" spans="1:11" x14ac:dyDescent="0.35">
@@ -23091,10 +23088,10 @@
         <v>0</v>
       </c>
       <c r="J548" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K548" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="549" spans="1:11" x14ac:dyDescent="0.35">
@@ -23127,10 +23124,10 @@
         <v>6</v>
       </c>
       <c r="J549" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K549" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="550" spans="1:11" x14ac:dyDescent="0.35">
@@ -23163,10 +23160,10 @@
         <v>0</v>
       </c>
       <c r="J550" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K550" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="551" spans="1:11" x14ac:dyDescent="0.35">
@@ -23199,10 +23196,10 @@
         <v>0</v>
       </c>
       <c r="J551" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K551" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="552" spans="1:11" x14ac:dyDescent="0.35">
@@ -23235,10 +23232,10 @@
         <v>8</v>
       </c>
       <c r="J552" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K552" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="553" spans="1:11" x14ac:dyDescent="0.35">
@@ -23271,10 +23268,10 @@
         <v>0</v>
       </c>
       <c r="J553" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K553" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.35">
@@ -23307,10 +23304,10 @@
         <v>23</v>
       </c>
       <c r="J554" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K554" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="555" spans="1:11" x14ac:dyDescent="0.35">
@@ -23343,10 +23340,10 @@
         <v>0</v>
       </c>
       <c r="J555" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K555" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="556" spans="1:11" x14ac:dyDescent="0.35">
@@ -23379,10 +23376,10 @@
         <v>4</v>
       </c>
       <c r="J556" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K556" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="557" spans="1:11" x14ac:dyDescent="0.35">
@@ -23415,10 +23412,10 @@
         <v>96</v>
       </c>
       <c r="J557" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K557" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="558" spans="1:11" x14ac:dyDescent="0.35">
@@ -23451,10 +23448,10 @@
         <v>6</v>
       </c>
       <c r="J558" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K558" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.35">
@@ -23487,10 +23484,10 @@
         <v>0</v>
       </c>
       <c r="J559" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K559" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="560" spans="1:11" x14ac:dyDescent="0.35">
@@ -23523,10 +23520,10 @@
         <v>0</v>
       </c>
       <c r="J560" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K560" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="561" spans="1:11" x14ac:dyDescent="0.35">
@@ -23559,10 +23556,10 @@
         <v>0</v>
       </c>
       <c r="J561" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K561" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="562" spans="1:11" x14ac:dyDescent="0.35">
@@ -23595,10 +23592,10 @@
         <v>0</v>
       </c>
       <c r="J562" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K562" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="563" spans="1:11" x14ac:dyDescent="0.35">
@@ -23631,10 +23628,10 @@
         <v>19</v>
       </c>
       <c r="J563" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K563" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="564" spans="1:11" x14ac:dyDescent="0.35">
@@ -23667,10 +23664,10 @@
         <v>0</v>
       </c>
       <c r="J564" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K564" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="565" spans="1:11" x14ac:dyDescent="0.35">
@@ -23703,10 +23700,10 @@
         <v>0</v>
       </c>
       <c r="J565" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K565" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="566" spans="1:11" x14ac:dyDescent="0.35">
@@ -23739,10 +23736,10 @@
         <v>32</v>
       </c>
       <c r="J566" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K566" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.35">
@@ -23775,10 +23772,10 @@
         <v>27</v>
       </c>
       <c r="J567" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K567" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="568" spans="1:11" x14ac:dyDescent="0.35">
@@ -23811,10 +23808,10 @@
         <v>0</v>
       </c>
       <c r="J568" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K568" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="569" spans="1:11" x14ac:dyDescent="0.35">
@@ -23847,10 +23844,10 @@
         <v>0</v>
       </c>
       <c r="J569" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K569" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="570" spans="1:11" x14ac:dyDescent="0.35">
@@ -23883,10 +23880,10 @@
         <v>12</v>
       </c>
       <c r="J570" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K570" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="571" spans="1:11" x14ac:dyDescent="0.35">
@@ -23919,10 +23916,10 @@
         <v>0</v>
       </c>
       <c r="J571" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K571" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="572" spans="1:11" x14ac:dyDescent="0.35">
@@ -23955,10 +23952,10 @@
         <v>0</v>
       </c>
       <c r="J572" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K572" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="573" spans="1:11" x14ac:dyDescent="0.35">
@@ -23991,10 +23988,10 @@
         <v>20</v>
       </c>
       <c r="J573" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K573" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="574" spans="1:11" x14ac:dyDescent="0.35">
@@ -24027,10 +24024,10 @@
         <v>30</v>
       </c>
       <c r="J574" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K574" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="575" spans="1:11" x14ac:dyDescent="0.35">
@@ -24063,10 +24060,10 @@
         <v>0</v>
       </c>
       <c r="J575" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K575" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="576" spans="1:11" x14ac:dyDescent="0.35">
@@ -24099,10 +24096,10 @@
         <v>0</v>
       </c>
       <c r="J576" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K576" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="577" spans="1:11" x14ac:dyDescent="0.35">
@@ -24135,10 +24132,10 @@
         <v>35</v>
       </c>
       <c r="J577" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K577" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="578" spans="1:11" x14ac:dyDescent="0.35">
@@ -24171,10 +24168,10 @@
         <v>41</v>
       </c>
       <c r="J578" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K578" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="579" spans="1:11" x14ac:dyDescent="0.35">
@@ -24207,10 +24204,10 @@
         <v>0</v>
       </c>
       <c r="J579" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K579" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="580" spans="1:11" x14ac:dyDescent="0.35">
@@ -24243,10 +24240,10 @@
         <v>7</v>
       </c>
       <c r="J580" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K580" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="581" spans="1:11" x14ac:dyDescent="0.35">
@@ -24279,10 +24276,10 @@
         <v>52</v>
       </c>
       <c r="J581" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K581" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="582" spans="1:11" x14ac:dyDescent="0.35">
@@ -24315,10 +24312,10 @@
         <v>8</v>
       </c>
       <c r="J582" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K582" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="583" spans="1:11" x14ac:dyDescent="0.35">
@@ -24351,10 +24348,10 @@
         <v>12</v>
       </c>
       <c r="J583" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K583" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="584" spans="1:11" x14ac:dyDescent="0.35">
@@ -24387,10 +24384,10 @@
         <v>10</v>
       </c>
       <c r="J584" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K584" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="585" spans="1:11" x14ac:dyDescent="0.35">
@@ -24423,10 +24420,10 @@
         <v>0</v>
       </c>
       <c r="J585" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K585" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="586" spans="1:11" x14ac:dyDescent="0.35">
@@ -24459,10 +24456,10 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="J586" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K586" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="587" spans="1:11" x14ac:dyDescent="0.35">
@@ -24495,10 +24492,10 @@
         <v>0</v>
       </c>
       <c r="J587" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K587" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="588" spans="1:11" x14ac:dyDescent="0.35">
@@ -24531,10 +24528,10 @@
         <v>0</v>
       </c>
       <c r="J588" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K588" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="589" spans="1:11" x14ac:dyDescent="0.35">
@@ -24567,10 +24564,10 @@
         <v>4</v>
       </c>
       <c r="J589" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K589" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="590" spans="1:11" x14ac:dyDescent="0.35">
@@ -24603,10 +24600,10 @@
         <v>10</v>
       </c>
       <c r="J590" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K590" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="591" spans="1:11" x14ac:dyDescent="0.35">
@@ -24639,10 +24636,10 @@
         <v>56</v>
       </c>
       <c r="J591" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K591" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="592" spans="1:11" x14ac:dyDescent="0.35">
@@ -24675,10 +24672,10 @@
         <v>0</v>
       </c>
       <c r="J592" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K592" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="593" spans="1:11" x14ac:dyDescent="0.35">
@@ -24711,10 +24708,10 @@
         <v>4</v>
       </c>
       <c r="J593" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K593" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="594" spans="1:11" x14ac:dyDescent="0.35">
@@ -24747,10 +24744,10 @@
         <v>0</v>
       </c>
       <c r="J594" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K594" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="595" spans="1:11" x14ac:dyDescent="0.35">
@@ -24783,10 +24780,10 @@
         <v>0</v>
       </c>
       <c r="J595" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K595" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="596" spans="1:11" x14ac:dyDescent="0.35">
@@ -24819,10 +24816,10 @@
         <v>0</v>
       </c>
       <c r="J596" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K596" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="597" spans="1:11" x14ac:dyDescent="0.35">
@@ -24855,10 +24852,10 @@
         <v>0</v>
       </c>
       <c r="J597" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K597" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="598" spans="1:11" x14ac:dyDescent="0.35">
@@ -24891,10 +24888,10 @@
         <v>1</v>
       </c>
       <c r="J598" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K598" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="599" spans="1:11" x14ac:dyDescent="0.35">
@@ -24927,10 +24924,10 @@
         <v>0</v>
       </c>
       <c r="J599" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K599" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="600" spans="1:11" x14ac:dyDescent="0.35">
@@ -24963,10 +24960,10 @@
         <v>0</v>
       </c>
       <c r="J600" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K600" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="601" spans="1:11" x14ac:dyDescent="0.35">
@@ -24999,10 +24996,10 @@
         <v>3</v>
       </c>
       <c r="J601" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K601" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="602" spans="1:11" x14ac:dyDescent="0.35">
@@ -25035,10 +25032,10 @@
         <v>0</v>
       </c>
       <c r="J602" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K602" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="603" spans="1:11" x14ac:dyDescent="0.35">
@@ -25071,10 +25068,10 @@
         <v>29</v>
       </c>
       <c r="J603" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K603" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="604" spans="1:11" x14ac:dyDescent="0.35">
@@ -25107,10 +25104,10 @@
         <v>0</v>
       </c>
       <c r="J604" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K604" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="605" spans="1:11" x14ac:dyDescent="0.35">
@@ -25143,10 +25140,10 @@
         <v>0</v>
       </c>
       <c r="J605" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K605" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="606" spans="1:11" x14ac:dyDescent="0.35">
@@ -25179,10 +25176,10 @@
         <v>1</v>
       </c>
       <c r="J606" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K606" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="607" spans="1:11" x14ac:dyDescent="0.35">
@@ -25215,10 +25212,10 @@
         <v>1</v>
       </c>
       <c r="J607" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K607" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="608" spans="1:11" x14ac:dyDescent="0.35">
@@ -25251,10 +25248,10 @@
         <v>0</v>
       </c>
       <c r="J608" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K608" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="609" spans="1:11" x14ac:dyDescent="0.35">
@@ -25287,10 +25284,10 @@
         <v>0</v>
       </c>
       <c r="J609" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K609" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="610" spans="1:11" x14ac:dyDescent="0.35">
@@ -25323,10 +25320,10 @@
         <v>51</v>
       </c>
       <c r="J610" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K610" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="611" spans="1:11" x14ac:dyDescent="0.35">
@@ -25359,10 +25356,10 @@
         <v>0</v>
       </c>
       <c r="J611" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K611" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="612" spans="1:11" x14ac:dyDescent="0.35">
@@ -25395,10 +25392,10 @@
         <v>0</v>
       </c>
       <c r="J612" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K612" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="613" spans="1:11" x14ac:dyDescent="0.35">
@@ -25431,10 +25428,10 @@
         <v>78</v>
       </c>
       <c r="J613" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K613" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="614" spans="1:11" x14ac:dyDescent="0.35">
@@ -25467,10 +25464,10 @@
         <v>15</v>
       </c>
       <c r="J614" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K614" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="615" spans="1:11" x14ac:dyDescent="0.35">
@@ -25503,10 +25500,10 @@
         <v>0</v>
       </c>
       <c r="J615" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K615" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="616" spans="1:11" x14ac:dyDescent="0.35">
@@ -25539,10 +25536,10 @@
         <v>26</v>
       </c>
       <c r="J616" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K616" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="617" spans="1:11" x14ac:dyDescent="0.35">
@@ -25575,10 +25572,10 @@
         <v>36</v>
       </c>
       <c r="J617" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K617" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="618" spans="1:11" x14ac:dyDescent="0.35">
@@ -25611,10 +25608,10 @@
         <v>0</v>
       </c>
       <c r="J618" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K618" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="619" spans="1:11" x14ac:dyDescent="0.35">
@@ -25647,10 +25644,10 @@
         <v>0</v>
       </c>
       <c r="J619" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K619" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="620" spans="1:11" x14ac:dyDescent="0.35">
@@ -25683,10 +25680,10 @@
         <v>0</v>
       </c>
       <c r="J620" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K620" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="621" spans="1:11" x14ac:dyDescent="0.35">
@@ -25719,10 +25716,10 @@
         <v>69</v>
       </c>
       <c r="J621" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K621" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="622" spans="1:11" x14ac:dyDescent="0.35">
@@ -25755,10 +25752,10 @@
         <v>47</v>
       </c>
       <c r="J622" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K622" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="623" spans="1:11" x14ac:dyDescent="0.35">
@@ -25791,10 +25788,10 @@
         <v>27</v>
       </c>
       <c r="J623" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K623" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="624" spans="1:11" x14ac:dyDescent="0.35">
@@ -25827,10 +25824,10 @@
         <v>0</v>
       </c>
       <c r="J624" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K624" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="625" spans="1:11" x14ac:dyDescent="0.35">
@@ -25863,10 +25860,10 @@
         <v>2</v>
       </c>
       <c r="J625" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K625" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="626" spans="1:11" x14ac:dyDescent="0.35">
@@ -25899,10 +25896,10 @@
         <v>0</v>
       </c>
       <c r="J626" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K626" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="627" spans="1:11" x14ac:dyDescent="0.35">
@@ -25935,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="J627" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K627" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="628" spans="1:11" x14ac:dyDescent="0.35">
@@ -25971,10 +25968,10 @@
         <v>49</v>
       </c>
       <c r="J628" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K628" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="629" spans="1:11" x14ac:dyDescent="0.35">
@@ -26007,10 +26004,10 @@
         <v>0</v>
       </c>
       <c r="J629" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K629" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="630" spans="1:11" x14ac:dyDescent="0.35">
@@ -26043,10 +26040,10 @@
         <v>0</v>
       </c>
       <c r="J630" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K630" s="12" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="631" spans="1:11" x14ac:dyDescent="0.35">
@@ -26079,10 +26076,10 @@
         <v>47</v>
       </c>
       <c r="J631" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K631" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="632" spans="1:11" x14ac:dyDescent="0.35">
@@ -26099,25 +26096,25 @@
         <v>-60.994610000000002</v>
       </c>
       <c r="E632" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F632" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G632" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H632" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I632" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="J632" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K632" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
   </sheetData>
